--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE180D5-10A1-4978-9C92-38CF9F47855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F302DD-5E29-45DD-82C5-FB9C09690B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -902,15 +902,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>山下実優
-中島翔子
-上福ゆき</t>
-    <rPh sb="5" eb="9">
-      <t>ナカジマショウコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>渡辺未詩
 原宿ぽむ
 らく
@@ -1063,10 +1054,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;Y&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;彩夢&gt;</t>
   </si>
   <si>
@@ -1537,14 +1524,6 @@
     <rPh sb="24" eb="25">
       <t>キュウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>郷田明日香(休)
-ブランキー真帆(休)
-Chi Chi
-ZONES
-勇気みなみ(休)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1793,6 +1772,31 @@
 &lt;さとうもも&gt;(7/18デビュー予定)</t>
     <rPh sb="25" eb="27">
       <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郷田明日香(休)
+ブランキー真帆
+Chi Chi
+ZONES
+勇気みなみ(休)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;Y&gt;
+&lt;みく&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山下実優
+中島翔子
+上福ゆき(2026.12.26引退)</t>
+    <rPh sb="5" eb="9">
+      <t>ナカジマショウコ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>インタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2784,7 +2788,7 @@
     <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2848,7 +2852,7 @@
      LEN(J5:J1001) - LEN(SUBSTITUTE(J5:J1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1" cm="1">
         <f t="array" ref="K2">SUMPRODUCT(
@@ -3014,7 +3018,7 @@
         <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3032,7 +3036,7 @@
         <v>113</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>87</v>
@@ -3638,10 +3642,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -3673,7 +3677,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
@@ -3929,7 +3933,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -3943,7 +3947,7 @@
         <v>56</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -3993,7 +3997,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -4003,7 +4007,7 @@
         <v>84</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4063,13 +4067,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4089,7 +4093,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4212,7 +4216,7 @@
         <v>122</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>39</v>
@@ -4242,7 +4246,7 @@
         <v>89</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
@@ -4255,15 +4259,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>129</v>
+        <v>233</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4276,7 +4280,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4287,7 +4291,7 @@
         <v>128</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -4299,7 +4303,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4322,10 +4326,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -4337,7 +4341,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4365,7 +4369,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4377,7 +4381,7 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -4405,7 +4409,7 @@
         <v>111</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4417,7 +4421,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4439,13 +4443,13 @@
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4467,16 +4471,16 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
@@ -4488,7 +4492,7 @@
         <v>65</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
@@ -4506,10 +4510,10 @@
         <v>91</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4521,7 +4525,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4536,7 +4540,7 @@
         <v>21</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>66</v>
@@ -4556,10 +4560,10 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4598,10 +4602,10 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -4616,16 +4620,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>26</v>
@@ -4648,11 +4652,11 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="1"/>
@@ -4665,19 +4669,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
@@ -4692,7 +4696,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4700,14 +4704,14 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -4722,16 +4726,16 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3" t="s">
@@ -4745,7 +4749,7 @@
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>106</v>
@@ -4760,14 +4764,14 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4791,26 +4795,26 @@
         <v>121</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>103</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -4824,7 +4828,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -4837,38 +4841,38 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4876,11 +4880,11 @@
         <v>115</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -4894,29 +4898,29 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -4924,7 +4928,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -4934,34 +4938,34 @@
     </row>
     <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
@@ -4970,7 +4974,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5059,7 +5063,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5279,7 +5283,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5330,7 +5334,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5399,7 +5403,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5419,29 +5423,29 @@
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5450,10 +5454,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F302DD-5E29-45DD-82C5-FB9C09690B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5615649-72B9-48B1-9497-8DDCC2E4CFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="28598" yWindow="2602" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1401,27 +1401,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;七世真理子&gt;(Rose)
-&lt;星野 さやか&gt;(九州女子プロレス)
-&lt;今野結菜&gt;(伊藤道場)(仮合格)</t>
-    <rPh sb="23" eb="27">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ドウジョウ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>志真うた(伊藤道場)
 CoCo(MyWay)
 大竹仁美(BBJ)
@@ -1634,11 +1613,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>堀このみ(Rose)
-彩桜(アップタウン)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>リアラ(休)</t>
     <rPh sb="4" eb="5">
       <t>キュウ</t>
@@ -1798,6 +1772,20 @@
     <rPh sb="25" eb="27">
       <t>インタイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;七世真理子&gt;(Rose)
+&lt;星野 さやか&gt;(九州女子プロレス)</t>
+    <rPh sb="23" eb="27">
+      <t>キュウシュウジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堀このみ(Rose)
+彩桜(アップタウン)
+結菜(伊藤道場)(休)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3645,7 +3633,7 @@
         <v>152</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -3997,7 +3985,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -4007,7 +3995,7 @@
         <v>84</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -4073,7 +4061,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4093,7 +4081,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4263,11 +4251,11 @@
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4280,7 +4268,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4369,7 +4357,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4409,7 +4397,7 @@
         <v>111</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4449,7 +4437,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4471,7 +4459,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>138</v>
@@ -4480,7 +4468,7 @@
         <v>129</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
@@ -4510,10 +4498,10 @@
         <v>91</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4602,7 +4590,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>174</v>
@@ -4620,7 +4608,7 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>182</v>
@@ -4669,7 +4657,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>132</v>
@@ -4681,7 +4669,7 @@
         <v>131</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="s">
@@ -4729,7 +4717,7 @@
         <v>162</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>187</v>
@@ -4764,14 +4752,14 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4795,13 +4783,13 @@
         <v>121</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>102</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>71</v>
@@ -4844,20 +4832,20 @@
         <v>167</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>148</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>180</v>
@@ -4869,10 +4857,10 @@
         <v>158</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4884,7 +4872,7 @@
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -4898,7 +4886,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>166</v>
@@ -4908,7 +4896,7 @@
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
@@ -4928,7 +4916,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -4942,26 +4930,26 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3" t="s">
@@ -4974,7 +4962,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5434,7 +5422,7 @@
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5615649-72B9-48B1-9497-8DDCC2E4CFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4874574D-8899-4FB3-8036-CD694B1BECD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28598" yWindow="2602" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="235">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -558,15 +558,6 @@
   <si>
     <t>山縣優
 唯我</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>柊くるみ(PR)
-夏実もち(PR)
-LINDA(信州)</t>
-    <rPh sb="24" eb="26">
-      <t>シンシュウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1054,9 +1045,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;彩夢&gt;</t>
-  </si>
-  <si>
     <t>小夏れん</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1179,10 +1167,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>神嵜志音</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鉄アキラ
 姫ゆりあ
 金屋あんね
@@ -1197,19 +1181,6 @@
 琉悪夏</t>
     <rPh sb="11" eb="14">
       <t>ルアカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スターライト・キッド
-なつぽい
-安納サオリ
-小波</t>
-    <rPh sb="16" eb="18">
-      <t>アノウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>コナミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1444,27 +1415,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>なる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>松橋ななを?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;州王叶多&gt;(すおうかなた, プロテスト合格)</t>
-    <rPh sb="1" eb="2">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カナタ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ゴウカク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1537,33 +1488,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>風城ハル
-芦田美歩(別名あり)
-大久保琉那(休)
-鈴木志乃(休)
-凍雅
-上原わかな</t>
-    <rPh sb="5" eb="9">
-      <t>アシダミフ</t>
-    </rPh>
-    <rPh sb="16" eb="21">
-      <t>オオクボルナ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ヤス</t>
-    </rPh>
-    <rPh sb="25" eb="29">
-      <t>スズキシノ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>トウガ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ウエハラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>松井珠紗</t>
     <rPh sb="0" eb="4">
       <t>マツイミサ</t>
@@ -1591,28 +1515,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>吏南
-妃南
-鈴季すず
-水森由菜
-星来芽依
-ジーナ
-林下詩美</t>
-    <rPh sb="6" eb="8">
-      <t>スズキ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ミズモリ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ユナ</t>
-    </rPh>
-    <rPh sb="16" eb="20">
-      <t>セイラメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>リアラ(休)</t>
     <rPh sb="4" eb="5">
       <t>キュウ</t>
@@ -1640,13 +1542,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;高野玲菜&gt;プロテスト合格</t>
-    <rPh sb="11" eb="13">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>山岡聖怜(休)
 心希
 山﨑裕花</t>
@@ -1663,10 +1558,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Anna</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>天咲光由
 ボジラ(休)</t>
     <rPh sb="9" eb="10">
@@ -1738,14 +1629,6 @@
 ノア・ヒカリ</t>
     <rPh sb="0" eb="2">
       <t>アイカワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;ユウカ&gt;(仮)
-&lt;さとうもも&gt;(7/18デビュー予定)</t>
-    <rPh sb="25" eb="27">
-      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1758,11 +1641,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;Y&gt;
-&lt;みく&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>山下実優
 中島翔子
 上福ゆき(2026.12.26引退)</t>
@@ -1786,6 +1664,151 @@
     <t>堀このみ(Rose)
 彩桜(アップタウン)
 結菜(伊藤道場)(休)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吏南
+妃南
+鈴季すず
+水森由菜
+星来芽依
+林下詩美</t>
+    <rPh sb="6" eb="8">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ミズモリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ユナ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>セイラメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なる(11月引退予定)</t>
+    <rPh sb="5" eb="6">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>インタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Anna
+Fiony</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)
+清司麗菜(8/1デビュー予定)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神嵜志音
+さとうもも</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>柊くるみ(PR)(2026.9.21より休予定)
+夏実もち(PR)
+LINDA(信州)</t>
+    <rPh sb="20" eb="21">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;Y&gt;
+&lt;みく&gt;
+&lt;ちゅら愛花&gt;(8.11デビュー予定)</t>
+    <rPh sb="13" eb="14">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;濱名亜実&gt;(はまな あみ)
+&lt;椿本浩子&gt;(つばきもと ひろこ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高野玲菜</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;洲王叶多&gt;(すおうかなた, プロテスト合格)</t>
+    <rPh sb="20" eb="22">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風城ハル
+芦田美歩(別名あり)
+大久保琉那(休)
+鈴木志乃
+凍雅
+上原わかな</t>
+    <rPh sb="5" eb="9">
+      <t>アシダミフ</t>
+    </rPh>
+    <rPh sb="16" eb="21">
+      <t>オオクボルナ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヤス</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>スズキシノ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>トウガ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ウエハラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スターライト・キッド
+なつぽい(2027.1.3引退予定)
+安納サオリ
+小波</t>
+    <rPh sb="24" eb="26">
+      <t>インタイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>アノウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>コナミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;MIHO&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1871,28 +1894,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2073,6 +2074,28 @@
         <charset val="128"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2381,22 +2404,22 @@
     <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="17"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="3"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="14"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="12"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="10"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="0"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="2"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="14"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="12"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="11"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="7"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2719,7 +2742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AD56"/>
+  <dimension ref="A1:AH56"/>
   <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
@@ -2729,54 +2752,58 @@
     <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.3125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.9375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="30.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="21.3125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="27.3125" style="1"/>
-    <col min="31" max="16384" width="27.3125" style="1"/>
+    <col min="8" max="8" width="27.3125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.9375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="30.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="27.3125" style="1"/>
+    <col min="35" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="L1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH1" s="1"/>
+    </row>
+    <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2784,7 +2811,7 @@
      LEN(C5:C1001) - LEN(SUBSTITUTE(C5:C1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" cm="1">
         <f t="array" ref="D2">SUMPRODUCT(
@@ -2800,7 +2827,7 @@
      LEN(E5:E1001) - LEN(SUBSTITUTE(E5:E1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" cm="1">
         <f t="array" ref="F2">SUMPRODUCT(
@@ -2816,7 +2843,7 @@
      LEN(G5:G1001) - LEN(SUBSTITUTE(G5:G1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
@@ -2824,7 +2851,7 @@
      LEN(H5:H1001) - LEN(SUBSTITUTE(H5:H1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" cm="1">
         <f t="array" ref="I2">SUMPRODUCT(
@@ -2832,7 +2859,7 @@
      LEN(I5:I1001) - LEN(SUBSTITUTE(I5:I1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J2" s="1" cm="1">
         <f t="array" ref="J2">SUMPRODUCT(
@@ -2848,7 +2875,7 @@
      LEN(K5:K1001) - LEN(SUBSTITUTE(K5:K1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="1" cm="1">
         <f t="array" ref="L2">SUMPRODUCT(
@@ -2864,7 +2891,7 @@
      LEN(M5:M1001) - LEN(SUBSTITUTE(M5:M1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
@@ -2880,7 +2907,7 @@
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P2" s="1" cm="1">
         <f t="array" ref="P2">SUMPRODUCT(
@@ -2947,28 +2974,34 @@
         <v>51</v>
       </c>
       <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-    </row>
-    <row r="3" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH2" s="1"/>
+    </row>
+    <row r="3" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="L3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-    </row>
-    <row r="4" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH3" s="1"/>
+    </row>
+    <row r="4" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -2988,25 +3021,25 @@
         <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="K4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3021,13 +3054,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>33</v>
@@ -3036,11 +3069,13 @@
         <v>9</v>
       </c>
       <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-    </row>
-    <row r="5" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH4" s="1"/>
+    </row>
+    <row r="5" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3049,10 +3084,10 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -3068,11 +3103,13 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-    </row>
-    <row r="6" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH5" s="1"/>
+    </row>
+    <row r="6" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3098,11 +3135,13 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-    </row>
-    <row r="7" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH6" s="1"/>
+    </row>
+    <row r="7" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3128,11 +3167,13 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-    </row>
-    <row r="8" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH7" s="1"/>
+    </row>
+    <row r="8" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3141,11 +3182,11 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3162,11 +3203,13 @@
         <v>28</v>
       </c>
       <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-    </row>
-    <row r="9" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH8" s="1"/>
+    </row>
+    <row r="9" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3192,11 +3235,13 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-    </row>
-    <row r="10" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH9" s="1"/>
+    </row>
+    <row r="10" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3222,11 +3267,13 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-    </row>
-    <row r="11" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH10" s="1"/>
+    </row>
+    <row r="11" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3252,11 +3299,13 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-    </row>
-    <row r="12" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH11" s="1"/>
+    </row>
+    <row r="12" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3282,11 +3331,13 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-    </row>
-    <row r="13" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH12" s="1"/>
+    </row>
+    <row r="13" spans="1:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3310,15 +3361,17 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-    </row>
-    <row r="14" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH13" s="1"/>
+    </row>
+    <row r="14" spans="1:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3350,11 +3403,13 @@
         <v>13</v>
       </c>
       <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-    </row>
-    <row r="15" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH14" s="1"/>
+    </row>
+    <row r="15" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3379,14 +3434,16 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-    </row>
-    <row r="16" spans="1:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH15" s="1"/>
+    </row>
+    <row r="16" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3395,10 +3452,10 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -3416,11 +3473,13 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-    </row>
-    <row r="17" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH16" s="1"/>
+    </row>
+    <row r="17" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3444,17 +3503,19 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-    </row>
-    <row r="18" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH17" s="1"/>
+    </row>
+    <row r="18" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3480,11 +3541,13 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
-    </row>
-    <row r="19" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH18" s="1"/>
+    </row>
+    <row r="19" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3510,11 +3573,13 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
-    </row>
-    <row r="20" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH19" s="1"/>
+    </row>
+    <row r="20" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3540,11 +3605,13 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
-    </row>
-    <row r="21" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH20" s="1"/>
+    </row>
+    <row r="21" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3570,11 +3637,13 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
-    </row>
-    <row r="22" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH21" s="1"/>
+    </row>
+    <row r="22" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3600,11 +3669,13 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
-    </row>
-    <row r="23" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH22" s="1"/>
+    </row>
+    <row r="23" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3616,11 +3687,11 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -3630,17 +3701,19 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
-    </row>
-    <row r="24" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH23" s="1"/>
+    </row>
+    <row r="24" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3665,14 +3738,16 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
-    </row>
-    <row r="25" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH24" s="1"/>
+    </row>
+    <row r="25" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3686,7 +3761,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3702,11 +3777,13 @@
         <v>75</v>
       </c>
       <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
-    </row>
-    <row r="26" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH25" s="1"/>
+    </row>
+    <row r="26" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3736,11 +3813,13 @@
         <v>30</v>
       </c>
       <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
-    </row>
-    <row r="27" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH26" s="1"/>
+    </row>
+    <row r="27" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3770,11 +3849,13 @@
       </c>
       <c r="W27" s="3"/>
       <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
-    </row>
-    <row r="28" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH27" s="1"/>
+    </row>
+    <row r="28" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3790,7 +3871,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3806,11 +3887,13 @@
         <v>77</v>
       </c>
       <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
-    </row>
-    <row r="29" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH28" s="1"/>
+    </row>
+    <row r="29" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3819,10 +3902,10 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -3840,11 +3923,13 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
-    </row>
-    <row r="30" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH29" s="1"/>
+    </row>
+    <row r="30" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3872,11 +3957,13 @@
       </c>
       <c r="W30" s="3"/>
       <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
-    </row>
-    <row r="31" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH30" s="1"/>
+    </row>
+    <row r="31" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3902,11 +3989,13 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
-    </row>
-    <row r="32" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH31" s="1"/>
+    </row>
+    <row r="32" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -3918,11 +4007,11 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="L32" s="3"/>
-      <c r="M32" s="3" t="s">
-        <v>191</v>
-      </c>
+      <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -3935,14 +4024,16 @@
         <v>56</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
-    </row>
-    <row r="33" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH32" s="1"/>
+    </row>
+    <row r="33" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -3962,21 +4053,23 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W33" s="3"/>
       <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
-    </row>
-    <row r="34" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH33" s="1"/>
+    </row>
+    <row r="34" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -3985,18 +4078,18 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="L34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>202</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -4009,14 +4102,16 @@
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
-    </row>
-    <row r="35" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH34" s="1"/>
+    </row>
+    <row r="35" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4039,29 +4134,31 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
-    </row>
-    <row r="36" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH35" s="1"/>
+    </row>
+    <row r="36" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4081,14 +4178,16 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
-    </row>
-    <row r="37" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH36" s="1"/>
+    </row>
+    <row r="37" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4116,11 +4215,13 @@
       </c>
       <c r="W37" s="3"/>
       <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
-    </row>
-    <row r="38" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH37" s="1"/>
+    </row>
+    <row r="38" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4132,11 +4233,11 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3" t="s">
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
@@ -4148,15 +4249,17 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
-    </row>
-    <row r="39" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH38" s="1"/>
+    </row>
+    <row r="39" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4164,19 +4267,19 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="L39" s="3"/>
-      <c r="M39" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4189,38 +4292,40 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
-    </row>
-    <row r="40" spans="2:30" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH39" s="1"/>
+    </row>
+    <row r="40" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4231,31 +4336,33 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
-    </row>
-    <row r="41" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH40" s="1"/>
+    </row>
+    <row r="41" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4268,30 +4375,32 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
-    </row>
-    <row r="42" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH41" s="1"/>
+    </row>
+    <row r="42" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4314,22 +4423,24 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
-    </row>
-    <row r="43" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH42" s="1"/>
+    </row>
+    <row r="43" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4340,11 +4451,11 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
+      <c r="K43" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="L43" s="3"/>
-      <c r="M43" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -4353,23 +4464,25 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
-    </row>
-    <row r="44" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH43" s="1"/>
+    </row>
+    <row r="44" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -4377,11 +4490,11 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4394,22 +4507,24 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
-    </row>
-    <row r="45" spans="2:30" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH44" s="1"/>
+    </row>
+    <row r="45" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4417,72 +4532,74 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3" t="s">
-        <v>117</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
+      <c r="K45" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="L45" s="3"/>
-      <c r="M45" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
-    </row>
-    <row r="46" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AH45" s="1"/>
+    </row>
+    <row r="46" spans="2:34" ht="148.5" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G46" s="3"/>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3" t="s">
+      <c r="K46" s="3"/>
+      <c r="L46" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
@@ -4491,29 +4608,31 @@
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
-    </row>
-    <row r="47" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH46" s="1"/>
+    </row>
+    <row r="47" spans="2:34" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4521,23 +4640,23 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H47" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="I47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>163</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4548,17 +4667,19 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
-    </row>
-    <row r="48" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH47" s="1"/>
+    </row>
+    <row r="48" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4576,7 +4697,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4584,23 +4705,25 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
-    </row>
-    <row r="49" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH48" s="1"/>
+    </row>
+    <row r="49" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4608,23 +4731,23 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H49" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -4640,51 +4763,53 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
-    </row>
-    <row r="50" spans="2:30" ht="132" x14ac:dyDescent="0.7">
+      <c r="AH49" s="1"/>
+    </row>
+    <row r="50" spans="2:34" ht="132" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="H50" s="3"/>
+        <v>211</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="I50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K50" s="3" t="s">
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
       <c r="N50" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4692,21 +4817,23 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
-    </row>
-    <row r="51" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH50" s="1"/>
+    </row>
+    <row r="51" spans="2:34" ht="132" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4714,59 +4841,61 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H51" s="3"/>
+        <v>159</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="I51" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J51" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-    </row>
-    <row r="52" spans="2:30" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH51" s="1"/>
+    </row>
+    <row r="52" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4780,29 +4909,29 @@
         <v>42</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="M52" s="3"/>
+      <c r="M52" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="N52" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -4811,104 +4940,110 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
-    </row>
-    <row r="53" spans="2:30" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AH52" s="1"/>
+    </row>
+    <row r="53" spans="2:34" ht="165" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H53" s="3"/>
+        <v>92</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="I53" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>180</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+      <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
-    </row>
-    <row r="54" spans="2:30" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH53" s="1"/>
+    </row>
+    <row r="54" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>166</v>
+        <v>226</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G54" s="3"/>
-      <c r="H54" s="3" t="s">
-        <v>199</v>
-      </c>
+      <c r="H54" s="3"/>
       <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
+      <c r="J54" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="L54" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -4916,45 +5051,47 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+      <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
-    </row>
-    <row r="55" spans="2:30" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH54" s="1"/>
+    </row>
+    <row r="55" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-      <c r="M55" s="3" t="s">
-        <v>215</v>
-      </c>
+      <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-      <c r="O55" s="3" t="s">
-        <v>147</v>
-      </c>
+      <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
@@ -4962,26 +5099,28 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+      <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
-    </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.7">
+      <c r="AH55" s="1"/>
+    </row>
+    <row r="56" spans="2:34" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
+      <c r="J56" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -4996,10 +5135,10 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
-      <c r="AA56"/>
+      <c r="AB56" s="1"/>
+      <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
+      <c r="AH56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5051,7 +5190,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5271,7 +5410,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5322,7 +5461,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5356,7 +5495,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5391,7 +5530,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5406,34 +5545,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5442,10 +5581,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4874574D-8899-4FB3-8036-CD694B1BECD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247A068A-AAFD-4B39-B84E-E5BEFD2555C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="236">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1216,21 +1216,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>バニー及川
-マドレーヌ
-ウナギ・サヤカ
-松澤さん
-rhythm
-山中絵里奈</t>
-    <rPh sb="3" eb="5">
-      <t>オイカワ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>マツザワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>未愛</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1653,14 +1638,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;七世真理子&gt;(Rose)
-&lt;星野 さやか&gt;(九州女子プロレス)</t>
-    <rPh sb="23" eb="27">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>堀このみ(Rose)
 彩桜(アップタウン)
 結菜(伊藤道場)(休)</t>
@@ -1809,6 +1786,35 @@
   </si>
   <si>
     <t>&lt;MIHO&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バニー及川
+マドレーヌ
+ウナギ・サヤカ
+松澤さん
+rhythm</t>
+    <rPh sb="3" eb="5">
+      <t>オイカワ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>マツザワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山中絵里奈</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;七世真理子&gt;(Rose)(2026.10.17デビュー予定)
+&lt;星野 さやか&gt;(九州女子プロレス)</t>
+    <rPh sb="28" eb="30">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>キュウシュウジョシ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1894,6 +1900,28 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2074,28 +2102,6 @@
         <charset val="128"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2404,22 +2410,22 @@
     <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="17"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="3"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="0"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="2"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="14"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="12"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="7"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="10"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2762,7 +2768,7 @@
     <col min="19" max="19" width="12.3125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.5625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.9375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="50.0625" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11.875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.9375" style="1" bestFit="1" customWidth="1"/>
@@ -2835,7 +2841,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -2971,7 +2977,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="X2" s="1"/>
       <c r="AA2" s="1"/>
@@ -3704,7 +3710,7 @@
         <v>150</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="X23" s="1"/>
       <c r="AA23" s="1"/>
@@ -4008,7 +4014,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -4024,7 +4030,7 @@
         <v>56</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X32" s="1"/>
       <c r="AA32" s="1"/>
@@ -4078,13 +4084,13 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>83</v>
@@ -4158,7 +4164,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4178,7 +4184,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X36" s="1"/>
       <c r="AA36" s="1"/>
@@ -4249,7 +4255,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
@@ -4354,15 +4360,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4375,7 +4381,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4386,7 +4392,7 @@
         <v>127</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X41" s="1"/>
       <c r="AA41" s="1"/>
@@ -4423,7 +4429,7 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>167</v>
@@ -4440,7 +4446,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4468,7 +4474,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X43" s="1"/>
       <c r="AA43" s="1"/>
@@ -4510,7 +4516,7 @@
         <v>110</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X44" s="1"/>
       <c r="AA44" s="1"/>
@@ -4552,7 +4558,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4576,7 +4582,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>137</v>
@@ -4585,7 +4591,7 @@
         <v>128</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4595,7 +4601,7 @@
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>65</v>
@@ -4615,10 +4621,10 @@
         <v>90</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X46" s="1"/>
       <c r="AA46" s="1"/>
@@ -4627,7 +4633,7 @@
       <c r="AD46" s="1"/>
       <c r="AH46" s="1"/>
     </row>
-    <row r="47" spans="2:34" ht="115.5" x14ac:dyDescent="0.7">
+    <row r="47" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
@@ -4638,7 +4644,9 @@
       <c r="E47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="G47" s="3" t="s">
         <v>93</v>
       </c>
@@ -4670,7 +4678,7 @@
         <v>139</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="X47" s="1"/>
       <c r="AA47" s="1"/>
@@ -4711,7 +4719,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>170</v>
@@ -4731,16 +4739,16 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
@@ -4782,7 +4790,7 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>131</v>
@@ -4794,7 +4802,7 @@
         <v>130</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -4844,10 +4852,10 @@
         <v>160</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>159</v>
@@ -4879,14 +4887,14 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X51" s="1"/>
       <c r="AA51" s="1"/>
@@ -4912,10 +4920,10 @@
         <v>120</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>71</v>
@@ -4928,7 +4936,7 @@
         <v>102</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>153</v>
@@ -4945,7 +4953,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -4963,22 +4971,22 @@
         <v>164</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>146</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>92</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -4988,10 +4996,10 @@
         <v>156</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5003,7 +5011,7 @@
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -5019,25 +5027,25 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
@@ -5051,7 +5059,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -5061,31 +5069,31 @@
       <c r="AD54" s="1"/>
       <c r="AH54" s="1"/>
     </row>
-    <row r="55" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+    <row r="55" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
         <v>147</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
@@ -5099,7 +5107,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5561,7 +5569,7 @@
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
@@ -5581,7 +5589,7 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>147</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247A068A-AAFD-4B39-B84E-E5BEFD2555C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3627A45-05DC-4221-9008-8B346BC702F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="2610" yWindow="397" windowWidth="17183" windowHeight="14633" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="237">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -394,13 +394,6 @@
     </rPh>
     <rPh sb="5" eb="9">
       <t>ハシモトチヒロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>岡優里佳</t>
-    <rPh sb="0" eb="4">
-      <t>オカユリカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1638,12 +1631,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>堀このみ(Rose)
-彩桜(アップタウン)
-結菜(伊藤道場)(休)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>吏南
 妃南
 鈴季すず
@@ -1815,6 +1802,25 @@
     <rPh sb="41" eb="45">
       <t>キュウシュウジョシ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堀このみ(Rose)(休)
+彩桜(アップタウン)
+結菜(伊藤道場)(休)
+志翠ヒカリ(EVO)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>岡優里佳
+アニータ・ヴォーン</t>
+    <rPh sb="0" eb="4">
+      <t>オカユリカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サファイア・リード</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1900,6 +1906,26 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2022,26 +2048,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2412,20 +2418,20 @@
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="10"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="11"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2748,7 +2754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AI56"/>
   <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
@@ -2759,57 +2765,58 @@
     <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.3125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.3125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.9375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="50.0625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="21.3125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="30.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="27.3125" style="1"/>
-    <col min="35" max="16384" width="27.3125" style="1"/>
+    <col min="10" max="10" width="21.3125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.3125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.9375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="50.0625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="30.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="27.3125" style="1"/>
+    <col min="36" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="M1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="P1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="V1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="AA1" s="1"/>
+      <c r="Y1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
-      <c r="AH1" s="1"/>
-    </row>
-    <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE1" s="1"/>
+      <c r="AI1" s="1"/>
+    </row>
+    <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2873,7 +2880,7 @@
      LEN(J5:J1001) - LEN(SUBSTITUTE(J5:J1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" s="1" cm="1">
         <f t="array" ref="K2">SUMPRODUCT(
@@ -2881,7 +2888,7 @@
      LEN(K5:K1001) - LEN(SUBSTITUTE(K5:K1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" s="1" cm="1">
         <f t="array" ref="L2">SUMPRODUCT(
@@ -2901,113 +2908,115 @@
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
-  IF(LEN(N5:N1001)=0, 0,
-     LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" cm="1">
-        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(O5:O1001)=0, 0,
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="P2" s="1" cm="1">
-        <f t="array" ref="P2">SUMPRODUCT(
+      <c r="O2" s="1" cm="1">
+        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(P5:P1001)=0, 0,
      LEN(P5:P1001) - LEN(SUBSTITUTE(P5:P1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="Q2" s="1" cm="1">
-        <f t="array" ref="Q2">SUMPRODUCT(
+      <c r="P2" s="1" cm="1">
+        <f t="array" ref="P2">SUMPRODUCT(
   IF(LEN(Q5:Q1001)=0, 0,
      LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
+      <c r="Q2" s="1" cm="1">
+        <f t="array" ref="Q2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>8</v>
       </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>53</v>
-      </c>
-      <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2">SUMPRODUCT(
+        <v>54</v>
+      </c>
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
   IF(LEN(W5:W1001)=0, 0,
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>50</v>
       </c>
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2">SUMPRODUCT(
+  IF(LEN(X5:X1001)=0, 0,
+     LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>0</v>
+      </c>
       <c r="X2" s="1"/>
-      <c r="AA2" s="1"/>
+      <c r="Y2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AH2" s="1"/>
-    </row>
-    <row r="3" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE2" s="1"/>
+      <c r="AI2" s="1"/>
+    </row>
+    <row r="3" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="N3" s="1"/>
+      <c r="M3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="P3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
-      <c r="W3" s="1"/>
+      <c r="V3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="AA3" s="1"/>
+      <c r="Y3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AH3" s="1"/>
-    </row>
-    <row r="4" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE3" s="1"/>
+      <c r="AI3" s="1"/>
+    </row>
+    <row r="4" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -3024,7 +3033,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
@@ -3033,19 +3042,19 @@
         <v>45</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="L4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3060,13 +3069,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>33</v>
@@ -3075,13 +3084,14 @@
         <v>9</v>
       </c>
       <c r="X4" s="1"/>
-      <c r="AA4" s="1"/>
+      <c r="Y4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AH4" s="1"/>
-    </row>
-    <row r="5" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE4" s="1"/>
+      <c r="AI4" s="1"/>
+    </row>
+    <row r="5" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3109,13 +3119,14 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="1"/>
-      <c r="AA5" s="1"/>
+      <c r="Y5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AH5" s="1"/>
-    </row>
-    <row r="6" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE5" s="1"/>
+      <c r="AI5" s="1"/>
+    </row>
+    <row r="6" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3141,13 +3152,14 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="1"/>
-      <c r="AA6" s="1"/>
+      <c r="Y6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AH6" s="1"/>
-    </row>
-    <row r="7" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE6" s="1"/>
+      <c r="AI6" s="1"/>
+    </row>
+    <row r="7" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3173,13 +3185,14 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="1"/>
-      <c r="AA7" s="1"/>
+      <c r="Y7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AH7" s="1"/>
-    </row>
-    <row r="8" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE7" s="1"/>
+      <c r="AI7" s="1"/>
+    </row>
+    <row r="8" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3190,10 +3203,10 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -3209,13 +3222,14 @@
         <v>28</v>
       </c>
       <c r="X8" s="1"/>
-      <c r="AA8" s="1"/>
+      <c r="Y8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AH8" s="1"/>
-    </row>
-    <row r="9" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE8" s="1"/>
+      <c r="AI8" s="1"/>
+    </row>
+    <row r="9" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3241,13 +3255,14 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="1"/>
-      <c r="AA9" s="1"/>
+      <c r="Y9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AH9" s="1"/>
-    </row>
-    <row r="10" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE9" s="1"/>
+      <c r="AI9" s="1"/>
+    </row>
+    <row r="10" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3273,13 +3288,14 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="1"/>
-      <c r="AA10" s="1"/>
+      <c r="Y10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AH10" s="1"/>
-    </row>
-    <row r="11" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE10" s="1"/>
+      <c r="AI10" s="1"/>
+    </row>
+    <row r="11" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3305,13 +3321,14 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="1"/>
-      <c r="AA11" s="1"/>
+      <c r="Y11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AH11" s="1"/>
-    </row>
-    <row r="12" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE11" s="1"/>
+      <c r="AI11" s="1"/>
+    </row>
+    <row r="12" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3337,13 +3354,14 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="1"/>
-      <c r="AA12" s="1"/>
+      <c r="Y12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AH12" s="1"/>
-    </row>
-    <row r="13" spans="1:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE12" s="1"/>
+      <c r="AI12" s="1"/>
+    </row>
+    <row r="13" spans="1:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3367,17 +3385,18 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="1"/>
-      <c r="AA13" s="1"/>
+      <c r="Y13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AH13" s="1"/>
-    </row>
-    <row r="14" spans="1:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE13" s="1"/>
+      <c r="AI13" s="1"/>
+    </row>
+    <row r="14" spans="1:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3403,19 +3422,20 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="X14" s="1"/>
-      <c r="AA14" s="1"/>
+      <c r="Y14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AH14" s="1"/>
-    </row>
-    <row r="15" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE14" s="1"/>
+      <c r="AI14" s="1"/>
+    </row>
+    <row r="15" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3440,16 +3460,17 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X15" s="1"/>
-      <c r="AA15" s="1"/>
+      <c r="Y15" s="1"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AH15" s="1"/>
-    </row>
-    <row r="16" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE15" s="1"/>
+      <c r="AI15" s="1"/>
+    </row>
+    <row r="16" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3479,13 +3500,14 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="1"/>
-      <c r="AA16" s="1"/>
+      <c r="Y16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AH16" s="1"/>
-    </row>
-    <row r="17" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE16" s="1"/>
+      <c r="AI16" s="1"/>
+    </row>
+    <row r="17" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3509,19 +3531,20 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X17" s="1"/>
-      <c r="AA17" s="1"/>
+      <c r="Y17" s="1"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AH17" s="1"/>
-    </row>
-    <row r="18" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE17" s="1"/>
+      <c r="AI17" s="1"/>
+    </row>
+    <row r="18" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3547,13 +3570,14 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="1"/>
-      <c r="AA18" s="1"/>
+      <c r="Y18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
-      <c r="AH18" s="1"/>
-    </row>
-    <row r="19" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE18" s="1"/>
+      <c r="AI18" s="1"/>
+    </row>
+    <row r="19" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3579,13 +3603,14 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="1"/>
-      <c r="AA19" s="1"/>
+      <c r="Y19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
-      <c r="AH19" s="1"/>
-    </row>
-    <row r="20" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE19" s="1"/>
+      <c r="AI19" s="1"/>
+    </row>
+    <row r="20" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3611,13 +3636,14 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="1"/>
-      <c r="AA20" s="1"/>
+      <c r="Y20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
-      <c r="AH20" s="1"/>
-    </row>
-    <row r="21" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE20" s="1"/>
+      <c r="AI20" s="1"/>
+    </row>
+    <row r="21" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3643,13 +3669,14 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="1"/>
-      <c r="AA21" s="1"/>
+      <c r="Y21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
-      <c r="AH21" s="1"/>
-    </row>
-    <row r="22" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE21" s="1"/>
+      <c r="AI21" s="1"/>
+    </row>
+    <row r="22" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3675,13 +3702,14 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="1"/>
-      <c r="AA22" s="1"/>
+      <c r="Y22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
-      <c r="AH22" s="1"/>
-    </row>
-    <row r="23" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE22" s="1"/>
+      <c r="AI22" s="1"/>
+    </row>
+    <row r="23" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3696,7 +3724,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3707,19 +3735,20 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X23" s="1"/>
-      <c r="AA23" s="1"/>
+      <c r="Y23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
-      <c r="AH23" s="1"/>
-    </row>
-    <row r="24" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE23" s="1"/>
+      <c r="AI23" s="1"/>
+    </row>
+    <row r="24" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3744,16 +3773,17 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="X24" s="1"/>
-      <c r="AA24" s="1"/>
+      <c r="Y24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
-      <c r="AH24" s="1"/>
-    </row>
-    <row r="25" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE24" s="1"/>
+      <c r="AI24" s="1"/>
+    </row>
+    <row r="25" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3767,7 +3797,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3780,16 +3810,17 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X25" s="1"/>
-      <c r="AA25" s="1"/>
+      <c r="Y25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
-      <c r="AH25" s="1"/>
-    </row>
-    <row r="26" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE25" s="1"/>
+      <c r="AI25" s="1"/>
+    </row>
+    <row r="26" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3813,19 +3844,20 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="X26" s="1"/>
-      <c r="AA26" s="1"/>
+      <c r="Y26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
-      <c r="AH26" s="1"/>
-    </row>
-    <row r="27" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE26" s="1"/>
+      <c r="AI26" s="1"/>
+    </row>
+    <row r="27" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3851,17 +3883,18 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="W27" s="3"/>
       <c r="X27" s="1"/>
-      <c r="AA27" s="1"/>
+      <c r="Y27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
-      <c r="AH27" s="1"/>
-    </row>
-    <row r="28" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE27" s="1"/>
+      <c r="AI27" s="1"/>
+    </row>
+    <row r="28" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3877,7 +3910,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3890,16 +3923,17 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="X28" s="1"/>
-      <c r="AA28" s="1"/>
+      <c r="Y28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
-      <c r="AH28" s="1"/>
-    </row>
-    <row r="29" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE28" s="1"/>
+      <c r="AI28" s="1"/>
+    </row>
+    <row r="29" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3920,7 +3954,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -3929,13 +3963,14 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="1"/>
-      <c r="AA29" s="1"/>
+      <c r="Y29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
-      <c r="AH29" s="1"/>
-    </row>
-    <row r="30" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE29" s="1"/>
+      <c r="AI29" s="1"/>
+    </row>
+    <row r="30" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3959,17 +3994,18 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W30" s="3"/>
       <c r="X30" s="1"/>
-      <c r="AA30" s="1"/>
+      <c r="Y30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
-      <c r="AH30" s="1"/>
-    </row>
-    <row r="31" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE30" s="1"/>
+      <c r="AI30" s="1"/>
+    </row>
+    <row r="31" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3995,13 +4031,14 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="1"/>
-      <c r="AA31" s="1"/>
+      <c r="Y31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
-      <c r="AH31" s="1"/>
-    </row>
-    <row r="32" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE31" s="1"/>
+      <c r="AI31" s="1"/>
+    </row>
+    <row r="32" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -4012,10 +4049,10 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3" t="s">
-        <v>186</v>
-      </c>
+      <c r="J32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
@@ -4027,19 +4064,20 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X32" s="1"/>
-      <c r="AA32" s="1"/>
+      <c r="Y32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
-      <c r="AH32" s="1"/>
-    </row>
-    <row r="33" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE32" s="1"/>
+      <c r="AI32" s="1"/>
+    </row>
+    <row r="33" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4059,23 +4097,24 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W33" s="3"/>
       <c r="X33" s="1"/>
-      <c r="AA33" s="1"/>
+      <c r="Y33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
-      <c r="AH33" s="1"/>
-    </row>
-    <row r="34" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE33" s="1"/>
+      <c r="AI33" s="1"/>
+    </row>
+    <row r="34" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -4084,16 +4123,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3" t="s">
-        <v>195</v>
-      </c>
+      <c r="J34" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4104,20 +4143,21 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="X34" s="1"/>
-      <c r="AA34" s="1"/>
+      <c r="Y34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
-      <c r="AH34" s="1"/>
-    </row>
-    <row r="35" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE34" s="1"/>
+      <c r="AI34" s="1"/>
+    </row>
+    <row r="35" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4140,31 +4180,32 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X35" s="1"/>
-      <c r="AA35" s="1"/>
+      <c r="Y35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
-      <c r="AH35" s="1"/>
-    </row>
-    <row r="36" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE35" s="1"/>
+      <c r="AI35" s="1"/>
+    </row>
+    <row r="36" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4180,20 +4221,21 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X36" s="1"/>
-      <c r="AA36" s="1"/>
+      <c r="Y36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
-      <c r="AH36" s="1"/>
-    </row>
-    <row r="37" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE36" s="1"/>
+      <c r="AI36" s="1"/>
+    </row>
+    <row r="37" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4217,17 +4259,18 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W37" s="3"/>
       <c r="X37" s="1"/>
-      <c r="AA37" s="1"/>
+      <c r="Y37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
-      <c r="AH37" s="1"/>
-    </row>
-    <row r="38" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AE37" s="1"/>
+      <c r="AI37" s="1"/>
+    </row>
+    <row r="38" spans="2:35" ht="132" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4242,7 +4285,7 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
@@ -4255,17 +4298,18 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
-      <c r="AA38" s="1"/>
+      <c r="Y38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
-      <c r="AH38" s="1"/>
-    </row>
-    <row r="39" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE38" s="1"/>
+      <c r="AI38" s="1"/>
+    </row>
+    <row r="39" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4273,17 +4317,17 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="J39" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
@@ -4298,40 +4342,41 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X39" s="1"/>
-      <c r="AA39" s="1"/>
+      <c r="Y39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
-      <c r="AH39" s="1"/>
-    </row>
-    <row r="40" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE39" s="1"/>
+      <c r="AI39" s="1"/>
+    </row>
+    <row r="40" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4342,33 +4387,34 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
-      <c r="AA40" s="1"/>
+      <c r="Y40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
-      <c r="AH40" s="1"/>
-    </row>
-    <row r="41" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE40" s="1"/>
+      <c r="AI40" s="1"/>
+    </row>
+    <row r="41" spans="2:35" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4381,32 +4427,33 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="X41" s="1"/>
-      <c r="AA41" s="1"/>
+      <c r="Y41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
-      <c r="AH41" s="1"/>
-    </row>
-    <row r="42" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE41" s="1"/>
+      <c r="AI41" s="1"/>
+    </row>
+    <row r="42" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4429,24 +4476,25 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X42" s="1"/>
-      <c r="AA42" s="1"/>
+      <c r="Y42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
-      <c r="AH42" s="1"/>
-    </row>
-    <row r="43" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE42" s="1"/>
+      <c r="AI42" s="1"/>
+    </row>
+    <row r="43" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4456,10 +4504,10 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
@@ -4470,25 +4518,26 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X43" s="1"/>
-      <c r="AA43" s="1"/>
+      <c r="Y43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
-      <c r="AH43" s="1"/>
-    </row>
-    <row r="44" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE43" s="1"/>
+      <c r="AI43" s="1"/>
+    </row>
+    <row r="44" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -4498,10 +4547,10 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="3"/>
+      <c r="K44" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
@@ -4513,24 +4562,25 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X44" s="1"/>
-      <c r="AA44" s="1"/>
+      <c r="Y44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
-      <c r="AH44" s="1"/>
-    </row>
-    <row r="45" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE44" s="1"/>
+      <c r="AI44" s="1"/>
+    </row>
+    <row r="45" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4538,133 +4588,135 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="J45" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X45" s="1"/>
-      <c r="AA45" s="1"/>
+      <c r="Y45" s="1"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
-      <c r="AH45" s="1"/>
-    </row>
-    <row r="46" spans="2:34" ht="148.5" x14ac:dyDescent="0.7">
+      <c r="AE45" s="1"/>
+      <c r="AI45" s="1"/>
+    </row>
+    <row r="46" spans="2:35" ht="181.5" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X46" s="1"/>
-      <c r="AA46" s="1"/>
+      <c r="Y46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
-      <c r="AH46" s="1"/>
-    </row>
-    <row r="47" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE46" s="1"/>
+      <c r="AI46" s="1"/>
+    </row>
+    <row r="47" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
         <v>41</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4675,19 +4727,20 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="X47" s="1"/>
-      <c r="AA47" s="1"/>
+      <c r="Y47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
-      <c r="AH47" s="1"/>
-    </row>
-    <row r="48" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE47" s="1"/>
+      <c r="AI47" s="1"/>
+    </row>
+    <row r="48" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4705,7 +4758,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4713,25 +4766,26 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X48" s="1"/>
-      <c r="AA48" s="1"/>
+      <c r="Y48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
-      <c r="AH48" s="1"/>
-    </row>
-    <row r="49" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE48" s="1"/>
+      <c r="AI48" s="1"/>
+    </row>
+    <row r="49" spans="2:35" ht="148.5" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4739,85 +4793,88 @@
         <v>47</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J49" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="1"/>
-      <c r="AA49" s="1"/>
+      <c r="Y49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
-      <c r="AH49" s="1"/>
-    </row>
-    <row r="50" spans="2:34" ht="132" x14ac:dyDescent="0.7">
+      <c r="AE49" s="1"/>
+      <c r="AI49" s="1"/>
+    </row>
+    <row r="50" spans="2:35" ht="132" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4825,23 +4882,24 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="X50" s="1"/>
-      <c r="AA50" s="1"/>
+      <c r="Y50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
-      <c r="AH50" s="1"/>
-    </row>
-    <row r="51" spans="2:34" ht="132" x14ac:dyDescent="0.7">
+      <c r="AE50" s="1"/>
+      <c r="AI50" s="1"/>
+    </row>
+    <row r="51" spans="2:35" ht="165" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4849,66 +4907,67 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="J51" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X51" s="1"/>
-      <c r="AA51" s="1"/>
+      <c r="Y51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-      <c r="AH51" s="1"/>
-    </row>
-    <row r="52" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE51" s="1"/>
+      <c r="AI51" s="1"/>
+    </row>
+    <row r="52" spans="2:35" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>32</v>
@@ -4917,141 +4976,143 @@
         <v>42</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J52" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
-      <c r="AA52" s="1"/>
+      <c r="Y52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
-      <c r="AH52" s="1"/>
-    </row>
-    <row r="53" spans="2:34" ht="165" x14ac:dyDescent="0.7">
+      <c r="AE52" s="1"/>
+      <c r="AI52" s="1"/>
+    </row>
+    <row r="53" spans="2:35" ht="280.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
-      <c r="AA53" s="1"/>
+      <c r="Y53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
-      <c r="AH53" s="1"/>
-    </row>
-    <row r="54" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE53" s="1"/>
+      <c r="AI53" s="1"/>
+    </row>
+    <row r="54" spans="2:35" ht="132" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -5059,43 +5120,44 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
-      <c r="AA54" s="1"/>
+      <c r="Y54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
-      <c r="AH54" s="1"/>
-    </row>
-    <row r="55" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE54" s="1"/>
+      <c r="AI54" s="1"/>
+    </row>
+    <row r="55" spans="2:35" ht="132" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
@@ -5107,17 +5169,18 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
-      <c r="AA55" s="1"/>
+      <c r="Y55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
-      <c r="AH55" s="1"/>
-    </row>
-    <row r="56" spans="2:34" x14ac:dyDescent="0.7">
+      <c r="AE55" s="1"/>
+      <c r="AI55" s="1"/>
+    </row>
+    <row r="56" spans="2:35" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5126,10 +5189,10 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
@@ -5143,10 +5206,13 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="AA56"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
-      <c r="AH56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AI56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5198,7 +5264,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5418,7 +5484,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5469,7 +5535,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5503,7 +5569,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5538,7 +5604,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5553,34 +5619,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5589,10 +5655,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3627A45-05DC-4221-9008-8B346BC702F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D76474-273E-4032-A441-2954EB0C8B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2610" yWindow="397" windowWidth="17183" windowHeight="14633" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -193,13 +193,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>茉莉</t>
-    <rPh sb="0" eb="2">
-      <t>マリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>さくらあや
 HANAKO
 玖麗さやか
@@ -924,32 +917,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>荒幡寧々
-福永莉子
-水嶋さくら
-みあ朝子
-石川はるか
-岩井杏加
-才原茉莉乃
-汐月なぎさ</t>
-    <rPh sb="18" eb="20">
-      <t>アサコ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>イシカワ</t>
-    </rPh>
-    <rPh sb="27" eb="31">
-      <t>イワイキョウカ</t>
-    </rPh>
-    <rPh sb="32" eb="37">
-      <t>サイハラマリノ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>シオツキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>PPP</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -983,13 +950,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>惡斗(休)</t>
-    <rPh sb="3" eb="4">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MIRAI(みちのく)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1121,24 +1081,6 @@
 chou・chou(HCC)</t>
     <rPh sb="9" eb="10">
       <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>青葉ちい
-山下真菜
-研菜々美</t>
-    <rPh sb="0" eb="2">
-      <t>アオバ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヤマシタ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>マナ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>トギナナミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1821,6 +1763,56 @@
   </si>
   <si>
     <t>サファイア・リード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惡斗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>茉莉(休)</t>
+    <rPh sb="0" eb="2">
+      <t>マリ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>荒幡寧々
+水嶋さくら
+みあ朝子
+石川はるか
+岩井杏加
+才原茉莉乃
+汐月なぎさ</t>
+    <rPh sb="13" eb="15">
+      <t>アサコ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イシカワ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>イワイキョウカ</t>
+    </rPh>
+    <rPh sb="27" eb="32">
+      <t>サイハラマリノ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>シオツキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青葉ちい
+研菜々美</t>
+    <rPh sb="0" eb="2">
+      <t>アオバ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>トギナナミ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1906,26 +1898,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2048,6 +2020,26 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2418,20 +2410,20 @@
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="13"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="12"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="11"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="8"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="4"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="12"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="10"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2773,7 +2765,7 @@
     <col min="19" max="19" width="28.375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.3125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.9375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.0625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="50.0625" style="1" customWidth="1"/>
     <col min="24" max="24" width="10.375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11.875" bestFit="1" customWidth="1"/>
@@ -2790,7 +2782,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2816,7 +2808,7 @@
     <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2832,7 +2824,7 @@
      LEN(D5:D1001) - LEN(SUBSTITUTE(D5:D1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(
@@ -3027,34 +3019,34 @@
         <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3063,22 +3055,22 @@
         <v>3</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>9</v>
@@ -3205,7 +3197,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3219,7 +3211,7 @@
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -3361,7 +3353,7 @@
       <c r="AE12" s="1"/>
       <c r="AI12" s="1"/>
     </row>
-    <row r="13" spans="1:35" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="13" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3385,7 +3377,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="1"/>
@@ -3396,7 +3388,7 @@
       <c r="AE13" s="1"/>
       <c r="AI13" s="1"/>
     </row>
-    <row r="14" spans="1:35" ht="33" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3422,7 +3414,7 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>13</v>
@@ -3460,7 +3452,7 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -3507,7 +3499,7 @@
       <c r="AE16" s="1"/>
       <c r="AI16" s="1"/>
     </row>
-    <row r="17" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+    <row r="17" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3531,10 +3523,10 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -3724,7 +3716,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3735,10 +3727,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -3773,7 +3765,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
@@ -3797,7 +3789,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3810,7 +3802,7 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
@@ -3820,7 +3812,7 @@
       <c r="AE25" s="1"/>
       <c r="AI25" s="1"/>
     </row>
-    <row r="26" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+    <row r="26" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3844,10 +3836,10 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
@@ -3857,12 +3849,12 @@
       <c r="AE26" s="1"/>
       <c r="AI26" s="1"/>
     </row>
-    <row r="27" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+    <row r="27" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3883,7 +3875,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W27" s="3"/>
       <c r="X27" s="1"/>
@@ -3900,7 +3892,7 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -3910,7 +3902,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3923,7 +3915,7 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
@@ -3954,7 +3946,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -3970,7 +3962,7 @@
       <c r="AE29" s="1"/>
       <c r="AI29" s="1"/>
     </row>
-    <row r="30" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="30" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3994,7 +3986,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W30" s="3"/>
       <c r="X30" s="1"/>
@@ -4038,7 +4030,7 @@
       <c r="AE31" s="1"/>
       <c r="AI31" s="1"/>
     </row>
-    <row r="32" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+    <row r="32" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -4050,7 +4042,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4064,10 +4056,10 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -4077,7 +4069,7 @@
       <c r="AE32" s="1"/>
       <c r="AI32" s="1"/>
     </row>
-    <row r="33" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+    <row r="33" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4097,13 +4089,13 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W33" s="3"/>
       <c r="X33" s="1"/>
@@ -4123,16 +4115,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4143,11 +4135,11 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
@@ -4180,11 +4172,11 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
@@ -4199,13 +4191,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4221,11 +4213,11 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4235,7 +4227,7 @@
       <c r="AE36" s="1"/>
       <c r="AI36" s="1"/>
     </row>
-    <row r="37" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+    <row r="37" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4259,7 +4251,7 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W37" s="3"/>
       <c r="X37" s="1"/>
@@ -4270,7 +4262,7 @@
       <c r="AE37" s="1"/>
       <c r="AI37" s="1"/>
     </row>
-    <row r="38" spans="2:35" ht="132" x14ac:dyDescent="0.7">
+    <row r="38" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4285,12 +4277,12 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -4298,7 +4290,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
@@ -4317,15 +4309,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4335,14 +4327,14 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
@@ -4357,16 +4349,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4376,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4387,10 +4379,10 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
@@ -4406,15 +4398,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4427,18 +4419,18 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -4448,16 +4440,16 @@
       <c r="AE41" s="1"/>
       <c r="AI41" s="1"/>
     </row>
-    <row r="42" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
+    <row r="42" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -4476,10 +4468,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -4494,18 +4486,18 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4518,11 +4510,11 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4537,10 +4529,10 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4549,7 +4541,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4562,10 +4554,10 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4575,12 +4567,12 @@
       <c r="AE44" s="1"/>
       <c r="AI44" s="1"/>
     </row>
-    <row r="45" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+    <row r="45" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4588,37 +4580,37 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
@@ -4628,54 +4620,54 @@
       <c r="AE45" s="1"/>
       <c r="AI45" s="1"/>
     </row>
-    <row r="46" spans="2:35" ht="181.5" x14ac:dyDescent="0.7">
+    <row r="46" spans="2:35" ht="99" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4690,33 +4682,33 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4727,10 +4719,10 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4740,12 +4732,12 @@
       <c r="AE47" s="1"/>
       <c r="AI47" s="1"/>
     </row>
-    <row r="48" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+    <row r="48" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4758,7 +4750,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4766,16 +4758,16 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -4785,53 +4777,53 @@
       <c r="AE48" s="1"/>
       <c r="AI48" s="1"/>
     </row>
-    <row r="49" spans="2:35" ht="148.5" x14ac:dyDescent="0.7">
+    <row r="49" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="1"/>
@@ -4842,39 +4834,39 @@
       <c r="AE49" s="1"/>
       <c r="AI49" s="1"/>
     </row>
-    <row r="50" spans="2:35" ht="132" x14ac:dyDescent="0.7">
+    <row r="50" spans="2:35" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4882,14 +4874,14 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -4899,60 +4891,60 @@
       <c r="AE50" s="1"/>
       <c r="AI50" s="1"/>
     </row>
-    <row r="51" spans="2:35" ht="165" x14ac:dyDescent="0.7">
+    <row r="51" spans="2:35" ht="99" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>159</v>
+        <v>236</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4967,52 +4959,52 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -5023,55 +5015,55 @@
       <c r="AE52" s="1"/>
       <c r="AI52" s="1"/>
     </row>
-    <row r="53" spans="2:35" ht="280.5" x14ac:dyDescent="0.7">
+    <row r="53" spans="2:35" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -5082,37 +5074,37 @@
       <c r="AE53" s="1"/>
       <c r="AI53" s="1"/>
     </row>
-    <row r="54" spans="2:35" ht="132" x14ac:dyDescent="0.7">
+    <row r="54" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -5120,7 +5112,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -5131,32 +5123,32 @@
       <c r="AE54" s="1"/>
       <c r="AI54" s="1"/>
     </row>
-    <row r="55" spans="2:35" ht="132" x14ac:dyDescent="0.7">
+    <row r="55" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="I55" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5169,7 +5161,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5191,7 +5183,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5264,7 +5256,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5484,7 +5476,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5535,7 +5527,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5569,7 +5561,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5604,7 +5596,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5619,34 +5611,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5655,10 +5647,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D76474-273E-4032-A441-2954EB0C8B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C58F34-C650-42EC-B0E9-FF9E0D7C2A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="397" windowWidth="17183" windowHeight="14633" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="2610" yWindow="405" windowWidth="17183" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C58F34-C650-42EC-B0E9-FF9E0D7C2A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19A570B-57C2-47E6-9D90-09FA538A83D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="405" windowWidth="17183" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="2610" yWindow="405" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="238">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1612,16 +1612,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;ユウカ&gt;(仮)
-清司麗菜(8/1デビュー予定)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>神嵜志音
-さとうもも</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>柊くるみ(PR)(2026.9.21より休予定)
 夏実もち(PR)
 LINDA(信州)</t>
@@ -1633,21 +1623,6 @@
     </rPh>
     <rPh sb="40" eb="42">
       <t>シンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;Y&gt;
-&lt;みく&gt;
-&lt;ちゅら愛花&gt;(8.11デビュー予定)</t>
-    <rPh sb="13" eb="14">
-      <t>アイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1813,6 +1788,25 @@
     <rPh sb="5" eb="9">
       <t>トギナナミ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神嵜志音
+さとうもも 
+清司麗菜</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちゅら愛花</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;Y&gt;
+&lt;みく&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2758,7 +2752,7 @@
     <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.3125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.3125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.8125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="23.375" style="1" bestFit="1" customWidth="1"/>
@@ -4290,7 +4284,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
@@ -4352,7 +4346,7 @@
         <v>119</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
@@ -4486,7 +4480,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4532,7 +4526,7 @@
         <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4689,7 +4683,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>91</v>
@@ -4701,7 +4695,7 @@
         <v>156</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4722,7 +4716,7 @@
         <v>135</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4801,7 +4795,7 @@
         <v>68</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>25</v>
@@ -4842,7 +4836,7 @@
         <v>203</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
@@ -4899,10 +4893,10 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>177</v>
@@ -5083,16 +5077,18 @@
         <v>200</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+      <c r="I54" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="J54" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>187</v>
@@ -5112,7 +5108,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -5132,23 +5128,23 @@
         <v>188</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>208</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5161,7 +5157,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19A570B-57C2-47E6-9D90-09FA538A83D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95858C28-78B9-407D-B5CC-64A919D2DE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2610" yWindow="405" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -513,10 +513,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>IR/ホットシュシュ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AKINO(OZ)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1553,14 +1549,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>郷田明日香(休)
-ブランキー真帆
-Chi Chi
-ZONES
-勇気みなみ(休)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>山下実優
 中島翔子
 上福ゆき(2026.12.26引退)</t>
@@ -1686,10 +1674,6 @@
     <rPh sb="36" eb="38">
       <t>コナミ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;MIHO&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1807,6 +1791,33 @@
   <si>
     <t>&lt;Y&gt;
 &lt;みく&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IR/ホットシュシュ/COR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;MIHO&gt;
+&lt;ヤギヌマメイ&gt;(9.19デビュー予定)</t>
+    <rPh sb="24" eb="26">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>郷田明日香(休)
+ブランキー真帆
+Chi Chi
+ZONES
+南ゆうき
+古川奈苗</t>
+    <rPh sb="31" eb="32">
+      <t>ミナミ</t>
+    </rPh>
+    <rPh sb="36" eb="40">
+      <t>フルカワナナエ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2401,7 +2412,7 @@
     <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="19"/>
     <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="17"/>
-    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ" dataDxfId="16"/>
+    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ/COR" dataDxfId="16"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
     <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
@@ -2776,7 +2787,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2802,7 +2813,7 @@
     <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2842,7 +2853,7 @@
      LEN(G5:G1001) - LEN(SUBSTITUTE(G5:G1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
@@ -2962,7 +2973,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W2" s="1" cm="1">
         <f t="array" ref="W2">SUMPRODUCT(
@@ -3019,7 +3030,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
@@ -3034,13 +3045,13 @@
         <v>7</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3055,13 +3066,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>32</v>
@@ -3371,7 +3382,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="1"/>
@@ -3446,7 +3457,7 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -3517,10 +3528,10 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -3721,10 +3732,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -3759,7 +3770,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
@@ -3783,7 +3794,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3796,7 +3807,7 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
@@ -3830,7 +3841,7 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>29</v>
@@ -3869,7 +3880,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="W27" s="3"/>
       <c r="X27" s="1"/>
@@ -3896,7 +3907,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3909,7 +3920,7 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
@@ -3980,7 +3991,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="W30" s="3"/>
       <c r="X30" s="1"/>
@@ -4036,7 +4047,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4053,7 +4064,7 @@
         <v>54</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -4083,13 +4094,13 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W33" s="3"/>
       <c r="X33" s="1"/>
@@ -4109,16 +4120,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4133,7 +4144,7 @@
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
@@ -4166,11 +4177,11 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
@@ -4185,13 +4196,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4211,7 +4222,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4284,7 +4295,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
@@ -4303,15 +4314,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4328,7 +4339,7 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
@@ -4343,16 +4354,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4362,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4373,10 +4384,10 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
@@ -4392,15 +4403,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4413,18 +4424,18 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -4439,7 +4450,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4462,10 +4473,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -4480,7 +4491,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4504,11 +4515,11 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4523,10 +4534,10 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4548,10 +4559,10 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4566,7 +4577,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4574,37 +4585,37 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
@@ -4619,16 +4630,16 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4638,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>63</v>
@@ -4651,17 +4662,17 @@
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4676,30 +4687,30 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>64</v>
@@ -4713,10 +4724,10 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4744,7 +4755,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4752,16 +4763,16 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -4779,23 +4790,23 @@
         <v>46</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>68</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>25</v>
@@ -4813,11 +4824,11 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="1"/>
@@ -4833,19 +4844,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -4860,7 +4871,7 @@
         <v>65</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4868,14 +4879,14 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -4893,25 +4904,25 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>45</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
@@ -4919,26 +4930,26 @@
         <v>66</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4962,29 +4973,29 @@
         <v>41</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -4993,12 +5004,12 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -5014,50 +5025,50 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -5074,33 +5085,33 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -5108,7 +5119,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -5121,30 +5132,30 @@
     </row>
     <row r="55" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5157,7 +5168,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5179,7 +5190,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5252,7 +5263,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5472,7 +5483,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5523,7 +5534,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5557,7 +5568,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5592,7 +5603,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5607,34 +5618,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5643,10 +5654,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95858C28-78B9-407D-B5CC-64A919D2DE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA1AD9C-4269-4BF7-97AF-80EAEC6DDB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2610" yWindow="405" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1243,11 +1243,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>浦幌ちほ(北都)
-ソイ(EVO)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ビクトリア弓月
 田中きずな(休)
 瀬戸レア</t>
@@ -1285,25 +1280,6 @@
   </si>
   <si>
     <t>水波綾</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>志真うた(伊藤道場)
-CoCo(MyWay)
-大竹仁美(BBJ)
-鰻マスクウーマン(DDT?/別名あり)</t>
-    <rPh sb="0" eb="2">
-      <t>シマ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ドウジョウ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ベツメイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1798,14 +1774,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;MIHO&gt;
-&lt;ヤギヌマメイ&gt;(9.19デビュー予定)</t>
-    <rPh sb="24" eb="26">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>郷田明日香(休)
 ブランキー真帆
 Chi Chi
@@ -1817,6 +1785,56 @@
     </rPh>
     <rPh sb="36" eb="40">
       <t>フルカワナナエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;MIHO&gt;(HCC)
+&lt;森田朋依&gt;(HCC)
+&lt;ヤギヌマメイ&gt;(COR9.19デビュー予定)</t>
+    <rPh sb="13" eb="15">
+      <t>モリタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浦幌ちほ(北都)
+ソイ(EVO)
+藤井瑠美愛(紀州)</t>
+    <rPh sb="23" eb="25">
+      <t>キシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>志真うた(伊藤道場)
+CoCo(MyWay)
+大竹仁美(BBJ)
+鰻マスクウーマン(DDT?/別名あり)
+真田十勇士桜(紀州)</t>
+    <rPh sb="0" eb="2">
+      <t>シマ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イトウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ドウジョウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ベツメイ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>キシュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2813,7 +2831,7 @@
     <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2853,7 +2871,7 @@
      LEN(G5:G1001) - LEN(SUBSTITUTE(G5:G1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" cm="1">
         <f t="array" ref="H2">SUMPRODUCT(
@@ -2965,7 +2983,7 @@
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="V2" s="1" cm="1">
         <f t="array" ref="V2">SUMPRODUCT(
@@ -3030,7 +3048,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
@@ -3735,7 +3753,7 @@
         <v>145</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -4047,7 +4065,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4064,7 +4082,7 @@
         <v>54</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -4120,12 +4138,12 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
@@ -4202,7 +4220,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4222,7 +4240,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4295,7 +4313,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
@@ -4357,7 +4375,7 @@
         <v>118</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
@@ -4403,15 +4421,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4424,7 +4442,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4473,7 +4491,7 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>161</v>
@@ -4491,7 +4509,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4519,7 +4537,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4537,7 +4555,7 @@
         <v>159</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4562,7 +4580,7 @@
         <v>107</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4605,7 +4623,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4630,7 +4648,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>133</v>
@@ -4639,7 +4657,7 @@
         <v>125</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4669,10 +4687,10 @@
         <v>87</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4694,7 +4712,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>90</v>
@@ -4706,7 +4724,7 @@
         <v>155</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4727,7 +4745,7 @@
         <v>134</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4769,7 +4787,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>164</v>
@@ -4790,7 +4808,7 @@
         <v>46</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>171</v>
@@ -4806,7 +4824,7 @@
         <v>68</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>25</v>
@@ -4844,10 +4862,10 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
@@ -4856,7 +4874,7 @@
         <v>127</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -4904,13 +4922,13 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>154</v>
@@ -4942,14 +4960,14 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>181</v>
+        <v>237</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4976,10 +4994,10 @@
         <v>117</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>69</v>
@@ -5009,7 +5027,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -5028,19 +5046,19 @@
         <v>158</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>141</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>89</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>169</v>
@@ -5053,10 +5071,10 @@
         <v>151</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5068,7 +5086,7 @@
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -5085,10 +5103,10 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>167</v>
@@ -5096,13 +5114,13 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>166</v>
@@ -5119,7 +5137,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -5130,32 +5148,32 @@
       <c r="AE54" s="1"/>
       <c r="AI54" s="1"/>
     </row>
-    <row r="55" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="55" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5168,7 +5186,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5634,7 +5652,7 @@
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA1AD9C-4269-4BF7-97AF-80EAEC6DDB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BB742C-0BF2-46BE-8684-86F066CF326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="405" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -495,10 +495,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>瀬戸ノノカ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>HisokA</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1671,17 +1667,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;七世真理子&gt;(Rose)(2026.10.17デビュー予定)
-&lt;星野 さやか&gt;(九州女子プロレス)</t>
-    <rPh sb="28" eb="30">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="41" eb="45">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>堀このみ(Rose)(休)
 彩桜(アップタウン)
 結菜(伊藤道場)(休)
@@ -1835,6 +1820,28 @@
     </rPh>
     <rPh sb="60" eb="62">
       <t>キシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>瀬戸ノノカ(休)(9/20引退)</t>
+    <rPh sb="6" eb="7">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>インタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;七世真理子&gt;(Rose)(2026.10.17デビュー予定)
+&lt;星野 さやか&gt;(九州女子プロレス)
+&lt;AYANO&gt;(九州女子プロレス)</t>
+    <rPh sb="28" eb="30">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>キュウシュウジョシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2805,7 +2812,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2831,7 +2838,7 @@
     <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2983,7 +2990,7 @@
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V2" s="1" cm="1">
         <f t="array" ref="V2">SUMPRODUCT(
@@ -3048,7 +3055,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
@@ -3063,13 +3070,13 @@
         <v>7</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3084,13 +3091,13 @@
         <v>6</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>32</v>
@@ -3400,7 +3407,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="1"/>
@@ -3475,7 +3482,7 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -3546,10 +3553,10 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -3750,10 +3757,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -3788,7 +3795,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
@@ -3812,7 +3819,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3825,7 +3832,7 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
@@ -3859,7 +3866,7 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>29</v>
@@ -3898,7 +3905,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W27" s="3"/>
       <c r="X27" s="1"/>
@@ -3925,7 +3932,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3938,7 +3945,7 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
@@ -4009,7 +4016,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W30" s="3"/>
       <c r="X30" s="1"/>
@@ -4065,7 +4072,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4082,7 +4089,7 @@
         <v>54</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -4112,13 +4119,13 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W33" s="3"/>
       <c r="X33" s="1"/>
@@ -4138,16 +4145,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4162,7 +4169,7 @@
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
@@ -4195,11 +4202,11 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
@@ -4214,13 +4221,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4240,7 +4247,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4313,7 +4320,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
@@ -4332,15 +4339,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4357,7 +4364,7 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
@@ -4372,16 +4379,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4391,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4402,10 +4409,10 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="1"/>
@@ -4421,15 +4428,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4442,18 +4449,18 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -4468,7 +4475,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4491,10 +4498,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -4509,7 +4516,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4533,11 +4540,11 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -4552,10 +4559,10 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4577,10 +4584,10 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -4595,7 +4602,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4603,37 +4610,37 @@
         <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
@@ -4648,16 +4655,16 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4667,7 +4674,7 @@
         <v>26</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>63</v>
@@ -4680,17 +4687,17 @@
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4705,30 +4712,30 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>64</v>
@@ -4742,10 +4749,10 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4773,7 +4780,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4781,16 +4788,16 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -4808,23 +4815,23 @@
         <v>46</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>25</v>
@@ -4842,11 +4849,11 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="1"/>
@@ -4862,25 +4869,25 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -4889,7 +4896,7 @@
         <v>65</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4897,14 +4904,14 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -4922,52 +4929,52 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>45</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -4991,29 +4998,29 @@
         <v>41</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -5022,12 +5029,12 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -5043,50 +5050,50 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="1"/>
@@ -5103,33 +5110,33 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -5137,7 +5144,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -5150,30 +5157,30 @@
     </row>
     <row r="55" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5186,7 +5193,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>
@@ -5208,7 +5215,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5281,7 +5288,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5501,7 +5508,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5552,7 +5559,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5586,7 +5593,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5621,7 +5628,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5636,34 +5643,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5672,10 +5679,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BB742C-0BF2-46BE-8684-86F066CF326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956020FA-76F8-469A-B227-94400DD702DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="237">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1399,13 +1399,6 @@
     </rPh>
     <rPh sb="44" eb="46">
       <t>シンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リアラ(休)</t>
-    <rPh sb="4" eb="5">
-      <t>キュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2838,7 +2831,7 @@
     <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2974,7 +2967,7 @@
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" s="1" cm="1">
         <f t="array" ref="T2">SUMPRODUCT(
@@ -3055,7 +3048,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
@@ -4145,7 +4138,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -4227,7 +4220,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4247,7 +4240,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -4320,7 +4313,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="1"/>
@@ -4382,7 +4375,7 @@
         <v>117</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
@@ -4432,11 +4425,11 @@
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4516,7 +4509,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4562,7 +4555,7 @@
         <v>158</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4655,7 +4648,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>132</v>
@@ -4697,7 +4690,7 @@
         <v>193</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -4719,7 +4712,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>89</v>
@@ -4731,7 +4724,7 @@
         <v>154</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4752,7 +4745,7 @@
         <v>133</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -4815,7 +4808,7 @@
         <v>46</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>170</v>
@@ -4831,7 +4824,7 @@
         <v>67</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>25</v>
@@ -4869,10 +4862,10 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
@@ -4881,7 +4874,7 @@
         <v>126</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -4929,10 +4922,10 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>174</v>
@@ -4952,7 +4945,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>101</v>
@@ -4966,15 +4959,13 @@
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
-      <c r="T51" s="3" t="s">
-        <v>194</v>
-      </c>
+      <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -5001,10 +4992,10 @@
         <v>116</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>68</v>
@@ -5034,7 +5025,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="1"/>
@@ -5053,19 +5044,19 @@
         <v>157</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>140</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>88</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>168</v>
@@ -5110,10 +5101,10 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>166</v>
@@ -5121,10 +5112,10 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>183</v>
@@ -5144,7 +5135,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="1"/>
@@ -5164,23 +5155,23 @@
         <v>184</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5193,7 +5184,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{956020FA-76F8-469A-B227-94400DD702DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D3BD8F-2E6E-49C5-B922-EAC1CD36F4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="233">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -909,32 +909,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>PPP</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鶴姫花（愛媛）
-緑野アミサ(アルマリブレ)
-豊田紗也夏(T-HEARTS)
-みゆ(BRS)</t>
-    <rPh sb="4" eb="6">
-      <t>エヒメ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>叶ミク(T-HEARTS)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ちゃんよた</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エチカミヤビ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>入江彩乃</t>
     <rPh sb="0" eb="4">
       <t>イリエアヤノ</t>
@@ -1062,10 +1036,6 @@
     <rPh sb="14" eb="16">
       <t>マイカ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>虎牙のん</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1341,22 +1311,6 @@
 真白優希(Rose)(休)</t>
     <rPh sb="24" eb="25">
       <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>苺畑ひより(666)
-横井真菜(REINA)
-タギリヒメ真夢(九州女子プロレス)
-彩月悠叶(Evolution, 2AW)
-さいとう(アップタウン)
-小久保アリサ(BBJ)
-CHIKA(EVO)</t>
-    <rPh sb="31" eb="33">
-      <t>キュウシュウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1729,10 +1683,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;ユウカ&gt;(仮)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>神嵜志音
 さとうもも 
 清司麗菜</t>
@@ -1767,24 +1717,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;MIHO&gt;(HCC)
-&lt;森田朋依&gt;(HCC)
-&lt;ヤギヌマメイ&gt;(COR9.19デビュー予定)</t>
-    <rPh sb="13" eb="15">
-      <t>モリタ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>トモ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>浦幌ちほ(北都)
 ソイ(EVO)
 藤井瑠美愛(紀州)</t>
@@ -1827,9 +1759,73 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>&lt;MIHO&gt;(HCC)(9/19デビュー予定)
+&lt;森田朋依&gt;(HCC)
+&lt;ヤギヌマメイ&gt;(COR9.19デビュー予定)</t>
+    <rPh sb="20" eb="22">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>モリタ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)
+&lt;咲森チエリ&gt;(10.3デビュー予定)</t>
+    <rPh sb="25" eb="27">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苺畑ひより(666)
+横井真菜(REINA)
+タギリヒメ真夢(九州女子プロレス)
+彩月悠叶(Evolution, 2AW)
+さいとう(アップタウン)
+小久保アリサ(BBJ)
+CHIKA(EVO)
+虎牙のん(PPP)</t>
+    <rPh sb="31" eb="33">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>叶ミク(T-HEARTS)
+エチカミヤビ(PPP)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鶴姫花（愛媛）
+緑野アミサ(アルマリブレ)
+豊田紗也夏(T-HEARTS)
+みゆ(BRS)
+ちゃんよた(PPP)</t>
+    <rPh sb="4" eb="6">
+      <t>エヒメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>&lt;七世真理子&gt;(Rose)(2026.10.17デビュー予定)
 &lt;星野 さやか&gt;(九州女子プロレス)
-&lt;AYANO&gt;(九州女子プロレス)</t>
+&lt;AYANO&gt;(九州女子プロレス)
+&lt;KAORI&gt;(九州女子プロレス)
+&lt;KARIN&gt;(九州女子プロレス)</t>
     <rPh sb="28" eb="30">
       <t>ヨテイ</t>
     </rPh>
@@ -1920,7 +1916,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="23">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1941,26 +1937,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2422,28 +2398,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:W56" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
-  <autoFilter ref="B4:W56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="20"/>
-    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="19"/>
-    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="17"/>
-    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ/COR" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="12"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="10"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{F6B1BCBE-A702-4B7C-9B81-2600AE026FEA}" name="PPP" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:V56" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="B4:V56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="16"/>
+    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ/COR" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="14"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="11"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="10"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="9"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="3"/>
     <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
     <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
     <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
@@ -2769,7 +2744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AH56"/>
   <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
@@ -2786,24 +2761,23 @@
     <col min="17" max="17" width="13.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="23.375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.3125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.0625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="50.0625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="21.3125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="30.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="27.3125" style="1"/>
-    <col min="36" max="16384" width="27.3125" style="1"/>
+    <col min="20" max="20" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="41.0625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="50.0625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="30.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="27.3125" style="1"/>
+    <col min="35" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
@@ -2819,19 +2793,18 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
+      <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AI1" s="1"/>
-    </row>
-    <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH1" s="1"/>
+    </row>
+    <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
-        <f>SUM(C2:RW2)</f>
-        <v>364</v>
+        <f>SUM(C2:RV2)</f>
+        <v>376</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2855,7 +2828,7 @@
      LEN(E5:E1001) - LEN(SUBSTITUTE(E5:E1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" cm="1">
         <f t="array" ref="F2">SUMPRODUCT(
@@ -2923,93 +2896,85 @@
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
+  IF(LEN(N5:N1001)=0, 0,
+     LEN(N5:N1001) - LEN(SUBSTITUTE(N5:N1001, CHAR(10), "")) + 1
+  )
+)</f>
+        <v>9</v>
+      </c>
+      <c r="O2" s="1" cm="1">
+        <f t="array" ref="O2">SUMPRODUCT(
   IF(LEN(O5:O1001)=0, 0,
      LEN(O5:O1001) - LEN(SUBSTITUTE(O5:O1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="O2" s="1" cm="1">
-        <f t="array" ref="O2">SUMPRODUCT(
+      <c r="P2" s="1" cm="1">
+        <f t="array" ref="P2">SUMPRODUCT(
   IF(LEN(P5:P1001)=0, 0,
      LEN(P5:P1001) - LEN(SUBSTITUTE(P5:P1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>6</v>
       </c>
-      <c r="P2" s="1" cm="1">
-        <f t="array" ref="P2">SUMPRODUCT(
+      <c r="Q2" s="1" cm="1">
+        <f t="array" ref="Q2">SUMPRODUCT(
   IF(LEN(Q5:Q1001)=0, 0,
      LEN(Q5:Q1001) - LEN(SUBSTITUTE(Q5:Q1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="Q2" s="1" cm="1">
-        <f t="array" ref="Q2">SUMPRODUCT(
+      <c r="R2" s="1" cm="1">
+        <f t="array" ref="R2">SUMPRODUCT(
   IF(LEN(R5:R1001)=0, 0,
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="R2" s="1" cm="1">
-        <f t="array" ref="R2">SUMPRODUCT(
+      <c r="S2" s="1" cm="1">
+        <f t="array" ref="S2">SUMPRODUCT(
   IF(LEN(S5:S1001)=0, 0,
      LEN(S5:S1001) - LEN(SUBSTITUTE(S5:S1001, CHAR(10), "")) + 1
   )
 )</f>
         <v>4</v>
       </c>
-      <c r="S2" s="1" cm="1">
-        <f t="array" ref="S2">SUMPRODUCT(
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2">SUMPRODUCT(
   IF(LEN(T5:T1001)=0, 0,
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>3</v>
-      </c>
-      <c r="T2" s="1" cm="1">
-        <f t="array" ref="T2">SUMPRODUCT(
+        <v>8</v>
+      </c>
+      <c r="U2" s="1" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT(
   IF(LEN(U5:U1001)=0, 0,
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>8</v>
-      </c>
-      <c r="U2" s="1" cm="1">
-        <f t="array" ref="U2">SUMPRODUCT(
+        <v>62</v>
+      </c>
+      <c r="V2" s="1" cm="1">
+        <f t="array" ref="V2">SUMPRODUCT(
   IF(LEN(V5:V1001)=0, 0,
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>57</v>
-      </c>
-      <c r="V2" s="1" cm="1">
-        <f t="array" ref="V2">SUMPRODUCT(
-  IF(LEN(W5:W1001)=0, 0,
-     LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
-  )
-)</f>
         <v>51</v>
       </c>
-      <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2">SUMPRODUCT(
-  IF(LEN(X5:X1001)=0, 0,
-     LEN(X5:X1001) - LEN(SUBSTITUTE(X5:X1001, CHAR(10), "")) + 1
-  )
-)</f>
-        <v>0</v>
-      </c>
+      <c r="W2" s="1"/>
       <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
+      <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AI2" s="1"/>
-    </row>
-    <row r="3" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH2" s="1"/>
+    </row>
+    <row r="3" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -3022,16 +2987,15 @@
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
+      <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AI3" s="1"/>
-    </row>
-    <row r="4" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH3" s="1"/>
+    </row>
+    <row r="4" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
@@ -3048,7 +3012,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>15</v>
@@ -3069,7 +3033,7 @@
         <v>51</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>17</v>
@@ -3087,26 +3051,23 @@
         <v>108</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W4" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
+      <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AI4" s="1"/>
-    </row>
-    <row r="5" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH4" s="1"/>
+    </row>
+    <row r="5" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3132,16 +3093,15 @@
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
+      <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
+      <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AI5" s="1"/>
-    </row>
-    <row r="6" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH5" s="1"/>
+    </row>
+    <row r="6" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3165,16 +3125,15 @@
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
+      <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AI6" s="1"/>
-    </row>
-    <row r="7" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH6" s="1"/>
+    </row>
+    <row r="7" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3198,16 +3157,15 @@
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
+      <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
+      <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AI7" s="1"/>
-    </row>
-    <row r="8" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH7" s="1"/>
+    </row>
+    <row r="8" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3232,19 +3190,18 @@
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3" t="s">
+      <c r="V8" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
+      <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AI8" s="1"/>
-    </row>
-    <row r="9" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH8" s="1"/>
+    </row>
+    <row r="9" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3268,16 +3225,15 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
+      <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
+      <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AI9" s="1"/>
-    </row>
-    <row r="10" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH9" s="1"/>
+    </row>
+    <row r="10" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3301,16 +3257,15 @@
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
+      <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
+      <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AI10" s="1"/>
-    </row>
-    <row r="11" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH10" s="1"/>
+    </row>
+    <row r="11" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3334,16 +3289,15 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
+      <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AI11" s="1"/>
-    </row>
-    <row r="12" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH11" s="1"/>
+    </row>
+    <row r="12" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3367,16 +3321,15 @@
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
+      <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AI12" s="1"/>
-    </row>
-    <row r="13" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH12" s="1"/>
+    </row>
+    <row r="13" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3398,20 +3351,19 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3" t="s">
+      <c r="U13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="W13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
+      <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AI13" s="1"/>
-    </row>
-    <row r="14" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH13" s="1"/>
+    </row>
+    <row r="14" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3435,22 +3387,21 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
+      <c r="U14" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="V14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="W14" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
+      <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AI14" s="1"/>
-    </row>
-    <row r="15" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH14" s="1"/>
+    </row>
+    <row r="15" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3473,19 +3424,18 @@
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3" t="s">
+      <c r="V15" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
+      <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AI15" s="1"/>
-    </row>
-    <row r="16" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH15" s="1"/>
+    </row>
+    <row r="16" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3513,16 +3463,15 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
+      <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
+      <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AI16" s="1"/>
-    </row>
-    <row r="17" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH16" s="1"/>
+    </row>
+    <row r="17" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3544,22 +3493,21 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
+      <c r="U17" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="V17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="W17" s="3" t="s">
         <v>113</v>
       </c>
+      <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
+      <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AI17" s="1"/>
-    </row>
-    <row r="18" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH17" s="1"/>
+    </row>
+    <row r="18" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3583,16 +3531,15 @@
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
+      <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AI18" s="1"/>
-    </row>
-    <row r="19" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH18" s="1"/>
+    </row>
+    <row r="19" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3616,16 +3563,15 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
+      <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
+      <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AI19" s="1"/>
-    </row>
-    <row r="20" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH19" s="1"/>
+    </row>
+    <row r="20" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3649,16 +3595,15 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
+      <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
+      <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AI20" s="1"/>
-    </row>
-    <row r="21" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH20" s="1"/>
+    </row>
+    <row r="21" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3682,16 +3627,15 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
+      <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
+      <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AI21" s="1"/>
-    </row>
-    <row r="22" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH21" s="1"/>
+    </row>
+    <row r="22" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3715,16 +3659,15 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
+      <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
+      <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AI22" s="1"/>
-    </row>
-    <row r="23" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH22" s="1"/>
+    </row>
+    <row r="23" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3748,22 +3691,21 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
+      <c r="U23" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="V23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>181</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
+      <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AI23" s="1"/>
-    </row>
-    <row r="24" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH23" s="1"/>
+    </row>
+    <row r="24" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3786,19 +3728,18 @@
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3" t="s">
-        <v>143</v>
-      </c>
+      <c r="V24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
+      <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AI24" s="1"/>
-    </row>
-    <row r="25" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH24" s="1"/>
+    </row>
+    <row r="25" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3823,19 +3764,18 @@
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3" t="s">
+      <c r="V25" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
+      <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AI25" s="1"/>
-    </row>
-    <row r="26" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH25" s="1"/>
+    </row>
+    <row r="26" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3857,22 +3797,21 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
+      <c r="U26" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="V26" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="W26" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
+      <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AI26" s="1"/>
-    </row>
-    <row r="27" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH26" s="1"/>
+    </row>
+    <row r="27" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3896,20 +3835,19 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3" t="s">
+      <c r="U27" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="W27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
+      <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
-      <c r="AI27" s="1"/>
-    </row>
-    <row r="28" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH27" s="1"/>
+    </row>
+    <row r="28" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3936,19 +3874,18 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3" t="s">
+      <c r="V28" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
+      <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AI28" s="1"/>
-    </row>
-    <row r="29" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH28" s="1"/>
+    </row>
+    <row r="29" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3976,16 +3913,15 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
+      <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
+      <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
-      <c r="AI29" s="1"/>
-    </row>
-    <row r="30" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH29" s="1"/>
+    </row>
+    <row r="30" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -4007,20 +3943,19 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3" t="s">
+      <c r="U30" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="W30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
+      <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AI30" s="1"/>
-    </row>
-    <row r="31" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH30" s="1"/>
+    </row>
+    <row r="31" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -4044,16 +3979,15 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
+      <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
+      <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
-      <c r="AI31" s="1"/>
-    </row>
-    <row r="32" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH31" s="1"/>
+    </row>
+    <row r="32" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -4065,7 +3999,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4077,22 +4011,21 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
+      <c r="U32" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="V32" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>177</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
+      <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
-      <c r="AI32" s="1"/>
-    </row>
-    <row r="33" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH32" s="1"/>
+    </row>
+    <row r="33" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4116,20 +4049,19 @@
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3" t="s">
+      <c r="U33" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="W33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
+      <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
-      <c r="AE33" s="1"/>
-      <c r="AI33" s="1"/>
-    </row>
-    <row r="34" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH33" s="1"/>
+    </row>
+    <row r="34" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -4138,12 +4070,12 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
@@ -4156,23 +4088,22 @@
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3" t="s">
+      <c r="T34" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3" t="s">
+      <c r="U34" s="3"/>
+      <c r="V34" s="3" t="s">
         <v>95</v>
       </c>
+      <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
+      <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
-      <c r="AI34" s="1"/>
-    </row>
-    <row r="35" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH34" s="1"/>
+    </row>
+    <row r="35" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4193,34 +4124,33 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3" t="s">
+      <c r="T35" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3" t="s">
+      <c r="U35" s="3"/>
+      <c r="V35" s="3" t="s">
         <v>120</v>
       </c>
+      <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
+      <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
-      <c r="AI35" s="1"/>
-    </row>
-    <row r="36" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH35" s="1"/>
+    </row>
+    <row r="36" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4234,23 +4164,22 @@
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3" t="s">
+      <c r="T36" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3" t="s">
-        <v>204</v>
-      </c>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
+      <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
-      <c r="AI36" s="1"/>
-    </row>
-    <row r="37" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AH36" s="1"/>
+    </row>
+    <row r="37" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4272,20 +4201,19 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3" t="s">
+      <c r="U37" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="W37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="1"/>
       <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
+      <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
-      <c r="AI37" s="1"/>
-    </row>
-    <row r="38" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH37" s="1"/>
+    </row>
+    <row r="38" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4311,20 +4239,19 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="W38" s="3"/>
+      <c r="U38" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="V38" s="3"/>
+      <c r="W38" s="1"/>
       <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
+      <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
-      <c r="AI38" s="1"/>
-    </row>
-    <row r="39" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH38" s="1"/>
+    </row>
+    <row r="39" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4355,19 +4282,18 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3" t="s">
+      <c r="V39" s="3" t="s">
         <v>122</v>
       </c>
+      <c r="W39" s="1"/>
       <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
+      <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
-      <c r="AI39" s="1"/>
-    </row>
-    <row r="40" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH39" s="1"/>
+    </row>
+    <row r="40" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
@@ -4375,7 +4301,7 @@
         <v>117</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>38</v>
@@ -4400,36 +4326,35 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
+      <c r="T40" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="U40" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="V40" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="W40" s="3"/>
+        <v>153</v>
+      </c>
+      <c r="V40" s="3"/>
+      <c r="W40" s="1"/>
       <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
+      <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
-      <c r="AI40" s="1"/>
-    </row>
-    <row r="41" spans="2:35" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH40" s="1"/>
+    </row>
+    <row r="41" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4442,33 +4367,32 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
+      <c r="T41" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="U41" s="3" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>169</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="W41" s="1"/>
       <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
+      <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
-      <c r="AE41" s="1"/>
-      <c r="AI41" s="1"/>
-    </row>
-    <row r="42" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH41" s="1"/>
+    </row>
+    <row r="42" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4489,27 +4413,26 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
+      <c r="U42" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="V42" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="W42" s="1"/>
       <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
+      <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
-      <c r="AI42" s="1"/>
-    </row>
-    <row r="43" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH42" s="1"/>
+    </row>
+    <row r="43" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4531,31 +4454,30 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3" t="s">
+      <c r="T43" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3" t="s">
-        <v>179</v>
-      </c>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
+      <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
-      <c r="AI43" s="1"/>
-    </row>
-    <row r="44" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH43" s="1"/>
+    </row>
+    <row r="44" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4575,27 +4497,26 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
+      <c r="U44" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="V44" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>185</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="W44" s="1"/>
       <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
+      <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
-      <c r="AI44" s="1"/>
-    </row>
-    <row r="45" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AH44" s="1"/>
+    </row>
+    <row r="45" spans="2:34" ht="33" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4617,47 +4538,46 @@
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="T45" s="3"/>
+        <v>184</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="U45" s="3" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="W45" s="3" t="s">
         <v>104</v>
       </c>
+      <c r="W45" s="1"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
+      <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
-      <c r="AI45" s="1"/>
-    </row>
-    <row r="46" spans="2:35" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH45" s="1"/>
+    </row>
+    <row r="46" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>124</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4667,7 +4587,7 @@
         <v>26</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>63</v>
@@ -4682,37 +4602,36 @@
       <c r="S46" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="T46" s="3"/>
+      <c r="T46" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="U46" s="3" t="s">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>206</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="W46" s="1"/>
       <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
+      <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
-      <c r="AI46" s="1"/>
-    </row>
-    <row r="47" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AH46" s="1"/>
+    </row>
+    <row r="47" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>89</v>
@@ -4721,10 +4640,10 @@
         <v>21</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4740,22 +4659,21 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
+      <c r="U47" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="V47" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="W47" s="1"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
+      <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
-      <c r="AI47" s="1"/>
-    </row>
-    <row r="48" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AH47" s="1"/>
+    </row>
+    <row r="48" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4785,22 +4703,21 @@
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
+      <c r="U48" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="V48" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>163</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="W48" s="1"/>
       <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
+      <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
-      <c r="AI48" s="1"/>
-    </row>
-    <row r="49" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH48" s="1"/>
+    </row>
+    <row r="49" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4808,23 +4725,23 @@
         <v>46</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>67</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>25</v>
@@ -4841,31 +4758,28 @@
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
-      <c r="T49" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="W49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="V49" s="3"/>
+      <c r="W49" s="1"/>
       <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
+      <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
-      <c r="AI49" s="1"/>
-    </row>
-    <row r="50" spans="2:35" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AH49" s="1"/>
+    </row>
+    <row r="50" spans="2:34" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>36</v>
@@ -4874,7 +4788,7 @@
         <v>126</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -4889,32 +4803,29 @@
         <v>65</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
-      <c r="T50" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="U50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="V50" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="W50" s="3" t="s">
-        <v>148</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="W50" s="1"/>
       <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
+      <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
-      <c r="AI50" s="1"/>
-    </row>
-    <row r="51" spans="2:35" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH50" s="1"/>
+    </row>
+    <row r="51" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4922,16 +4833,16 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>100</v>
@@ -4945,7 +4856,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>101</v>
@@ -4960,22 +4871,21 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
+      <c r="U51" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="V51" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="W51" s="3" t="s">
-        <v>231</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="W51" s="1"/>
       <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
+      <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
-      <c r="AI51" s="1"/>
-    </row>
-    <row r="52" spans="2:35" ht="99" x14ac:dyDescent="0.7">
+      <c r="AH51" s="1"/>
+    </row>
+    <row r="52" spans="2:34" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4992,10 +4902,10 @@
         <v>116</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>68</v>
@@ -5008,10 +4918,10 @@
         <v>98</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -5023,155 +4933,150 @@
         <v>111</v>
       </c>
       <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="W52" s="3"/>
+      <c r="U52" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="V52" s="3"/>
+      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
+      <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
-      <c r="AI52" s="1"/>
-    </row>
-    <row r="53" spans="2:35" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AH52" s="1"/>
+    </row>
+    <row r="53" spans="2:34" ht="132" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>88</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="T53" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="W53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="V53" s="3"/>
+      <c r="W53" s="1"/>
       <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
+      <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
-      <c r="AE53" s="1"/>
-      <c r="AI53" s="1"/>
-    </row>
-    <row r="54" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH53" s="1"/>
+    </row>
+    <row r="54" spans="2:34" ht="66" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="W54" s="3"/>
+      <c r="U54" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="V54" s="3"/>
+      <c r="W54" s="1"/>
       <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
+      <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
-      <c r="AI54" s="1"/>
-    </row>
-    <row r="55" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AH54" s="1"/>
+    </row>
+    <row r="55" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5182,20 +5087,19 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="W55" s="3"/>
+      <c r="U55" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="V55" s="3"/>
+      <c r="W55" s="1"/>
       <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
+      <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
-      <c r="AE55" s="1"/>
-      <c r="AI55" s="1"/>
-    </row>
-    <row r="56" spans="2:35" x14ac:dyDescent="0.7">
+      <c r="AH55" s="1"/>
+    </row>
+    <row r="56" spans="2:34" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5219,15 +5123,14 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
+      <c r="W56" s="1"/>
       <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
-      <c r="AA56"/>
+      <c r="Z56"/>
+      <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
-      <c r="AI56" s="1"/>
+      <c r="AH56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -5279,7 +5182,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
@@ -5499,7 +5402,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5550,7 +5453,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5619,7 +5522,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5639,29 +5542,29 @@
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5670,10 +5573,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D3BD8F-2E6E-49C5-B922-EAC1CD36F4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D600D15-F1D3-4334-890A-3EFA6EB579EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="234">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1759,27 +1759,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;MIHO&gt;(HCC)(9/19デビュー予定)
-&lt;森田朋依&gt;(HCC)
-&lt;ヤギヌマメイ&gt;(COR9.19デビュー予定)</t>
-    <rPh sb="20" eb="22">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>モリタ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>トモ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;ユウカ&gt;(仮)
 &lt;咲森チエリ&gt;(10.3デビュー予定)</t>
     <rPh sb="25" eb="27">
@@ -1831,6 +1810,30 @@
     </rPh>
     <rPh sb="41" eb="45">
       <t>キュウシュウジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;森田朋依&gt;(HCC)</t>
+    <rPh sb="1" eb="3">
+      <t>モリタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MIHO(HCC)
+ヤギヌマメイ(所属不明・いったんOCR)</t>
+    <rPh sb="17" eb="19">
+      <t>ショゾク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>フメイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4760,7 +4763,7 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="1"/>
@@ -4812,7 +4815,7 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V50" s="3" t="s">
         <v>143</v>
@@ -4990,7 +4993,7 @@
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="1"/>
@@ -5015,7 +5018,9 @@
       <c r="F54" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G54" s="3"/>
+      <c r="G54" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
         <v>220</v>
@@ -5060,13 +5065,13 @@
         <v>178</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>205</v>
@@ -5088,7 +5093,7 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D600D15-F1D3-4334-890A-3EFA6EB579EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4758A994-32BB-437F-9332-BBFB1847D887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -72,10 +72,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>シード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AWG</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -190,13 +186,6 @@
     <rPh sb="0" eb="3">
       <t>ウメサキハルカ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>さくらあや
-HANAKO
-玖麗さやか
-八神蘭奈</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1023,22 +1012,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>飯田沙耶
-上谷沙弥
-向後桃
-舞華</t>
-    <rPh sb="10" eb="12">
-      <t>コウゴ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>モモ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>マイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ゆづき(HCC)(休)
 chou・chou(HCC)</t>
     <rPh sb="9" eb="10">
@@ -1061,15 +1034,6 @@
     <t>髙橋光咲
 伊田惟吹
 当麻煌</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鉄アキラ
-姫ゆりあ
-金屋あんね
-儛島エマ
-古沢稀杏
-フワちゃん</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1315,14 +1279,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>風南ユキ(休)
-望天セレネ</t>
-    <rPh sb="5" eb="6">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>沙恵(休)</t>
     <rPh sb="3" eb="4">
       <t>キュウ</t>
@@ -1442,20 +1398,6 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ミヤコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>星ハム子(IR)(休)
-藤本つかさ(休8.15復帰)</t>
-    <rPh sb="0" eb="1">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>フッキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1827,14 +1769,60 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>さくらあや
+HANAKO
+玖麗さやか(休)
+八神蘭奈</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鉄アキラ
+姫ゆりあ(休)
+金屋あんね
+儛島エマ
+古沢稀杏
+フワちゃん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飯田沙耶
+上谷沙弥
+向後桃(休)
+舞華</t>
+    <rPh sb="10" eb="12">
+      <t>コウゴ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>モモ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>マイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>星ハム子(IR)(休)
+藤本つかさ</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>MIHO(HCC)
-ヤギヌマメイ(所属不明・いったんOCR)</t>
-    <rPh sb="17" eb="19">
-      <t>ショゾク</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>フメイ</t>
-    </rPh>
+ヤギヌマメイ/ふゆぽい(SUGAMO)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風南ユキ
+望天セレネ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SEAdLINNNG</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2418,7 +2406,7 @@
     <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="9"/>
     <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="8"/>
     <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="シード" dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="SEAdLINNNG" dataDxfId="6"/>
     <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="3"/>
@@ -2752,7 +2740,7 @@
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.8125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.3125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
@@ -2760,7 +2748,7 @@
     <col min="8" max="8" width="27.3125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.3125" style="1" customWidth="1"/>
     <col min="11" max="11" width="37.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.8125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="23.375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="28.375" bestFit="1" customWidth="1"/>
@@ -2782,7 +2770,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3000,67 +2988,67 @@
     </row>
     <row r="4" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>3</v>
+        <v>233</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -3080,7 +3068,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3181,7 +3169,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3194,7 +3182,7 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
@@ -3355,7 +3343,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="1"/>
@@ -3383,7 +3371,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -3391,10 +3379,10 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
@@ -3428,7 +3416,7 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
@@ -3448,7 +3436,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -3457,7 +3445,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -3497,10 +3485,10 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -3685,7 +3673,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3695,10 +3683,10 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
@@ -3732,7 +3720,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
@@ -3756,7 +3744,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3768,7 +3756,7 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
@@ -3801,10 +3789,10 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
@@ -3819,7 +3807,7 @@
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3839,7 +3827,7 @@
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="1"/>
@@ -3856,7 +3844,7 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -3866,7 +3854,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3878,7 +3866,7 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
@@ -3898,7 +3886,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -3909,7 +3897,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -3947,7 +3935,7 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="1"/>
@@ -4002,7 +3990,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4015,10 +4003,10 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -4048,12 +4036,12 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="1"/>
@@ -4073,16 +4061,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4092,11 +4080,11 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
@@ -4128,11 +4116,11 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
@@ -4147,13 +4135,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4168,11 +4156,11 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
@@ -4205,7 +4193,7 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="1"/>
@@ -4231,19 +4219,19 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="1"/>
@@ -4262,15 +4250,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4280,13 +4268,13 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
@@ -4301,16 +4289,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4320,7 +4308,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4330,10 +4318,10 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="1"/>
@@ -4349,15 +4337,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4370,17 +4358,17 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
@@ -4395,11 +4383,11 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -4417,10 +4405,10 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
@@ -4435,18 +4423,18 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4458,11 +4446,11 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
@@ -4477,10 +4465,10 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4489,7 +4477,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4501,10 +4489,10 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
@@ -4519,44 +4507,44 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
@@ -4571,48 +4559,48 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
@@ -4627,33 +4615,33 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>146</v>
+        <v>229</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4663,10 +4651,10 @@
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
@@ -4681,12 +4669,12 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4694,7 +4682,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4702,15 +4690,15 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
@@ -4725,45 +4713,45 @@
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="1"/>
@@ -4779,34 +4767,34 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4815,10 +4803,10 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
@@ -4833,52 +4821,52 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -4893,51 +4881,51 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="1"/>
@@ -4953,47 +4941,47 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>151</v>
+        <v>228</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>183</v>
+        <v>232</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="1"/>
@@ -5010,42 +4998,42 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="1"/>
@@ -5058,30 +5046,30 @@
     </row>
     <row r="55" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5093,7 +5081,7 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="1"/>
@@ -5115,7 +5103,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5187,13 +5175,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.7">
@@ -5202,7 +5190,7 @@
         <v>1977</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.7">
@@ -5281,7 +5269,7 @@
         <v>1988</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.7">
@@ -5374,7 +5362,7 @@
         <v>2001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.7">
@@ -5407,7 +5395,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5458,7 +5446,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5492,7 +5480,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5508,7 +5496,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.7">
@@ -5527,13 +5515,13 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.7">
@@ -5542,34 +5530,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5578,10 +5566,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4758A994-32BB-437F-9332-BBFB1847D887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2CF3BA-352B-466B-A8EA-39A3E0A549DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -68,10 +68,6 @@
     <t>彩羽匠</t>
   </si>
   <si>
-    <t>マリゴ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AWG</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1173,21 +1169,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ビクトリア弓月
-田中きずな(休)
-瀬戸レア</t>
-    <rPh sb="8" eb="10">
-      <t>タナカ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>セト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>あきば栞(SECRETBASE)
 MICHIKO(休)</t>
     <rPh sb="3" eb="4">
@@ -1823,6 +1804,28 @@
   </si>
   <si>
     <t>SEAdLINNNG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マリーゴールド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビクトリア弓月
+田中きずな(10.24復帰予定)
+瀬戸レア</t>
+    <rPh sb="8" eb="10">
+      <t>タナカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>フッキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セト</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2396,7 +2399,7 @@
     <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="19"/>
     <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="18"/>
     <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリゴ" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリーゴールド" dataDxfId="16"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ/COR" dataDxfId="15"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="14"/>
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
@@ -2770,7 +2773,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2988,67 +2991,67 @@
     </row>
     <row r="4" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>2</v>
+        <v>232</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -3068,7 +3071,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3169,7 +3172,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3182,7 +3185,7 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
@@ -3343,7 +3346,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="1"/>
@@ -3371,7 +3374,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -3379,10 +3382,10 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
@@ -3416,7 +3419,7 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
@@ -3436,7 +3439,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -3445,7 +3448,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -3485,10 +3488,10 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -3673,7 +3676,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3683,10 +3686,10 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
@@ -3720,7 +3723,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
@@ -3744,7 +3747,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3756,7 +3759,7 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
@@ -3789,10 +3792,10 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
@@ -3807,7 +3810,7 @@
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3827,7 +3830,7 @@
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="1"/>
@@ -3844,7 +3847,7 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -3854,7 +3857,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3866,7 +3869,7 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
@@ -3886,7 +3889,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -3897,7 +3900,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -3935,7 +3938,7 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="1"/>
@@ -3990,7 +3993,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4003,10 +4006,10 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -4036,12 +4039,12 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="1"/>
@@ -4061,16 +4064,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4080,11 +4083,11 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
@@ -4116,11 +4119,11 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
@@ -4135,13 +4138,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4156,11 +4159,11 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
@@ -4193,7 +4196,7 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="1"/>
@@ -4219,19 +4222,19 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="1"/>
@@ -4250,15 +4253,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4268,13 +4271,13 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
@@ -4289,16 +4292,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4308,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4318,10 +4321,10 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="1"/>
@@ -4337,15 +4340,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4358,17 +4361,17 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
@@ -4383,11 +4386,11 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -4405,10 +4408,10 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
@@ -4423,18 +4426,18 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4446,11 +4449,11 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
@@ -4465,10 +4468,10 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4477,7 +4480,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4489,10 +4492,10 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
@@ -4507,44 +4510,44 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
@@ -4559,48 +4562,48 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
@@ -4615,33 +4618,33 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4651,10 +4654,10 @@
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
@@ -4669,12 +4672,12 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4682,7 +4685,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4690,15 +4693,15 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
@@ -4713,45 +4716,45 @@
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="1"/>
@@ -4767,34 +4770,34 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="H50" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4803,10 +4806,10 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
@@ -4821,52 +4824,52 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -4881,51 +4884,51 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="1"/>
@@ -4941,47 +4944,47 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="G53" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="1"/>
@@ -4998,42 +5001,42 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="1"/>
@@ -5046,30 +5049,30 @@
     </row>
     <row r="55" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5081,7 +5084,7 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="1"/>
@@ -5103,7 +5106,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5175,13 +5178,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.7">
@@ -5190,7 +5193,7 @@
         <v>1977</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.7">
@@ -5269,7 +5272,7 @@
         <v>1988</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.7">
@@ -5362,7 +5365,7 @@
         <v>2001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.7">
@@ -5395,7 +5398,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5446,7 +5449,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5480,7 +5483,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5496,7 +5499,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.7">
@@ -5515,13 +5518,13 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.7">
@@ -5530,34 +5533,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5566,10 +5569,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2CF3BA-352B-466B-A8EA-39A3E0A549DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCCB98A-EDEA-4F27-B8E6-B7F8094C3C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="233">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1621,10 +1621,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>IR/ホットシュシュ/COR</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>郷田明日香(休)
 ブランキー真帆
 Chi Chi
@@ -1668,16 +1664,6 @@
     </rPh>
     <rPh sb="60" eb="62">
       <t>キシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>瀬戸ノノカ(休)(9/20引退)</t>
-    <rPh sb="6" eb="7">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>インタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1826,6 +1812,10 @@
     <rPh sb="25" eb="27">
       <t>セト</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイスリボン/Hotシュシュ/COR</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2400,7 +2390,7 @@
     <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="18"/>
     <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="17"/>
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリーゴールド" dataDxfId="16"/>
-    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="IR/ホットシュシュ/COR" dataDxfId="15"/>
+    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="アイスリボン/Hotシュシュ/COR" dataDxfId="15"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="14"/>
     <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
     <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
@@ -2798,7 +2788,7 @@
     <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RV2)</f>
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2886,7 +2876,7 @@
      LEN(M5:M1001) - LEN(SUBSTITUTE(M5:M1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N2" s="1" cm="1">
         <f t="array" ref="N2">SUMPRODUCT(
@@ -3003,10 +2993,10 @@
         <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -3033,7 +3023,7 @@
         <v>15</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>20</v>
@@ -4144,7 +4134,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4618,7 +4608,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
@@ -4754,7 +4744,7 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="1"/>
@@ -4806,7 +4796,7 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="V50" s="3" t="s">
         <v>140</v>
@@ -4824,7 +4814,7 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>210</v>
@@ -4833,7 +4823,7 @@
         <v>200</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>143</v>
@@ -4849,9 +4839,7 @@
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
-      <c r="M51" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
         <v>98</v>
       </c>
@@ -4866,10 +4854,10 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -4928,7 +4916,7 @@
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="1"/>
@@ -4944,7 +4932,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>180</v>
@@ -4975,7 +4963,7 @@
         <v>175</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4984,7 +4972,7 @@
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="1"/>
@@ -5010,7 +4998,7 @@
         <v>155</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
@@ -5056,13 +5044,13 @@
         <v>172</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>197</v>
@@ -5084,7 +5072,7 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCCB98A-EDEA-4F27-B8E6-B7F8094C3C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE22675-0F5D-4A6B-A0BF-7BBDD3799057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="234">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1816,6 +1816,10 @@
   </si>
   <si>
     <t>アイスリボン/Hotシュシュ/COR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒼あいな</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2788,7 +2792,7 @@
     <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RV2)</f>
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2948,7 +2952,7 @@
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -4974,7 +4978,9 @@
       <c r="U53" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="V53" s="3"/>
+      <c r="V53" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="AA53" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE22675-0F5D-4A6B-A0BF-7BBDD3799057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7273D2FC-1D4D-41CA-9AFD-FE3D1887FC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="235">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1820,6 +1820,11 @@
   </si>
   <si>
     <t>蒼あいな</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;中嶋野乃&gt;
+&lt;えん&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2792,7 +2797,7 @@
     <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RV2)</f>
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2920,7 +2925,7 @@
      LEN(R5:R1001) - LEN(SUBSTITUTE(R5:R1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S2" s="1" cm="1">
         <f t="array" ref="S2">SUMPRODUCT(
@@ -5074,7 +5079,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
+      <c r="R55" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7273D2FC-1D4D-41CA-9AFD-FE3D1887FC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D7CFB9-EEC6-426D-93FD-E1AC120E481A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6120" yWindow="315" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="31035" yWindow="555" windowWidth="21690" windowHeight="14633" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -960,10 +960,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>渡辺桃(休)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シン・広田・葛飾さくら</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1825,6 +1821,10 @@
   <si>
     <t>&lt;中嶋野乃&gt;
 &lt;えん&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>渡辺桃</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3002,10 +3002,10 @@
         <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -3026,13 +3026,13 @@
         <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>20</v>
@@ -3685,10 +3685,10 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
@@ -3722,7 +3722,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
@@ -3992,7 +3992,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4008,7 +4008,7 @@
         <v>51</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -4063,12 +4063,12 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
@@ -4143,7 +4143,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
@@ -4233,7 +4233,7 @@
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="1"/>
@@ -4294,7 +4294,7 @@
         <v>114</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>35</v>
@@ -4323,7 +4323,7 @@
         <v>81</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="1"/>
@@ -4339,15 +4339,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4360,7 +4360,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3" t="s">
@@ -4370,7 +4370,7 @@
         <v>120</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
@@ -4385,7 +4385,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>134</v>
+        <v>234</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4407,10 +4407,10 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
@@ -4425,7 +4425,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
@@ -4467,10 +4467,10 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4494,7 +4494,7 @@
         <v>103</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
@@ -4509,7 +4509,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4531,13 +4531,13 @@
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>93</v>
@@ -4561,7 +4561,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>124</v>
@@ -4570,7 +4570,7 @@
         <v>121</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4580,7 +4580,7 @@
         <v>23</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>60</v>
@@ -4599,10 +4599,10 @@
         <v>83</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
@@ -4617,14 +4617,14 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>86</v>
@@ -4633,10 +4633,10 @@
         <v>19</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4656,7 +4656,7 @@
         <v>125</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
@@ -4697,10 +4697,10 @@
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
@@ -4718,23 +4718,23 @@
         <v>43</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>22</v>
@@ -4753,7 +4753,7 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="1"/>
@@ -4769,10 +4769,10 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>33</v>
@@ -4781,7 +4781,7 @@
         <v>123</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>18</v>
@@ -4796,7 +4796,7 @@
         <v>62</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4805,10 +4805,10 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
@@ -4823,19 +4823,19 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>97</v>
@@ -4863,10 +4863,10 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -4893,10 +4893,10 @@
         <v>113</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>65</v>
@@ -4909,10 +4909,10 @@
         <v>95</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="1"/>
@@ -4941,38 +4941,38 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>132</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>85</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4981,10 +4981,10 @@
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
@@ -5000,42 +5000,42 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="1"/>
@@ -5052,26 +5052,26 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5080,12 +5080,12 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="1"/>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
@@ -5561,7 +5561,7 @@
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5570,7 +5570,7 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>133</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D7CFB9-EEC6-426D-93FD-E1AC120E481A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7B25BD-03BB-49E7-85E8-D41929F1A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31035" yWindow="555" windowWidth="21690" windowHeight="14633" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="6623" yWindow="368" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1453,11 +1453,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;濱名亜実&gt;(はまな あみ)
-&lt;椿本浩子&gt;(つばきもと ひろこ)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>高野玲菜</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1825,6 +1820,14 @@
   </si>
   <si>
     <t>渡辺桃</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;浜名あみ&gt;(はまな あみ)(10.25デビュー予定)
+&lt;椿本浩子&gt;(つばきもと ひろこ)</t>
+    <rPh sb="24" eb="26">
+      <t>ヨテイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3002,10 +3005,10 @@
         <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -3032,7 +3035,7 @@
         <v>15</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>20</v>
@@ -4143,7 +4146,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4294,7 +4297,7 @@
         <v>114</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>35</v>
@@ -4385,7 +4388,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
@@ -4425,7 +4428,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
@@ -4470,7 +4473,7 @@
         <v>146</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4617,14 +4620,14 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>86</v>
@@ -4636,7 +4639,7 @@
         <v>143</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4656,7 +4659,7 @@
         <v>125</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
@@ -4734,7 +4737,7 @@
         <v>64</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>22</v>
@@ -4753,7 +4756,7 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="1"/>
@@ -4772,7 +4775,7 @@
         <v>183</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>33</v>
@@ -4805,7 +4808,7 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="V50" s="3" t="s">
         <v>139</v>
@@ -4823,16 +4826,16 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>142</v>
@@ -4863,10 +4866,10 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -4925,7 +4928,7 @@
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="1"/>
@@ -4941,7 +4944,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>179</v>
@@ -4972,7 +4975,7 @@
         <v>174</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -4981,10 +4984,10 @@
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
@@ -5003,20 +5006,20 @@
         <v>180</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>154</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>170</v>
@@ -5035,7 +5038,7 @@
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="1"/>
@@ -5055,23 +5058,23 @@
         <v>171</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>188</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5080,12 +5083,12 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7B25BD-03BB-49E7-85E8-D41929F1A6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374E11C9-741B-4046-ADFE-E287138616B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6623" yWindow="368" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1823,9 +1823,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;浜名あみ&gt;(はまな あみ)(10.25デビュー予定)
-&lt;椿本浩子&gt;(つばきもと ひろこ)</t>
-    <rPh sb="24" eb="26">
+    <t>&lt;浜名あみ&gt;(10.25デビュー予定)
+&lt;TSUBAKI&gt;(10.25デビュー予定)</t>
+    <rPh sb="16" eb="18">
       <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374E11C9-741B-4046-ADFE-E287138616B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3954B925-6813-4F80-BC5D-74D4441CA8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6623" yWindow="368" windowWidth="21690" windowHeight="14632" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -109,20 +109,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>石川奈青
-桜井麻衣</t>
-    <rPh sb="0" eb="4">
-      <t>イシカワナオ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サクライ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アジャコング</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -590,11 +576,6 @@
   <si>
     <t>りこ(IR)
 緋彩もえ(HCC)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Yappy(IR)
-こゆき(HCC)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1597,12 +1578,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>神嵜志音
-さとうもも 
-清司麗菜</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ちゅら愛花</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1655,14 +1630,6 @@
     </rPh>
     <rPh sb="60" eb="62">
       <t>キシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;ユウカ&gt;(仮)
-&lt;咲森チエリ&gt;(10.3デビュー予定)</t>
-    <rPh sb="25" eb="27">
-      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1828,6 +1795,51 @@
     <rPh sb="16" eb="18">
       <t>ヨテイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石川奈青(休)
+桜井麻衣(10.24退団予定)</t>
+    <rPh sb="0" eb="4">
+      <t>イシカワナオ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクライ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>マイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>タイダン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Yappy(IR)
+こゆき(HCC)(12.26退団予定)</t>
+    <rPh sb="24" eb="26">
+      <t>タイダン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神嵜志音
+さとうもも 
+清司麗菜
+咲森チエリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2775,7 +2787,7 @@
   <sheetData>
     <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -3002,55 +3014,55 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>7</v>
@@ -3174,7 +3186,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3187,7 +3199,7 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
@@ -3348,7 +3360,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="1"/>
@@ -3376,7 +3388,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -3384,10 +3396,10 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
@@ -3421,7 +3433,7 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
@@ -3441,7 +3453,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -3450,7 +3462,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -3490,10 +3502,10 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -3678,7 +3690,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3688,10 +3700,10 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
@@ -3725,7 +3737,7 @@
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
@@ -3749,7 +3761,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3761,7 +3773,7 @@
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
@@ -3794,10 +3806,10 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
@@ -3812,7 +3824,7 @@
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3832,7 +3844,7 @@
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="1"/>
@@ -3849,7 +3861,7 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -3859,7 +3871,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3871,7 +3883,7 @@
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
@@ -3891,7 +3903,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -3902,7 +3914,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -3940,7 +3952,7 @@
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="1"/>
@@ -3995,7 +4007,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4008,10 +4020,10 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -4041,12 +4053,12 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="1"/>
@@ -4066,16 +4078,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4085,11 +4097,11 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
@@ -4121,11 +4133,11 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
@@ -4140,13 +4152,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4161,11 +4173,11 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
@@ -4198,7 +4210,7 @@
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="1"/>
@@ -4224,19 +4236,19 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="1"/>
@@ -4255,15 +4267,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4273,13 +4285,13 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
@@ -4294,16 +4306,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4313,7 +4325,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4323,10 +4335,10 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="1"/>
@@ -4342,15 +4354,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4363,17 +4375,17 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
@@ -4388,11 +4400,11 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -4410,10 +4422,10 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
@@ -4428,18 +4440,18 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4451,11 +4463,11 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
@@ -4470,10 +4482,10 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -4482,7 +4494,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4494,10 +4506,10 @@
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
@@ -4512,7 +4524,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4520,36 +4532,36 @@
         <v>9</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
@@ -4564,48 +4576,48 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
@@ -4620,33 +4632,33 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4656,10 +4668,10 @@
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
       <c r="U47" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
@@ -4674,12 +4686,12 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>10</v>
+        <v>231</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4687,7 +4699,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4695,15 +4707,15 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
@@ -4718,45 +4730,45 @@
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="1"/>
@@ -4772,34 +4784,34 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="H50" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4808,10 +4820,10 @@
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
@@ -4826,50 +4838,50 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
@@ -4884,51 +4896,51 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="1"/>
@@ -4944,50 +4956,50 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="G53" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T53" s="3"/>
       <c r="U53" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
@@ -5003,42 +5015,42 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="1"/>
@@ -5051,30 +5063,30 @@
     </row>
     <row r="55" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5083,12 +5095,12 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="1"/>
@@ -5110,7 +5122,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5182,13 +5194,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.7">
@@ -5276,7 +5288,7 @@
         <v>1988</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.7">
@@ -5369,7 +5381,7 @@
         <v>2001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.7">
@@ -5402,7 +5414,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5453,7 +5465,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5487,7 +5499,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5503,7 +5515,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.7">
@@ -5522,13 +5534,13 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.7">
@@ -5537,34 +5549,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5573,10 +5585,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3954B925-6813-4F80-BC5D-74D4441CA8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917B4E36-7440-49D9-B7FA-9851E8F033BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="983" yWindow="1927" windowWidth="12825" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1839,7 +1839,8 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;ユウカ&gt;(仮)</t>
+    <t>&lt;ユウカ&gt;(仮)
+&lt;双葉しおり&gt;(仮)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2812,7 +2813,7 @@
     <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RV2)</f>
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2836,7 +2837,7 @@
      LEN(E5:E1001) - LEN(SUBSTITUTE(E5:E1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" cm="1">
         <f t="array" ref="F2">SUMPRODUCT(

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917B4E36-7440-49D9-B7FA-9851E8F033BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0C6714-1E1C-46D1-9D63-DD596AB4FAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="983" yWindow="1927" windowWidth="12825" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1926,6 +1926,26 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2294,26 +2314,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2412,25 +2412,25 @@
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="19"/>
+    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="0"/>
     <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリーゴールド" dataDxfId="16"/>
-    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="アイスリボン/Hotシュシュ/COR" dataDxfId="15"/>
-    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="14"/>
-    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="11"/>
-    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="10"/>
-    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="9"/>
-    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="SEAdLINNNG" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="3"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリーゴールド" dataDxfId="17"/>
+    <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="アイスリボン/Hotシュシュ/COR" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
+    <tableColumn id="30" xr3:uid="{BB23C0DC-5AEB-431A-A828-4D1BDF4F315F}" name="JTO" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{9647ED0D-42FB-42C1-BFB2-8B8D56D414C4}" name="SENDAI" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{D066356F-6174-4702-9379-264D5C000032}" name="マーベラス" dataDxfId="12"/>
+    <tableColumn id="32" xr3:uid="{67EA2433-E1D1-4094-BFB4-0EDB7438926B}" name="Pure-J" dataDxfId="11"/>
+    <tableColumn id="29" xr3:uid="{ADFF1D58-E918-4FF6-B352-AA98020CFD16}" name="チョコプロ" dataDxfId="10"/>
+    <tableColumn id="34" xr3:uid="{C9FDFCD5-EB7A-4498-855C-DD4AF6E60734}" name="なにわ女子" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{86389032-6123-44BF-98AB-D3CA13F2577A}" name="LLPW-X" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{8FEFA60F-BAF5-466B-B569-8C96F8534AF7}" name="SEAdLINNNG" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2753,40 +2753,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AI56"/>
   <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.3125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.3125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="37.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.6875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="41.0625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="50.0625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="30.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="21.3125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="30.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="27.3125" style="1"/>
-    <col min="35" max="16384" width="27.3125" style="1"/>
+    <col min="3" max="3" width="23.5625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.3125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.3125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="37.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.6875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.0625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="50.0625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="30.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="27.3125" style="1"/>
+    <col min="36" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
@@ -2794,23 +2795,24 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="J1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="N1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="Q1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="V1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="AA1" s="1"/>
+      <c r="Y1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
-      <c r="AH1" s="1"/>
-    </row>
-    <row r="2" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE1" s="1"/>
+      <c r="AI1" s="1"/>
+    </row>
+    <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RV2)</f>
         <v>379</v>
@@ -2829,7 +2831,7 @@
      LEN(D5:D1001) - LEN(SUBSTITUTE(D5:D1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(
@@ -2837,7 +2839,7 @@
      LEN(E5:E1001) - LEN(SUBSTITUTE(E5:E1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" cm="1">
         <f t="array" ref="F2">SUMPRODUCT(
@@ -2975,36 +2977,37 @@
 )</f>
         <v>52</v>
       </c>
-      <c r="W2" s="1"/>
       <c r="X2" s="1"/>
-      <c r="AA2" s="1"/>
+      <c r="Y2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AH2" s="1"/>
-    </row>
-    <row r="3" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE2" s="1"/>
+      <c r="AI2" s="1"/>
+    </row>
+    <row r="3" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="K3" s="1"/>
+      <c r="J3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="O3" s="1"/>
+      <c r="N3" s="1"/>
       <c r="P3" s="1"/>
-      <c r="S3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
-      <c r="W3" s="1"/>
+      <c r="V3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="AA3" s="1"/>
+      <c r="Y3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AH3" s="1"/>
-    </row>
-    <row r="4" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE3" s="1"/>
+      <c r="AI3" s="1"/>
+    </row>
+    <row r="4" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
@@ -3012,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>224</v>
@@ -3068,15 +3071,15 @@
       <c r="V4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-      <c r="AA4" s="1"/>
+      <c r="Y4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AH4" s="1"/>
-    </row>
-    <row r="5" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE4" s="1"/>
+      <c r="AI4" s="1"/>
+    </row>
+    <row r="5" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3102,15 +3105,15 @@
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-      <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="AA5" s="1"/>
+      <c r="Y5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AH5" s="1"/>
-    </row>
-    <row r="6" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE5" s="1"/>
+      <c r="AI5" s="1"/>
+    </row>
+    <row r="6" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3134,15 +3137,15 @@
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-      <c r="AA6" s="1"/>
+      <c r="Y6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AH6" s="1"/>
-    </row>
-    <row r="7" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE6" s="1"/>
+      <c r="AI6" s="1"/>
+    </row>
+    <row r="7" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3166,15 +3169,15 @@
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
-      <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="AA7" s="1"/>
+      <c r="Y7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AH7" s="1"/>
-    </row>
-    <row r="8" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE7" s="1"/>
+      <c r="AI7" s="1"/>
+    </row>
+    <row r="8" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3202,15 +3205,15 @@
       <c r="V8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="AA8" s="1"/>
+      <c r="Y8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AH8" s="1"/>
-    </row>
-    <row r="9" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE8" s="1"/>
+      <c r="AI8" s="1"/>
+    </row>
+    <row r="9" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3234,15 +3237,15 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-      <c r="AA9" s="1"/>
+      <c r="Y9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
-      <c r="AH9" s="1"/>
-    </row>
-    <row r="10" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE9" s="1"/>
+      <c r="AI9" s="1"/>
+    </row>
+    <row r="10" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3266,15 +3269,15 @@
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="AA10" s="1"/>
+      <c r="Y10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
-      <c r="AH10" s="1"/>
-    </row>
-    <row r="11" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE10" s="1"/>
+      <c r="AI10" s="1"/>
+    </row>
+    <row r="11" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3298,15 +3301,15 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="AA11" s="1"/>
+      <c r="Y11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
-      <c r="AH11" s="1"/>
-    </row>
-    <row r="12" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE11" s="1"/>
+      <c r="AI11" s="1"/>
+    </row>
+    <row r="12" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3330,15 +3333,15 @@
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
-      <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-      <c r="AA12" s="1"/>
+      <c r="Y12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
-      <c r="AH12" s="1"/>
-    </row>
-    <row r="13" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE12" s="1"/>
+      <c r="AI12" s="1"/>
+    </row>
+    <row r="13" spans="1:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3364,15 +3367,15 @@
         <v>102</v>
       </c>
       <c r="V13" s="3"/>
-      <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="AA13" s="1"/>
+      <c r="Y13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
-      <c r="AH13" s="1"/>
-    </row>
-    <row r="14" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE13" s="1"/>
+      <c r="AI13" s="1"/>
+    </row>
+    <row r="14" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3402,15 +3405,15 @@
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-      <c r="AA14" s="1"/>
+      <c r="Y14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
-      <c r="AH14" s="1"/>
-    </row>
-    <row r="15" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE14" s="1"/>
+      <c r="AI14" s="1"/>
+    </row>
+    <row r="15" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3436,15 +3439,15 @@
       <c r="V15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-      <c r="AA15" s="1"/>
+      <c r="Y15" s="1"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
-      <c r="AH15" s="1"/>
-    </row>
-    <row r="16" spans="1:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE15" s="1"/>
+      <c r="AI15" s="1"/>
+    </row>
+    <row r="16" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3472,15 +3475,15 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-      <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="AA16" s="1"/>
+      <c r="Y16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
-      <c r="AH16" s="1"/>
-    </row>
-    <row r="17" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE16" s="1"/>
+      <c r="AI16" s="1"/>
+    </row>
+    <row r="17" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3508,15 +3511,15 @@
       <c r="V17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-      <c r="AA17" s="1"/>
+      <c r="Y17" s="1"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
-      <c r="AH17" s="1"/>
-    </row>
-    <row r="18" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE17" s="1"/>
+      <c r="AI17" s="1"/>
+    </row>
+    <row r="18" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3540,15 +3543,15 @@
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="AA18" s="1"/>
+      <c r="Y18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
-      <c r="AH18" s="1"/>
-    </row>
-    <row r="19" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE18" s="1"/>
+      <c r="AI18" s="1"/>
+    </row>
+    <row r="19" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3572,15 +3575,15 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-      <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="AA19" s="1"/>
+      <c r="Y19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
-      <c r="AH19" s="1"/>
-    </row>
-    <row r="20" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE19" s="1"/>
+      <c r="AI19" s="1"/>
+    </row>
+    <row r="20" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3604,15 +3607,15 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
-      <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="AA20" s="1"/>
+      <c r="Y20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
-      <c r="AH20" s="1"/>
-    </row>
-    <row r="21" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE20" s="1"/>
+      <c r="AI20" s="1"/>
+    </row>
+    <row r="21" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3636,15 +3639,15 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
-      <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="AA21" s="1"/>
+      <c r="Y21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
-      <c r="AH21" s="1"/>
-    </row>
-    <row r="22" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE21" s="1"/>
+      <c r="AI21" s="1"/>
+    </row>
+    <row r="22" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3668,15 +3671,15 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="AA22" s="1"/>
+      <c r="Y22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
-      <c r="AH22" s="1"/>
-    </row>
-    <row r="23" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE22" s="1"/>
+      <c r="AI22" s="1"/>
+    </row>
+    <row r="23" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3706,15 +3709,15 @@
       <c r="V23" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="AA23" s="1"/>
+      <c r="Y23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
-      <c r="AH23" s="1"/>
-    </row>
-    <row r="24" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE23" s="1"/>
+      <c r="AI23" s="1"/>
+    </row>
+    <row r="24" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3740,15 +3743,15 @@
       <c r="V24" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-      <c r="AA24" s="1"/>
+      <c r="Y24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
-      <c r="AH24" s="1"/>
-    </row>
-    <row r="25" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE24" s="1"/>
+      <c r="AI24" s="1"/>
+    </row>
+    <row r="25" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3776,15 +3779,15 @@
       <c r="V25" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-      <c r="AA25" s="1"/>
+      <c r="Y25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
-      <c r="AH25" s="1"/>
-    </row>
-    <row r="26" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE25" s="1"/>
+      <c r="AI25" s="1"/>
+    </row>
+    <row r="26" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3812,15 +3815,15 @@
       <c r="V26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-      <c r="AA26" s="1"/>
+      <c r="Y26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
-      <c r="AH26" s="1"/>
-    </row>
-    <row r="27" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE26" s="1"/>
+      <c r="AI26" s="1"/>
+    </row>
+    <row r="27" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3848,23 +3851,23 @@
         <v>66</v>
       </c>
       <c r="V27" s="3"/>
-      <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-      <c r="AA27" s="1"/>
+      <c r="Y27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
-      <c r="AH27" s="1"/>
-    </row>
-    <row r="28" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE27" s="1"/>
+      <c r="AI27" s="1"/>
+    </row>
+    <row r="28" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
       <c r="C28" s="3"/>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -3886,15 +3889,15 @@
       <c r="V28" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-      <c r="AA28" s="1"/>
+      <c r="Y28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
-      <c r="AH28" s="1"/>
-    </row>
-    <row r="29" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE28" s="1"/>
+      <c r="AI28" s="1"/>
+    </row>
+    <row r="29" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3922,15 +3925,15 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
-      <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="AA29" s="1"/>
+      <c r="Y29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
-      <c r="AH29" s="1"/>
-    </row>
-    <row r="30" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE29" s="1"/>
+      <c r="AI29" s="1"/>
+    </row>
+    <row r="30" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3956,15 +3959,15 @@
         <v>68</v>
       </c>
       <c r="V30" s="3"/>
-      <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-      <c r="AA30" s="1"/>
+      <c r="Y30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
-      <c r="AH30" s="1"/>
-    </row>
-    <row r="31" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE30" s="1"/>
+      <c r="AI30" s="1"/>
+    </row>
+    <row r="31" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3988,15 +3991,15 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
-      <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-      <c r="AA31" s="1"/>
+      <c r="Y31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
-      <c r="AH31" s="1"/>
-    </row>
-    <row r="32" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE31" s="1"/>
+      <c r="AI31" s="1"/>
+    </row>
+    <row r="32" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -4026,15 +4029,15 @@
       <c r="V32" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="AA32" s="1"/>
+      <c r="Y32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
-      <c r="AH32" s="1"/>
-    </row>
-    <row r="33" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE32" s="1"/>
+      <c r="AI32" s="1"/>
+    </row>
+    <row r="33" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4062,15 +4065,15 @@
         <v>114</v>
       </c>
       <c r="V33" s="3"/>
-      <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="AA33" s="1"/>
+      <c r="Y33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
-      <c r="AH33" s="1"/>
-    </row>
-    <row r="34" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE33" s="1"/>
+      <c r="AI33" s="1"/>
+    </row>
+    <row r="34" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -4104,15 +4107,15 @@
       <c r="V34" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="AA34" s="1"/>
+      <c r="Y34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
-      <c r="AH34" s="1"/>
-    </row>
-    <row r="35" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE34" s="1"/>
+      <c r="AI34" s="1"/>
+    </row>
+    <row r="35" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4140,15 +4143,15 @@
       <c r="V35" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-      <c r="AA35" s="1"/>
+      <c r="Y35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
-      <c r="AH35" s="1"/>
-    </row>
-    <row r="36" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE35" s="1"/>
+      <c r="AI35" s="1"/>
+    </row>
+    <row r="36" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
@@ -4180,15 +4183,15 @@
       <c r="V36" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-      <c r="AA36" s="1"/>
+      <c r="Y36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
-      <c r="AH36" s="1"/>
-    </row>
-    <row r="37" spans="2:34" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AE36" s="1"/>
+      <c r="AI36" s="1"/>
+    </row>
+    <row r="37" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4214,15 +4217,15 @@
         <v>49</v>
       </c>
       <c r="V37" s="3"/>
-      <c r="W37" s="1"/>
       <c r="X37" s="1"/>
-      <c r="AA37" s="1"/>
+      <c r="Y37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
-      <c r="AH37" s="1"/>
-    </row>
-    <row r="38" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE37" s="1"/>
+      <c r="AI37" s="1"/>
+    </row>
+    <row r="38" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4252,15 +4255,15 @@
         <v>193</v>
       </c>
       <c r="V38" s="3"/>
-      <c r="W38" s="1"/>
       <c r="X38" s="1"/>
-      <c r="AA38" s="1"/>
+      <c r="Y38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
-      <c r="AH38" s="1"/>
-    </row>
-    <row r="39" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE38" s="1"/>
+      <c r="AI38" s="1"/>
+    </row>
+    <row r="39" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4294,15 +4297,15 @@
       <c r="V39" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="W39" s="1"/>
       <c r="X39" s="1"/>
-      <c r="AA39" s="1"/>
+      <c r="Y39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
-      <c r="AH39" s="1"/>
-    </row>
-    <row r="40" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE39" s="1"/>
+      <c r="AI39" s="1"/>
+    </row>
+    <row r="40" spans="2:35" ht="33" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
@@ -4310,10 +4313,10 @@
         <v>112</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>97</v>
@@ -4342,25 +4345,25 @@
         <v>145</v>
       </c>
       <c r="V40" s="3"/>
-      <c r="W40" s="1"/>
       <c r="X40" s="1"/>
-      <c r="AA40" s="1"/>
+      <c r="Y40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
-      <c r="AH40" s="1"/>
-    </row>
-    <row r="41" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE40" s="1"/>
+      <c r="AI40" s="1"/>
+    </row>
+    <row r="41" spans="2:35" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>189</v>
       </c>
+      <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>184</v>
@@ -4388,25 +4391,25 @@
       <c r="V41" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="W41" s="1"/>
       <c r="X41" s="1"/>
-      <c r="AA41" s="1"/>
+      <c r="Y41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
-      <c r="AH41" s="1"/>
-    </row>
-    <row r="42" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE41" s="1"/>
+      <c r="AI41" s="1"/>
+    </row>
+    <row r="42" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
@@ -4428,25 +4431,25 @@
       <c r="V42" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="W42" s="1"/>
       <c r="X42" s="1"/>
-      <c r="AA42" s="1"/>
+      <c r="Y42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
-      <c r="AH42" s="1"/>
-    </row>
-    <row r="43" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE42" s="1"/>
+      <c r="AI42" s="1"/>
+    </row>
+    <row r="43" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -4470,25 +4473,25 @@
       <c r="V43" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="AA43" s="1"/>
+      <c r="Y43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
-      <c r="AH43" s="1"/>
-    </row>
-    <row r="44" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE43" s="1"/>
+      <c r="AI43" s="1"/>
+    </row>
+    <row r="44" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="3"/>
+      <c r="E44" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
@@ -4512,15 +4515,15 @@
       <c r="V44" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="W44" s="1"/>
       <c r="X44" s="1"/>
-      <c r="AA44" s="1"/>
+      <c r="Y44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
-      <c r="AH44" s="1"/>
-    </row>
-    <row r="45" spans="2:34" ht="33" x14ac:dyDescent="0.7">
+      <c r="AE44" s="1"/>
+      <c r="AI44" s="1"/>
+    </row>
+    <row r="45" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
@@ -4564,15 +4567,15 @@
       <c r="V45" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="W45" s="1"/>
       <c r="X45" s="1"/>
-      <c r="AA45" s="1"/>
+      <c r="Y45" s="1"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
-      <c r="AH45" s="1"/>
-    </row>
-    <row r="46" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE45" s="1"/>
+      <c r="AI45" s="1"/>
+    </row>
+    <row r="46" spans="2:35" ht="165" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
@@ -4580,10 +4583,10 @@
         <v>190</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>175</v>
@@ -4620,25 +4623,25 @@
       <c r="V46" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="W46" s="1"/>
       <c r="X46" s="1"/>
-      <c r="AA46" s="1"/>
+      <c r="Y46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
-      <c r="AH46" s="1"/>
-    </row>
-    <row r="47" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AE46" s="1"/>
+      <c r="AI46" s="1"/>
+    </row>
+    <row r="47" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
         <v>199</v>
       </c>
@@ -4674,15 +4677,15 @@
       <c r="V47" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="W47" s="1"/>
       <c r="X47" s="1"/>
-      <c r="AA47" s="1"/>
+      <c r="Y47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
-      <c r="AH47" s="1"/>
-    </row>
-    <row r="48" spans="2:34" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AE47" s="1"/>
+      <c r="AI47" s="1"/>
+    </row>
+    <row r="48" spans="2:35" ht="66" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4718,15 +4721,15 @@
       <c r="V48" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="W48" s="1"/>
       <c r="X48" s="1"/>
-      <c r="AA48" s="1"/>
+      <c r="Y48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
-      <c r="AH48" s="1"/>
-    </row>
-    <row r="49" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AE48" s="1"/>
+      <c r="AI48" s="1"/>
+    </row>
+    <row r="49" spans="2:35" ht="148.5" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4734,10 +4737,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>8</v>
@@ -4772,15 +4775,15 @@
         <v>214</v>
       </c>
       <c r="V49" s="3"/>
-      <c r="W49" s="1"/>
       <c r="X49" s="1"/>
-      <c r="AA49" s="1"/>
+      <c r="Y49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
-      <c r="AH49" s="1"/>
-    </row>
-    <row r="50" spans="2:34" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AE49" s="1"/>
+      <c r="AI49" s="1"/>
+    </row>
+    <row r="50" spans="2:35" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
@@ -4788,10 +4791,10 @@
         <v>181</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>121</v>
@@ -4826,15 +4829,15 @@
       <c r="V50" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="W50" s="1"/>
       <c r="X50" s="1"/>
-      <c r="AA50" s="1"/>
+      <c r="Y50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
-      <c r="AH50" s="1"/>
-    </row>
-    <row r="51" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE50" s="1"/>
+      <c r="AI50" s="1"/>
+    </row>
+    <row r="51" spans="2:35" ht="181.5" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
@@ -4842,10 +4845,10 @@
         <v>217</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>225</v>
@@ -4884,15 +4887,15 @@
       <c r="V51" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="W51" s="1"/>
       <c r="X51" s="1"/>
-      <c r="AA51" s="1"/>
+      <c r="Y51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-      <c r="AH51" s="1"/>
-    </row>
-    <row r="52" spans="2:34" ht="99" x14ac:dyDescent="0.7">
+      <c r="AE51" s="1"/>
+      <c r="AI51" s="1"/>
+    </row>
+    <row r="52" spans="2:35" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4900,10 +4903,10 @@
         <v>57</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>111</v>
@@ -4944,15 +4947,15 @@
         <v>210</v>
       </c>
       <c r="V52" s="3"/>
-      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="AA52" s="1"/>
+      <c r="Y52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
-      <c r="AH52" s="1"/>
-    </row>
-    <row r="53" spans="2:34" ht="132" x14ac:dyDescent="0.7">
+      <c r="AE52" s="1"/>
+      <c r="AI52" s="1"/>
+    </row>
+    <row r="53" spans="2:35" ht="280.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
@@ -4960,10 +4963,10 @@
         <v>218</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>179</v>
@@ -5002,24 +5005,24 @@
       <c r="V53" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="W53" s="1"/>
       <c r="X53" s="1"/>
-      <c r="AA53" s="1"/>
+      <c r="Y53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
-      <c r="AH53" s="1"/>
-    </row>
-    <row r="54" spans="2:34" ht="66" x14ac:dyDescent="0.7">
+      <c r="AE53" s="1"/>
+      <c r="AI53" s="1"/>
+    </row>
+    <row r="54" spans="2:35" ht="132" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>152</v>
@@ -5054,24 +5057,24 @@
         <v>200</v>
       </c>
       <c r="V54" s="3"/>
-      <c r="W54" s="1"/>
       <c r="X54" s="1"/>
-      <c r="AA54" s="1"/>
+      <c r="Y54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
-      <c r="AH54" s="1"/>
-    </row>
-    <row r="55" spans="2:34" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AE54" s="1"/>
+      <c r="AI54" s="1"/>
+    </row>
+    <row r="55" spans="2:35" ht="264" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>186</v>
@@ -5104,15 +5107,15 @@
         <v>215</v>
       </c>
       <c r="V55" s="3"/>
-      <c r="W55" s="1"/>
       <c r="X55" s="1"/>
-      <c r="AA55" s="1"/>
+      <c r="Y55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
-      <c r="AH55" s="1"/>
-    </row>
-    <row r="56" spans="2:34" x14ac:dyDescent="0.7">
+      <c r="AE55" s="1"/>
+      <c r="AI55" s="1"/>
+    </row>
+    <row r="56" spans="2:35" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5136,14 +5139,14 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-      <c r="W56" s="1"/>
       <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
       <c r="Z56"/>
-      <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
-      <c r="AH56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AI56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0C6714-1E1C-46D1-9D63-DD596AB4FAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B2842E-DFC5-4F4E-BB41-BB704B6CE47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="983" yWindow="1927" windowWidth="12825" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1509,13 +1509,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>堀このみ(Rose)(休)
-彩桜(アップタウン)
-結菜(伊藤道場)(休)
-志翠ヒカリ(EVO)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>岡優里佳
 アニータ・ヴォーン</t>
     <rPh sb="0" eb="4">
@@ -1602,15 +1595,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>浦幌ちほ(北都)
-ソイ(EVO)
-藤井瑠美愛(紀州)</t>
-    <rPh sb="23" eb="25">
-      <t>キシュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>志真うた(伊藤道場)
 CoCo(MyWay)
 大竹仁美(BBJ)
@@ -1634,23 +1618,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>苺畑ひより(666)
-横井真菜(REINA)
-タギリヒメ真夢(九州女子プロレス)
-彩月悠叶(Evolution, 2AW)
-さいとう(アップタウン)
-小久保アリサ(BBJ)
-CHIKA(EVO)
-虎牙のん(PPP)</t>
-    <rPh sb="31" eb="33">
-      <t>キュウシュウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>叶ミク(T-HEARTS)
 エチカミヤビ(PPP)</t>
     <phoneticPr fontId="1"/>
@@ -1841,6 +1808,53 @@
   <si>
     <t>&lt;ユウカ&gt;(仮)
 &lt;双葉しおり&gt;(仮)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Evolution</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CHIKA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>志翠ヒカリ
+Ayaka</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堀このみ(Rose)(休)
+彩桜(アップタウン)
+結菜(伊藤道場)(休)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>苺畑ひより(666)
+横井真菜(REINA)
+タギリヒメ真夢(九州女子プロレス)
+彩月悠叶(Evolution, 2AW)
+さいとう(アップタウン)
+小久保アリサ(BBJ)
+虎牙のん(PPP)</t>
+    <rPh sb="31" eb="33">
+      <t>キュウシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>浦幌ちほ(北都)
+藤井瑠美愛(紀州)</t>
+    <rPh sb="15" eb="17">
+      <t>キシュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1925,7 +1939,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -2314,6 +2328,26 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2407,12 +2441,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:V56" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="B4:V56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="19"/>
-    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}" name="テーブル1" displayName="テーブル1" ref="B4:W56" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="B4:W56" xr:uid="{4A34D807-EC26-4518-9852-7FFB26CEC57B}"/>
+  <tableColumns count="22">
+    <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="20"/>
+    <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="19"/>
     <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリーゴールド" dataDxfId="17"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="アイスリボン/Hotシュシュ/COR" dataDxfId="16"/>
@@ -2428,6 +2462,7 @@
     <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
     <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{8D9AD9D7-C22A-4356-B7C7-7A0C2345562B}" name="Evolution" dataDxfId="0"/>
     <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
     <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
     <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
@@ -2753,7 +2788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4F8F56-06F6-4E1D-8D81-5A485042419D}">
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AJ56"/>
   <sheetFormatPr defaultColWidth="27.3125" defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="1.875" style="1" bestFit="1" customWidth="1"/>
@@ -2770,24 +2805,25 @@
     <col min="15" max="15" width="28.375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="23.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.0625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="50.0625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.9375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="30.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="21.3125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="30.25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="21.1875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="30.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="27.3125" style="1"/>
-    <col min="36" max="16384" width="27.3125" style="1"/>
+    <col min="20" max="20" width="23.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="28.375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="36.625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="41.0625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="50.0625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="30.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="21.3125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="30.25" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.1875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="30.0625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="27.3125" style="1"/>
+    <col min="37" max="16384" width="27.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
@@ -2801,21 +2837,21 @@
       <c r="N1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="X1" s="1"/>
+      <c r="W1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="AB1" s="1"/>
+      <c r="Z1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
-      <c r="AI1" s="1"/>
-    </row>
-    <row r="2" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF1" s="1"/>
+      <c r="AJ1" s="1"/>
+    </row>
+    <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
-        <f>SUM(C2:RV2)</f>
-        <v>379</v>
+        <f>SUM(C2:RW2)</f>
+        <v>380</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2959,7 +2995,7 @@
      LEN(T5:T1001) - LEN(SUBSTITUTE(T5:T1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U2" s="1" cm="1">
         <f t="array" ref="U2">SUMPRODUCT(
@@ -2967,7 +3003,7 @@
      LEN(U5:U1001) - LEN(SUBSTITUTE(U5:U1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" cm="1">
         <f t="array" ref="V2">SUMPRODUCT(
@@ -2975,17 +3011,25 @@
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
+        <v>59</v>
+      </c>
+      <c r="W2" s="1" cm="1">
+        <f t="array" ref="W2">SUMPRODUCT(
+  IF(LEN(W5:W1001)=0, 0,
+     LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
+  )
+)</f>
         <v>52</v>
       </c>
-      <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="AB2" s="1"/>
+      <c r="Z2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
-      <c r="AI2" s="1"/>
-    </row>
-    <row r="3" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF2" s="1"/>
+      <c r="AJ2" s="1"/>
+    </row>
+    <row r="3" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -2996,18 +3040,18 @@
       <c r="N3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
-      <c r="X3" s="1"/>
+      <c r="W3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="AB3" s="1"/>
+      <c r="Z3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
-      <c r="AI3" s="1"/>
-    </row>
-    <row r="4" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF3" s="1"/>
+      <c r="AJ3" s="1"/>
+    </row>
+    <row r="4" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
@@ -3021,10 +3065,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -3051,7 +3095,7 @@
         <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>19</v>
@@ -3063,23 +3107,26 @@
         <v>103</v>
       </c>
       <c r="T4" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="AB4" s="1"/>
+      <c r="Z4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
-      <c r="AI4" s="1"/>
-    </row>
-    <row r="5" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF4" s="1"/>
+      <c r="AJ4" s="1"/>
+    </row>
+    <row r="5" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B5" s="3">
         <v>1977</v>
       </c>
@@ -3105,15 +3152,16 @@
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-      <c r="X5" s="1"/>
+      <c r="W5" s="3"/>
       <c r="Y5" s="1"/>
-      <c r="AB5" s="1"/>
+      <c r="Z5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
-      <c r="AI5" s="1"/>
-    </row>
-    <row r="6" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF5" s="1"/>
+      <c r="AJ5" s="1"/>
+    </row>
+    <row r="6" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B6" s="3">
         <v>1978</v>
       </c>
@@ -3137,15 +3185,16 @@
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="X6" s="1"/>
+      <c r="W6" s="3"/>
       <c r="Y6" s="1"/>
-      <c r="AB6" s="1"/>
+      <c r="Z6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
-      <c r="AI6" s="1"/>
-    </row>
-    <row r="7" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF6" s="1"/>
+      <c r="AJ6" s="1"/>
+    </row>
+    <row r="7" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B7" s="3">
         <v>1979</v>
       </c>
@@ -3169,15 +3218,16 @@
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
-      <c r="X7" s="1"/>
+      <c r="W7" s="3"/>
       <c r="Y7" s="1"/>
-      <c r="AB7" s="1"/>
+      <c r="Z7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
-      <c r="AI7" s="1"/>
-    </row>
-    <row r="8" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF7" s="1"/>
+      <c r="AJ7" s="1"/>
+    </row>
+    <row r="8" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B8" s="3">
         <v>1980</v>
       </c>
@@ -3202,18 +3252,19 @@
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="3" t="s">
+      <c r="V8" s="3"/>
+      <c r="W8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
-      <c r="AB8" s="1"/>
+      <c r="Z8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
-      <c r="AI8" s="1"/>
-    </row>
-    <row r="9" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF8" s="1"/>
+      <c r="AJ8" s="1"/>
+    </row>
+    <row r="9" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B9" s="3">
         <v>1981</v>
       </c>
@@ -3237,15 +3288,16 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="X9" s="1"/>
+      <c r="W9" s="3"/>
       <c r="Y9" s="1"/>
-      <c r="AB9" s="1"/>
+      <c r="Z9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
-      <c r="AI9" s="1"/>
-    </row>
-    <row r="10" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF9" s="1"/>
+      <c r="AJ9" s="1"/>
+    </row>
+    <row r="10" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B10" s="3">
         <v>1982</v>
       </c>
@@ -3269,15 +3321,16 @@
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="X10" s="1"/>
+      <c r="W10" s="3"/>
       <c r="Y10" s="1"/>
-      <c r="AB10" s="1"/>
+      <c r="Z10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1"/>
-      <c r="AI10" s="1"/>
-    </row>
-    <row r="11" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF10" s="1"/>
+      <c r="AJ10" s="1"/>
+    </row>
+    <row r="11" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B11" s="3">
         <v>1983</v>
       </c>
@@ -3301,15 +3354,16 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="X11" s="1"/>
+      <c r="W11" s="3"/>
       <c r="Y11" s="1"/>
-      <c r="AB11" s="1"/>
+      <c r="Z11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
-      <c r="AI11" s="1"/>
-    </row>
-    <row r="12" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF11" s="1"/>
+      <c r="AJ11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B12" s="3">
         <v>1984</v>
       </c>
@@ -3333,15 +3387,16 @@
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
-      <c r="X12" s="1"/>
+      <c r="W12" s="3"/>
       <c r="Y12" s="1"/>
-      <c r="AB12" s="1"/>
+      <c r="Z12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
-      <c r="AI12" s="1"/>
-    </row>
-    <row r="13" spans="1:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF12" s="1"/>
+      <c r="AJ12" s="1"/>
+    </row>
+    <row r="13" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B13" s="3">
         <v>1985</v>
       </c>
@@ -3363,19 +3418,20 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="3" t="s">
+      <c r="U13" s="3"/>
+      <c r="V13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="V13" s="3"/>
-      <c r="X13" s="1"/>
+      <c r="W13" s="3"/>
       <c r="Y13" s="1"/>
-      <c r="AB13" s="1"/>
+      <c r="Z13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
-      <c r="AI13" s="1"/>
-    </row>
-    <row r="14" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF13" s="1"/>
+      <c r="AJ13" s="1"/>
+    </row>
+    <row r="14" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B14" s="3">
         <v>1986</v>
       </c>
@@ -3399,21 +3455,22 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="3"/>
+      <c r="V14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
-      <c r="AB14" s="1"/>
+      <c r="Z14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
-      <c r="AI14" s="1"/>
-    </row>
-    <row r="15" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF14" s="1"/>
+      <c r="AJ14" s="1"/>
+    </row>
+    <row r="15" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B15" s="3">
         <v>1987</v>
       </c>
@@ -3436,18 +3493,19 @@
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
-      <c r="V15" s="3" t="s">
+      <c r="V15" s="3"/>
+      <c r="W15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
-      <c r="AB15" s="1"/>
+      <c r="Z15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
       <c r="AE15" s="1"/>
-      <c r="AI15" s="1"/>
-    </row>
-    <row r="16" spans="1:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF15" s="1"/>
+      <c r="AJ15" s="1"/>
+    </row>
+    <row r="16" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B16" s="3">
         <v>1988</v>
       </c>
@@ -3475,15 +3533,16 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-      <c r="X16" s="1"/>
+      <c r="W16" s="3"/>
       <c r="Y16" s="1"/>
-      <c r="AB16" s="1"/>
+      <c r="Z16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
       <c r="AE16" s="1"/>
-      <c r="AI16" s="1"/>
-    </row>
-    <row r="17" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF16" s="1"/>
+      <c r="AJ16" s="1"/>
+    </row>
+    <row r="17" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B17" s="3">
         <v>1989</v>
       </c>
@@ -3505,21 +3564,22 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="3" t="s">
+      <c r="U17" s="3"/>
+      <c r="V17" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="V17" s="3" t="s">
+      <c r="W17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="AB17" s="1"/>
+      <c r="Z17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
-      <c r="AI17" s="1"/>
-    </row>
-    <row r="18" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF17" s="1"/>
+      <c r="AJ17" s="1"/>
+    </row>
+    <row r="18" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B18" s="3">
         <v>1990</v>
       </c>
@@ -3543,15 +3603,16 @@
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
-      <c r="X18" s="1"/>
+      <c r="W18" s="3"/>
       <c r="Y18" s="1"/>
-      <c r="AB18" s="1"/>
+      <c r="Z18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
-      <c r="AI18" s="1"/>
-    </row>
-    <row r="19" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF18" s="1"/>
+      <c r="AJ18" s="1"/>
+    </row>
+    <row r="19" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B19" s="3">
         <v>1991</v>
       </c>
@@ -3575,15 +3636,16 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-      <c r="X19" s="1"/>
+      <c r="W19" s="3"/>
       <c r="Y19" s="1"/>
-      <c r="AB19" s="1"/>
+      <c r="Z19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
-      <c r="AI19" s="1"/>
-    </row>
-    <row r="20" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF19" s="1"/>
+      <c r="AJ19" s="1"/>
+    </row>
+    <row r="20" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B20" s="3">
         <v>1992</v>
       </c>
@@ -3607,15 +3669,16 @@
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
-      <c r="X20" s="1"/>
+      <c r="W20" s="3"/>
       <c r="Y20" s="1"/>
-      <c r="AB20" s="1"/>
+      <c r="Z20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
-      <c r="AI20" s="1"/>
-    </row>
-    <row r="21" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF20" s="1"/>
+      <c r="AJ20" s="1"/>
+    </row>
+    <row r="21" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B21" s="3">
         <v>1993</v>
       </c>
@@ -3639,15 +3702,16 @@
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
-      <c r="X21" s="1"/>
+      <c r="W21" s="3"/>
       <c r="Y21" s="1"/>
-      <c r="AB21" s="1"/>
+      <c r="Z21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
-      <c r="AI21" s="1"/>
-    </row>
-    <row r="22" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF21" s="1"/>
+      <c r="AJ21" s="1"/>
+    </row>
+    <row r="22" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B22" s="3">
         <v>1994</v>
       </c>
@@ -3671,15 +3735,16 @@
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="X22" s="1"/>
+      <c r="W22" s="3"/>
       <c r="Y22" s="1"/>
-      <c r="AB22" s="1"/>
+      <c r="Z22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1"/>
-      <c r="AI22" s="1"/>
-    </row>
-    <row r="23" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF22" s="1"/>
+      <c r="AJ22" s="1"/>
+    </row>
+    <row r="23" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B23" s="3">
         <v>1995</v>
       </c>
@@ -3703,21 +3768,22 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="3" t="s">
+      <c r="U23" s="3"/>
+      <c r="V23" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="V23" s="3" t="s">
+      <c r="W23" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="AB23" s="1"/>
+      <c r="Z23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
-      <c r="AI23" s="1"/>
-    </row>
-    <row r="24" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF23" s="1"/>
+      <c r="AJ23" s="1"/>
+    </row>
+    <row r="24" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B24" s="3">
         <v>1996</v>
       </c>
@@ -3740,18 +3806,19 @@
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
-      <c r="V24" s="3" t="s">
+      <c r="V24" s="3"/>
+      <c r="W24" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="AB24" s="1"/>
+      <c r="Z24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
-      <c r="AI24" s="1"/>
-    </row>
-    <row r="25" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF24" s="1"/>
+      <c r="AJ24" s="1"/>
+    </row>
+    <row r="25" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B25" s="3">
         <v>1997</v>
       </c>
@@ -3776,18 +3843,19 @@
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
-      <c r="V25" s="3" t="s">
+      <c r="V25" s="3"/>
+      <c r="W25" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="AB25" s="1"/>
+      <c r="Z25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
-      <c r="AI25" s="1"/>
-    </row>
-    <row r="26" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF25" s="1"/>
+      <c r="AJ25" s="1"/>
+    </row>
+    <row r="26" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3809,21 +3877,22 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="3" t="s">
+      <c r="U26" s="3"/>
+      <c r="V26" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="V26" s="3" t="s">
+      <c r="W26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="AB26" s="1"/>
+      <c r="Z26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
-      <c r="AI26" s="1"/>
-    </row>
-    <row r="27" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF26" s="1"/>
+      <c r="AJ26" s="1"/>
+    </row>
+    <row r="27" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B27" s="3">
         <v>1999</v>
       </c>
@@ -3847,19 +3916,20 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="3" t="s">
+      <c r="U27" s="3"/>
+      <c r="V27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V27" s="3"/>
-      <c r="X27" s="1"/>
+      <c r="W27" s="3"/>
       <c r="Y27" s="1"/>
-      <c r="AB27" s="1"/>
+      <c r="Z27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
-      <c r="AI27" s="1"/>
-    </row>
-    <row r="28" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF27" s="1"/>
+      <c r="AJ27" s="1"/>
+    </row>
+    <row r="28" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B28" s="3">
         <v>2000</v>
       </c>
@@ -3886,18 +3956,19 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
-      <c r="V28" s="3" t="s">
+      <c r="V28" s="3"/>
+      <c r="W28" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="AB28" s="1"/>
+      <c r="Z28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
       <c r="AE28" s="1"/>
-      <c r="AI28" s="1"/>
-    </row>
-    <row r="29" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF28" s="1"/>
+      <c r="AJ28" s="1"/>
+    </row>
+    <row r="29" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B29" s="3">
         <v>2001</v>
       </c>
@@ -3925,15 +3996,16 @@
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
-      <c r="X29" s="1"/>
+      <c r="W29" s="3"/>
       <c r="Y29" s="1"/>
-      <c r="AB29" s="1"/>
+      <c r="Z29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
-      <c r="AI29" s="1"/>
-    </row>
-    <row r="30" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF29" s="1"/>
+      <c r="AJ29" s="1"/>
+    </row>
+    <row r="30" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B30" s="3">
         <v>2002</v>
       </c>
@@ -3955,19 +4027,20 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3" t="s">
+      <c r="U30" s="3"/>
+      <c r="V30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="V30" s="3"/>
-      <c r="X30" s="1"/>
+      <c r="W30" s="3"/>
       <c r="Y30" s="1"/>
-      <c r="AB30" s="1"/>
+      <c r="Z30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
-      <c r="AI30" s="1"/>
-    </row>
-    <row r="31" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF30" s="1"/>
+      <c r="AJ30" s="1"/>
+    </row>
+    <row r="31" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B31" s="3">
         <v>2003</v>
       </c>
@@ -3991,15 +4064,16 @@
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
-      <c r="X31" s="1"/>
+      <c r="W31" s="3"/>
       <c r="Y31" s="1"/>
-      <c r="AB31" s="1"/>
+      <c r="Z31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
-      <c r="AI31" s="1"/>
-    </row>
-    <row r="32" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF31" s="1"/>
+      <c r="AJ31" s="1"/>
+    </row>
+    <row r="32" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B32" s="3">
         <v>2004</v>
       </c>
@@ -4023,21 +4097,22 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="3" t="s">
+      <c r="U32" s="3"/>
+      <c r="V32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="V32" s="3" t="s">
+      <c r="W32" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="AB32" s="1"/>
+      <c r="Z32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
-      <c r="AI32" s="1"/>
-    </row>
-    <row r="33" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AF32" s="1"/>
+      <c r="AJ32" s="1"/>
+    </row>
+    <row r="33" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B33" s="3">
         <v>2005</v>
       </c>
@@ -4061,19 +4136,20 @@
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="3" t="s">
+      <c r="U33" s="3"/>
+      <c r="V33" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="V33" s="3"/>
-      <c r="X33" s="1"/>
+      <c r="W33" s="3"/>
       <c r="Y33" s="1"/>
-      <c r="AB33" s="1"/>
+      <c r="Z33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
-      <c r="AI33" s="1"/>
-    </row>
-    <row r="34" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AF33" s="1"/>
+      <c r="AJ33" s="1"/>
+    </row>
+    <row r="34" spans="2:36" ht="66" x14ac:dyDescent="0.7">
       <c r="B34" s="3">
         <v>2006</v>
       </c>
@@ -4100,22 +4176,23 @@
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
-      <c r="T34" s="3" t="s">
+      <c r="T34" s="3"/>
+      <c r="U34" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3" t="s">
+      <c r="V34" s="3"/>
+      <c r="W34" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="AB34" s="1"/>
+      <c r="Z34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1"/>
-      <c r="AI34" s="1"/>
-    </row>
-    <row r="35" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AF34" s="1"/>
+      <c r="AJ34" s="1"/>
+    </row>
+    <row r="35" spans="2:36" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B35" s="3">
         <v>2007</v>
       </c>
@@ -4136,22 +4213,23 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
-      <c r="T35" s="3" t="s">
+      <c r="T35" s="3"/>
+      <c r="U35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3" t="s">
+      <c r="V35" s="3"/>
+      <c r="W35" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="AB35" s="1"/>
+      <c r="Z35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
-      <c r="AI35" s="1"/>
-    </row>
-    <row r="36" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF35" s="1"/>
+      <c r="AJ35" s="1"/>
+    </row>
+    <row r="36" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B36" s="3">
         <v>2008</v>
       </c>
@@ -4162,7 +4240,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4176,22 +4254,23 @@
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
-      <c r="T36" s="3" t="s">
+      <c r="T36" s="3"/>
+      <c r="U36" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3" t="s">
+      <c r="V36" s="3"/>
+      <c r="W36" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="AB36" s="1"/>
+      <c r="Z36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
-      <c r="AI36" s="1"/>
-    </row>
-    <row r="37" spans="2:35" ht="16.5" x14ac:dyDescent="0.7">
+      <c r="AF36" s="1"/>
+      <c r="AJ36" s="1"/>
+    </row>
+    <row r="37" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B37" s="3">
         <v>2009</v>
       </c>
@@ -4213,19 +4292,20 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="3" t="s">
+      <c r="U37" s="3"/>
+      <c r="V37" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="V37" s="3"/>
-      <c r="X37" s="1"/>
+      <c r="W37" s="3"/>
       <c r="Y37" s="1"/>
-      <c r="AB37" s="1"/>
+      <c r="Z37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
-      <c r="AI37" s="1"/>
-    </row>
-    <row r="38" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AF37" s="1"/>
+      <c r="AJ37" s="1"/>
+    </row>
+    <row r="38" spans="2:36" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B38" s="3">
         <v>2010</v>
       </c>
@@ -4251,19 +4331,20 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
-      <c r="U38" s="3" t="s">
+      <c r="U38" s="3"/>
+      <c r="V38" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="V38" s="3"/>
-      <c r="X38" s="1"/>
+      <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
-      <c r="AB38" s="1"/>
+      <c r="Z38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
-      <c r="AI38" s="1"/>
-    </row>
-    <row r="39" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF38" s="1"/>
+      <c r="AJ38" s="1"/>
+    </row>
+    <row r="39" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B39" s="3">
         <v>2011</v>
       </c>
@@ -4294,18 +4375,19 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-      <c r="V39" s="3" t="s">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="AB39" s="1"/>
+      <c r="Z39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
-      <c r="AI39" s="1"/>
-    </row>
-    <row r="40" spans="2:35" ht="33" x14ac:dyDescent="0.7">
+      <c r="AF39" s="1"/>
+      <c r="AJ39" s="1"/>
+    </row>
+    <row r="40" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B40" s="3">
         <v>2012</v>
       </c>
@@ -4316,7 +4398,7 @@
         <v>34</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>97</v>
@@ -4338,22 +4420,23 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-      <c r="T40" s="3" t="s">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U40" s="3" t="s">
+      <c r="V40" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="V40" s="3"/>
-      <c r="X40" s="1"/>
+      <c r="W40" s="3"/>
       <c r="Y40" s="1"/>
-      <c r="AB40" s="1"/>
+      <c r="Z40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
-      <c r="AI40" s="1"/>
-    </row>
-    <row r="41" spans="2:35" ht="99" x14ac:dyDescent="0.7">
+      <c r="AF40" s="1"/>
+      <c r="AJ40" s="1"/>
+    </row>
+    <row r="41" spans="2:36" ht="99" x14ac:dyDescent="0.7">
       <c r="B41" s="3">
         <v>2013</v>
       </c>
@@ -4382,29 +4465,30 @@
         <v>165</v>
       </c>
       <c r="S41" s="3"/>
-      <c r="T41" s="3" t="s">
+      <c r="T41" s="3"/>
+      <c r="U41" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="U41" s="3" t="s">
+      <c r="V41" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="V41" s="3" t="s">
+      <c r="W41" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="AB41" s="1"/>
+      <c r="Z41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
-      <c r="AI41" s="1"/>
-    </row>
-    <row r="42" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AF41" s="1"/>
+      <c r="AJ41" s="1"/>
+    </row>
+    <row r="42" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B42" s="3">
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
@@ -4425,21 +4509,22 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
-      <c r="U42" s="3" t="s">
+      <c r="U42" s="3"/>
+      <c r="V42" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="V42" s="3" t="s">
+      <c r="W42" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="AB42" s="1"/>
+      <c r="Z42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
-      <c r="AI42" s="1"/>
-    </row>
-    <row r="43" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AF42" s="1"/>
+      <c r="AJ42" s="1"/>
+    </row>
+    <row r="43" spans="2:36" ht="66" x14ac:dyDescent="0.7">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
@@ -4466,22 +4551,23 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
-      <c r="T43" s="3" t="s">
+      <c r="T43" s="3"/>
+      <c r="U43" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3" t="s">
+      <c r="V43" s="3"/>
+      <c r="W43" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
-      <c r="AB43" s="1"/>
+      <c r="Z43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
-      <c r="AI43" s="1"/>
-    </row>
-    <row r="44" spans="2:35" ht="49.5" x14ac:dyDescent="0.7">
+      <c r="AF43" s="1"/>
+      <c r="AJ43" s="1"/>
+    </row>
+    <row r="44" spans="2:36" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B44" s="3">
         <v>2016</v>
       </c>
@@ -4490,7 +4576,7 @@
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4509,21 +4595,22 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
-      <c r="U44" s="3" t="s">
+      <c r="U44" s="3"/>
+      <c r="V44" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="V44" s="3" t="s">
+      <c r="W44" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="AB44" s="1"/>
+      <c r="Z44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
-      <c r="AI44" s="1"/>
-    </row>
-    <row r="45" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AF44" s="1"/>
+      <c r="AJ44" s="1"/>
+    </row>
+    <row r="45" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B45" s="3">
         <v>2017</v>
       </c>
@@ -4558,24 +4645,25 @@
       <c r="S45" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="T45" s="3" t="s">
+      <c r="T45" s="3"/>
+      <c r="U45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U45" s="3" t="s">
+      <c r="V45" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="V45" s="3" t="s">
+      <c r="W45" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
-      <c r="AB45" s="1"/>
+      <c r="Z45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
-      <c r="AI45" s="1"/>
-    </row>
-    <row r="46" spans="2:35" ht="165" x14ac:dyDescent="0.7">
+      <c r="AF45" s="1"/>
+      <c r="AJ45" s="1"/>
+    </row>
+    <row r="46" spans="2:36" ht="99" x14ac:dyDescent="0.7">
       <c r="B46" s="3">
         <v>2018</v>
       </c>
@@ -4614,29 +4702,30 @@
       <c r="S46" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="T46" s="3" t="s">
+      <c r="T46" s="3"/>
+      <c r="U46" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="U46" s="3" t="s">
+      <c r="V46" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="V46" s="3" t="s">
+      <c r="W46" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="AB46" s="1"/>
+      <c r="Z46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
-      <c r="AI46" s="1"/>
-    </row>
-    <row r="47" spans="2:35" ht="82.5" x14ac:dyDescent="0.7">
+      <c r="AF46" s="1"/>
+      <c r="AJ46" s="1"/>
+    </row>
+    <row r="47" spans="2:36" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B47" s="3">
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>36</v>
@@ -4646,7 +4735,7 @@
         <v>199</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>18</v>
@@ -4655,7 +4744,7 @@
         <v>141</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4671,21 +4760,22 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="3" t="s">
+      <c r="U47" s="3"/>
+      <c r="V47" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="V47" s="3" t="s">
+      <c r="W47" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="AB47" s="1"/>
+      <c r="Z47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
-      <c r="AI47" s="1"/>
-    </row>
-    <row r="48" spans="2:35" ht="66" x14ac:dyDescent="0.7">
+      <c r="AF47" s="1"/>
+      <c r="AJ47" s="1"/>
+    </row>
+    <row r="48" spans="2:36" ht="49.5" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4695,7 +4785,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4715,21 +4805,22 @@
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="3" t="s">
+      <c r="U48" s="3"/>
+      <c r="V48" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="V48" s="3" t="s">
+      <c r="W48" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="AB48" s="1"/>
+      <c r="Z48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
-      <c r="AI48" s="1"/>
-    </row>
-    <row r="49" spans="2:35" ht="148.5" x14ac:dyDescent="0.7">
+      <c r="AF48" s="1"/>
+      <c r="AJ48" s="1"/>
+    </row>
+    <row r="49" spans="2:36" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B49" s="3">
         <v>2021</v>
       </c>
@@ -4753,7 +4844,7 @@
         <v>63</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>21</v>
@@ -4771,19 +4862,20 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="V49" s="3"/>
-      <c r="X49" s="1"/>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
-      <c r="AB49" s="1"/>
+      <c r="Z49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
       <c r="AE49" s="1"/>
-      <c r="AI49" s="1"/>
-    </row>
-    <row r="50" spans="2:35" ht="115.5" x14ac:dyDescent="0.7">
+      <c r="AF49" s="1"/>
+      <c r="AJ49" s="1"/>
+    </row>
+    <row r="50" spans="2:36" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
@@ -4794,7 +4886,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>121</v>
@@ -4823,35 +4915,36 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
-      <c r="U50" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="W50" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="AB50" s="1"/>
+      <c r="Z50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
-      <c r="AI50" s="1"/>
-    </row>
-    <row r="51" spans="2:35" ht="181.5" x14ac:dyDescent="0.7">
+      <c r="AF50" s="1"/>
+      <c r="AJ50" s="1"/>
+    </row>
+    <row r="51" spans="2:36" ht="99" x14ac:dyDescent="0.7">
       <c r="B51" s="3">
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>196</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>140</v>
@@ -4881,21 +4974,22 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
-      <c r="U51" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="X51" s="1"/>
+      <c r="W51" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="Y51" s="1"/>
-      <c r="AB51" s="1"/>
+      <c r="Z51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
-      <c r="AI51" s="1"/>
-    </row>
-    <row r="52" spans="2:35" ht="99" x14ac:dyDescent="0.7">
+      <c r="AF51" s="1"/>
+      <c r="AJ51" s="1"/>
+    </row>
+    <row r="52" spans="2:36" ht="99" x14ac:dyDescent="0.7">
       <c r="B52" s="3">
         <v>2024</v>
       </c>
@@ -4942,25 +5036,28 @@
       <c r="S52" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="T52" s="3"/>
-      <c r="U52" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="V52" s="3"/>
-      <c r="X52" s="1"/>
+      <c r="T52" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
-      <c r="AB52" s="1"/>
+      <c r="Z52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
-      <c r="AI52" s="1"/>
-    </row>
-    <row r="53" spans="2:35" ht="280.5" x14ac:dyDescent="0.7">
+      <c r="AF52" s="1"/>
+      <c r="AJ52" s="1"/>
+    </row>
+    <row r="53" spans="2:36" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>130</v>
@@ -4991,35 +5088,38 @@
         <v>172</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="T53" s="3"/>
-      <c r="U53" s="3" t="s">
-        <v>212</v>
-      </c>
+      <c r="T53" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="X53" s="1"/>
+        <v>237</v>
+      </c>
+      <c r="W53" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="Y53" s="1"/>
-      <c r="AB53" s="1"/>
+      <c r="Z53" s="1"/>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
-      <c r="AI53" s="1"/>
-    </row>
-    <row r="54" spans="2:35" ht="132" x14ac:dyDescent="0.7">
+      <c r="AF53" s="1"/>
+      <c r="AJ53" s="1"/>
+    </row>
+    <row r="54" spans="2:36" ht="66" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -5028,11 +5128,11 @@
         <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>194</v>
@@ -5052,26 +5152,29 @@
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="V54" s="3"/>
-      <c r="X54" s="1"/>
+      <c r="T54" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
-      <c r="AB54" s="1"/>
+      <c r="Z54" s="1"/>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
-      <c r="AI54" s="1"/>
-    </row>
-    <row r="55" spans="2:35" ht="264" x14ac:dyDescent="0.7">
+      <c r="AF54" s="1"/>
+      <c r="AJ54" s="1"/>
+    </row>
+    <row r="55" spans="2:36" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
         <v>131</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>169</v>
@@ -5080,13 +5183,13 @@
         <v>186</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5099,23 +5202,24 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="V55" s="3"/>
-      <c r="X55" s="1"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="W55" s="3"/>
       <c r="Y55" s="1"/>
-      <c r="AB55" s="1"/>
+      <c r="Z55" s="1"/>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
       <c r="AE55" s="1"/>
-      <c r="AI55" s="1"/>
-    </row>
-    <row r="56" spans="2:35" x14ac:dyDescent="0.7">
+      <c r="AF55" s="1"/>
+      <c r="AJ55" s="1"/>
+    </row>
+    <row r="56" spans="2:36" x14ac:dyDescent="0.7">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -5139,14 +5243,15 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-      <c r="X56" s="1"/>
+      <c r="W56" s="3"/>
       <c r="Y56" s="1"/>
-      <c r="Z56"/>
-      <c r="AB56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56"/>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
-      <c r="AI56" s="1"/>
+      <c r="AF56" s="1"/>
+      <c r="AJ56" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B2842E-DFC5-4F4E-BB41-BB704B6CE47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5CFCD3-4B02-4064-A92B-7A705CDA9925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="6750" yWindow="1222" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1345,11 +1345,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;あんり&gt;
-&lt;鈴夏&gt;(すずか)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>松本都</t>
     <rPh sb="0" eb="2">
       <t>マツモト</t>
@@ -1806,11 +1801,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;ユウカ&gt;(仮)
-&lt;双葉しおり&gt;(仮)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Evolution</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1855,6 +1845,19 @@
     <rPh sb="15" eb="17">
       <t>キシュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;あんり&gt;
+&lt;鈴夏&gt;(すずか)
+&lt;涼寧&gt;
+&lt;雅&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)
+&lt;双葉しおり&gt;(仮)
+&lt;ゆい&gt;(11.8デビュー予定)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1942,26 +1945,6 @@
   <dxfs count="24">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Noto Serif JP SemiBold"/>
-        <family val="1"/>
-        <charset val="128"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1980,6 +1963,26 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Noto Serif JP SemiBold"/>
+        <family val="1"/>
+        <charset val="128"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2462,10 +2465,10 @@
     <tableColumn id="26" xr3:uid="{73103D07-0C18-49E4-833A-41ADC2D3DE61}" name="Wave" dataDxfId="6"/>
     <tableColumn id="9" xr3:uid="{11B98A53-6EA8-44AD-B33B-82B313F30661}" name="ガンプロ" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{DDF38F40-8A77-4C8C-A9E5-47A29D5A7C86}" name="柳ヶ瀬" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{8D9AD9D7-C22A-4356-B7C7-7A0C2345562B}" name="Evolution" dataDxfId="0"/>
-    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="2"/>
-    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{8D9AD9D7-C22A-4356-B7C7-7A0C2345562B}" name="Evolution" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{56EE63D7-2296-4070-86B8-49B5D171AF20}" name="海外" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{50B4283E-4FFA-4BD0-B17F-8B3414F0E4D2}" name="その他" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{CE5E3F3B-FB92-45D8-AA5E-A154DC9761D3}" name="フリー" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2851,7 +2854,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2867,7 +2870,7 @@
      LEN(D5:D1001) - LEN(SUBSTITUTE(D5:D1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" cm="1">
         <f t="array" ref="E2">SUMPRODUCT(
@@ -2883,7 +2886,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -3065,10 +3068,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -3095,7 +3098,7 @@
         <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>19</v>
@@ -3107,7 +3110,7 @@
         <v>103</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>78</v>
@@ -4240,7 +4243,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4260,7 +4263,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4333,7 +4336,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4398,7 +4401,7 @@
         <v>34</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>97</v>
@@ -4444,7 +4447,7 @@
         <v>161</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -4488,7 +4491,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
@@ -4529,7 +4532,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>33</v>
@@ -4576,7 +4579,7 @@
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4668,7 +4671,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>119</v>
@@ -4710,7 +4713,7 @@
         <v>176</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4725,17 +4728,17 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>18</v>
@@ -4744,7 +4747,7 @@
         <v>141</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4765,7 +4768,7 @@
         <v>123</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4785,7 +4788,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4831,7 +4834,7 @@
         <v>156</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>8</v>
@@ -4844,7 +4847,7 @@
         <v>63</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>21</v>
@@ -4864,7 +4867,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4886,7 +4889,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>121</v>
@@ -4917,7 +4920,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>137</v>
@@ -4935,16 +4938,16 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>140</v>
@@ -4976,10 +4979,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5037,11 +5040,11 @@
         <v>106</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5057,7 +5060,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>130</v>
@@ -5072,7 +5075,7 @@
         <v>84</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>154</v>
@@ -5088,7 +5091,7 @@
         <v>172</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5096,14 +5099,14 @@
         <v>105</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5119,7 +5122,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -5128,14 +5131,14 @@
         <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>168</v>
@@ -5153,11 +5156,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5174,26 +5177,26 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>169</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5202,13 +5205,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5CFCD3-4B02-4064-A92B-7A705CDA9925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA89729-744E-42CC-A1FE-D833369D3553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6750" yWindow="1222" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1291,22 +1291,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>山岡聖怜(休)
-心希
-山﨑裕花</t>
-    <rPh sb="5" eb="6">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シンノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>NENE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>天咲光由
 ボジラ(休)</t>
     <rPh sb="9" eb="10">
@@ -1406,11 +1390,6 @@
     <rPh sb="8" eb="10">
       <t>ヨテイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Anna
-Fiony</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1663,15 +1642,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鉄アキラ
-姫ゆりあ(休)
-金屋あんね
-儛島エマ
-古沢稀杏
-フワちゃん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>飯田沙耶
 上谷沙弥
 向後桃(休)
@@ -1848,16 +1818,60 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;あんり&gt;
-&lt;鈴夏&gt;(すずか)
-&lt;涼寧&gt;
-&lt;雅&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;ユウカ&gt;(仮)
 &lt;双葉しおり&gt;(仮)
 &lt;ゆい&gt;(11.8デビュー予定)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NENE
+Syansyan(新臺灣)</t>
+    <rPh sb="14" eb="15">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイワン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Anna
+Fiony
+kuumu(新臺灣)</t>
+    <rPh sb="17" eb="18">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>タイワン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山岡聖怜(10.24復帰予定)
+心希
+山﨑裕花</t>
+    <rPh sb="16" eb="18">
+      <t>シンノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;あんり&gt;
+&lt;鈴夏&gt;(すずか)(プロテスト合格)
+&lt;涼寧&gt;
+&lt;雅&gt;</t>
+    <rPh sb="21" eb="23">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鉄アキラ
+姫ゆりあ(10.18復帰予定)
+金屋あんね
+儛島エマ
+古沢稀杏
+フワちゃん</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2854,7 +2868,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2902,7 +2916,7 @@
      LEN(H5:H1001) - LEN(SUBSTITUTE(H5:H1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" cm="1">
         <f t="array" ref="I2">SUMPRODUCT(
@@ -3068,10 +3082,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -3098,7 +3112,7 @@
         <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>19</v>
@@ -3110,7 +3124,7 @@
         <v>103</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>78</v>
@@ -4161,7 +4175,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -4243,7 +4257,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4263,7 +4277,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4336,7 +4350,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4401,7 +4415,7 @@
         <v>34</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>97</v>
@@ -4447,12 +4461,12 @@
         <v>161</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4491,7 +4505,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
@@ -4532,7 +4546,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>33</v>
@@ -4579,7 +4593,7 @@
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4671,7 +4685,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>119</v>
@@ -4713,7 +4727,7 @@
         <v>176</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4728,17 +4742,17 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>18</v>
@@ -4747,7 +4761,7 @@
         <v>141</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4768,7 +4782,7 @@
         <v>123</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4788,7 +4802,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4834,7 +4848,7 @@
         <v>156</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>8</v>
@@ -4847,7 +4861,7 @@
         <v>63</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>21</v>
@@ -4867,7 +4881,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4883,19 +4897,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>121</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>17</v>
@@ -4920,7 +4934,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>137</v>
@@ -4938,16 +4952,16 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>140</v>
@@ -4979,10 +4993,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5009,10 +5023,10 @@
         <v>111</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>64</v>
@@ -5040,11 +5054,11 @@
         <v>106</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5060,7 +5074,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>130</v>
@@ -5069,13 +5083,13 @@
         <v>177</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>84</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>154</v>
@@ -5091,7 +5105,7 @@
         <v>172</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5099,14 +5113,14 @@
         <v>105</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5122,7 +5136,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -5131,14 +5145,14 @@
         <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>168</v>
@@ -5156,11 +5170,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5177,7 +5191,7 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>169</v>
@@ -5186,17 +5200,17 @@
         <v>237</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5205,13 +5219,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA89729-744E-42CC-A1FE-D833369D3553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0311F7-72AC-49AB-8E29-B0241CA631D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="1222" windowWidth="21600" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1643" yWindow="1335" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1509,31 +1509,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>荒幡寧々
-水嶋さくら
-みあ朝子
-石川はるか
-岩井杏加
-才原茉莉乃
-汐月なぎさ</t>
-    <rPh sb="13" eb="15">
-      <t>アサコ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>イシカワ</t>
-    </rPh>
-    <rPh sb="22" eb="26">
-      <t>イワイキョウカ</t>
-    </rPh>
-    <rPh sb="27" eb="32">
-      <t>サイハラマリノ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>シオツキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>青葉ちい
 研菜々美</t>
     <rPh sb="0" eb="2">
@@ -1872,6 +1847,34 @@
 儛島エマ
 古沢稀杏
 フワちゃん</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>荒幡寧々
+水嶋さくら(12/29卒業プロレスラーへ)
+みあ朝子
+石川はるか
+岩井杏加
+才原茉莉乃
+汐月なぎさ</t>
+    <rPh sb="16" eb="18">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>アサコ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>イシカワ</t>
+    </rPh>
+    <rPh sb="38" eb="42">
+      <t>イワイキョウカ</t>
+    </rPh>
+    <rPh sb="43" eb="48">
+      <t>サイハラマリノ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>シオツキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3082,10 +3085,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -3112,7 +3115,7 @@
         <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>19</v>
@@ -3124,7 +3127,7 @@
         <v>103</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>78</v>
@@ -4257,7 +4260,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4505,7 +4508,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
@@ -4742,7 +4745,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>36</v>
@@ -4752,7 +4755,7 @@
         <v>195</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>18</v>
@@ -4802,7 +4805,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4881,7 +4884,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4892,7 +4895,7 @@
       <c r="AF49" s="1"/>
       <c r="AJ49" s="1"/>
     </row>
-    <row r="50" spans="2:36" ht="115.5" x14ac:dyDescent="0.7">
+    <row r="50" spans="2:36" ht="132" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
@@ -4903,7 +4906,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>121</v>
@@ -4934,7 +4937,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>137</v>
@@ -4952,16 +4955,16 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>192</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>140</v>
@@ -4993,10 +4996,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5026,7 +5029,7 @@
         <v>180</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>64</v>
@@ -5054,11 +5057,11 @@
         <v>106</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5074,7 +5077,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>130</v>
@@ -5083,13 +5086,13 @@
         <v>177</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>84</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>154</v>
@@ -5105,7 +5108,7 @@
         <v>172</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5113,14 +5116,14 @@
         <v>105</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5136,7 +5139,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -5145,11 +5148,11 @@
         <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>190</v>
@@ -5170,11 +5173,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5191,22 +5194,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>169</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5219,13 +5222,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0311F7-72AC-49AB-8E29-B0241CA631D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCAA031-63BA-4D70-A6BF-797EAEFA542D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1643" yWindow="1335" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1524,11 +1524,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;Y&gt;
-&lt;みく&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>郷田明日香(休)
 ブランキー真帆
 Chi Chi
@@ -1831,16 +1826,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;あんり&gt;
-&lt;鈴夏&gt;(すずか)(プロテスト合格)
-&lt;涼寧&gt;
-&lt;雅&gt;</t>
-    <rPh sb="21" eb="23">
-      <t>ゴウカク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鉄アキラ
 姫ゆりあ(10.18復帰予定)
 金屋あんね
@@ -1875,6 +1860,17 @@
     <rPh sb="49" eb="51">
       <t>シオツキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;Y&gt;
+&lt;みく&gt;(11.29デビュー予定)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;鈴夏&gt;(10.24デビュー予定)
+&lt;涼寧&gt;
+&lt;雅&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2871,7 +2867,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2903,7 +2899,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -3085,10 +3081,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -3115,7 +3111,7 @@
         <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>19</v>
@@ -3127,7 +3123,7 @@
         <v>103</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>78</v>
@@ -4260,7 +4256,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4508,7 +4504,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
@@ -4745,7 +4741,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>36</v>
@@ -4755,7 +4751,7 @@
         <v>195</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>18</v>
@@ -4805,7 +4801,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4884,7 +4880,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4906,7 +4902,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>121</v>
@@ -4937,7 +4933,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>137</v>
@@ -4955,7 +4951,7 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>192</v>
@@ -4964,7 +4960,7 @@
         <v>200</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>140</v>
@@ -4996,10 +4992,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5029,7 +5025,7 @@
         <v>180</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>64</v>
@@ -5057,11 +5053,11 @@
         <v>106</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5077,7 +5073,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>130</v>
@@ -5086,13 +5082,13 @@
         <v>177</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>84</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>154</v>
@@ -5108,7 +5104,7 @@
         <v>172</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5116,14 +5112,14 @@
         <v>105</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5139,7 +5135,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -5148,7 +5144,7 @@
         <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
@@ -5173,11 +5169,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5194,22 +5190,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>169</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5222,13 +5218,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCAA031-63BA-4D70-A6BF-797EAEFA542D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EEB544-CA9A-4193-B182-3AC43EF7D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1643" yWindow="1335" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1592,19 +1592,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;森田朋依&gt;(HCC)</t>
-    <rPh sb="1" eb="3">
-      <t>モリタ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>トモ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>さくらあや
 HANAKO
 玖麗さやか(休)
@@ -1871,6 +1858,19 @@
     <t>&lt;鈴夏&gt;(10.24デビュー予定)
 &lt;涼寧&gt;
 &lt;雅&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;森田朋依&gt;(HCC)(11.8デビュー予定)</t>
+    <rPh sb="1" eb="3">
+      <t>モリタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3081,10 +3081,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>12</v>
@@ -3111,7 +3111,7 @@
         <v>14</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>19</v>
@@ -3123,7 +3123,7 @@
         <v>103</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>78</v>
@@ -4256,7 +4256,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4504,7 +4504,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
@@ -4741,7 +4741,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>36</v>
@@ -4751,7 +4751,7 @@
         <v>195</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>18</v>
@@ -4801,7 +4801,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4902,7 +4902,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>121</v>
@@ -4951,7 +4951,7 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>192</v>
@@ -4960,7 +4960,7 @@
         <v>200</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>140</v>
@@ -5025,7 +5025,7 @@
         <v>180</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>64</v>
@@ -5053,11 +5053,11 @@
         <v>106</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5073,7 +5073,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>130</v>
@@ -5082,13 +5082,13 @@
         <v>177</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>84</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>154</v>
@@ -5104,7 +5104,7 @@
         <v>172</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5112,14 +5112,14 @@
         <v>105</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>178</v>
@@ -5144,7 +5144,7 @@
         <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
@@ -5169,11 +5169,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5190,22 +5190,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>169</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="H55" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5218,7 +5218,7 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EEB544-CA9A-4193-B182-3AC43EF7D2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203E5AD4-7425-4411-9811-836C51A52AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1643" yWindow="1335" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="12893" yWindow="1020" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -68,10 +68,6 @@
     <t>彩羽匠</t>
   </si>
   <si>
-    <t>AWG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>デビュー年</t>
     <rPh sb="4" eb="5">
       <t>ネン</t>
@@ -1204,12 +1200,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;小谷さつき&gt;
-&lt;桃羽もえは&gt;
-&lt;AHI&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>小橋マリカ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1281,13 +1271,6 @@
     <rPh sb="12" eb="14">
       <t>ニシムラ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>松橋ななを
-山根百合
-確変むぎ
-松﨑紗弥</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1492,10 +1475,6 @@
   </si>
   <si>
     <t>サファイア・リード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>惡斗</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1870,6 +1849,34 @@
     </rPh>
     <rPh sb="4" eb="5">
       <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWG/ACTRIUM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>松橋ななを
+山根百合
+確変むぎ
+松﨑紗弥
+初江律香(ACTRIUM)
+真白恵茉(ACTRIUM)
+西尾咲良(ACTRIUM)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>惡斗(ACTRIUM)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>//&lt;小谷さつき&gt;
+//&lt;桃羽もえは&gt;
+//&lt;AHI&gt;
+&lt;紅葉&gt;(ACTRIUM)</t>
+    <rPh sb="29" eb="31">
+      <t>クレハ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2463,7 +2470,7 @@
     <tableColumn id="1" xr3:uid="{C5BCADDE-F600-4480-BD2B-E93168A1BF7F}" name="デビュー年" dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{7319872F-B1DE-47E8-ADFA-F5962E445AE2}" name="Stardom" dataDxfId="20"/>
     <tableColumn id="22" xr3:uid="{8EA6491D-1F78-431F-AD9B-C8AB4F6616E9}" name="TJPW" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{6DD05DFF-D195-4CF5-BFC5-531553A9ADC5}" name="AWG/ACTRIUM" dataDxfId="18"/>
     <tableColumn id="3" xr3:uid="{CA5FBB65-FE37-40A8-B1DD-0182D7DD64C3}" name="マリーゴールド" dataDxfId="17"/>
     <tableColumn id="27" xr3:uid="{50745B86-8D07-4F72-B93E-5C2E105BB03C}" name="アイスリボン/Hotシュシュ/COR" dataDxfId="16"/>
     <tableColumn id="17" xr3:uid="{C0123278-DCF4-45DB-8696-FC0805957C5C}" name="Diana" dataDxfId="15"/>
@@ -2811,7 +2818,7 @@
     <col min="2" max="2" width="13.6875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.5625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.0625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.6875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.875" bestFit="1" customWidth="1"/>
@@ -2841,7 +2848,7 @@
   <sheetData>
     <row r="1" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2867,7 +2874,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2891,7 +2898,7 @@
      LEN(E5:E1001) - LEN(SUBSTITUTE(E5:E1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" cm="1">
         <f t="array" ref="F2">SUMPRODUCT(
@@ -3069,70 +3076,70 @@
     </row>
     <row r="4" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
@@ -3152,7 +3159,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -3256,7 +3263,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3270,7 +3277,7 @@
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
@@ -3436,7 +3443,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W13" s="3"/>
       <c r="Y13" s="1"/>
@@ -3464,7 +3471,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -3473,10 +3480,10 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
@@ -3511,7 +3518,7 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -3531,7 +3538,7 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -3540,7 +3547,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -3582,10 +3589,10 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3775,7 +3782,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3786,10 +3793,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3824,7 +3831,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3848,7 +3855,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3861,7 +3868,7 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3895,10 +3902,10 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -3913,7 +3920,7 @@
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3934,7 +3941,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="W27" s="3"/>
       <c r="Y27" s="1"/>
@@ -3952,7 +3959,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -3961,7 +3968,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3974,7 +3981,7 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
@@ -3994,7 +4001,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -4005,7 +4012,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -4045,7 +4052,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W30" s="3"/>
       <c r="Y30" s="1"/>
@@ -4101,7 +4108,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4115,10 +4122,10 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4148,13 +4155,13 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="W33" s="3"/>
       <c r="Y33" s="1"/>
@@ -4174,16 +4181,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4194,11 +4201,11 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
@@ -4231,11 +4238,11 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4250,13 +4257,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4272,11 +4279,11 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4310,7 +4317,7 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="W37" s="3"/>
       <c r="Y37" s="1"/>
@@ -4336,12 +4343,12 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -4349,7 +4356,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4368,15 +4375,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4386,14 +4393,14 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4408,16 +4415,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4427,7 +4434,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4438,10 +4445,10 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4457,15 +4464,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4478,18 +4485,18 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4504,10 +4511,10 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -4527,10 +4534,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4545,10 +4552,10 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -4556,7 +4563,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4569,11 +4576,11 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4588,11 +4595,11 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4600,7 +4607,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -4613,10 +4620,10 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4631,45 +4638,45 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
@@ -4684,49 +4691,49 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4741,33 +4748,33 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4778,10 +4785,10 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4796,12 +4803,12 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4809,7 +4816,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4817,16 +4824,16 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4841,46 +4848,46 @@
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4896,34 +4903,34 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4933,10 +4940,10 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4951,51 +4958,51 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5010,54 +5017,54 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5073,53 +5080,53 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5129,51 +5136,51 @@
       <c r="AF53" s="1"/>
       <c r="AJ53" s="1"/>
     </row>
-    <row r="54" spans="2:36" ht="66" x14ac:dyDescent="0.7">
+    <row r="54" spans="2:36" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B54" s="3">
         <v>2026</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5186,30 +5193,30 @@
     </row>
     <row r="55" spans="2:36" ht="82.5" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5218,13 +5225,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>
@@ -5246,7 +5253,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5319,13 +5326,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.7">
@@ -5334,7 +5341,7 @@
         <v>1977</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.7">
@@ -5413,7 +5420,7 @@
         <v>1988</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.7">
@@ -5506,7 +5513,7 @@
         <v>2001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.7">
@@ -5539,7 +5546,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5590,7 +5597,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5624,7 +5631,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5640,7 +5647,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.7">
@@ -5659,13 +5666,13 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.7">
@@ -5674,34 +5681,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5710,10 +5717,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203E5AD4-7425-4411-9811-836C51A52AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA26EA03-A7A4-4D7C-A6E7-8A677BB15139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12893" yWindow="1020" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1557,20 +1557,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;七世真理子&gt;(Rose)(2026.10.17デビュー予定)
-&lt;星野 さやか&gt;(九州女子プロレス)
-&lt;AYANO&gt;(九州女子プロレス)
-&lt;KAORI&gt;(九州女子プロレス)
-&lt;KARIN&gt;(九州女子プロレス)</t>
-    <rPh sb="28" eb="30">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="41" eb="45">
-      <t>キュウシュウジョシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>さくらあや
 HANAKO
 玖麗さやか(休)
@@ -1721,12 +1707,6 @@
   <si>
     <t>志翠ヒカリ
 Ayaka</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>堀このみ(Rose)(休)
-彩桜(アップタウン)
-結菜(伊藤道場)(休)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1878,6 +1858,23 @@
     <rPh sb="29" eb="31">
       <t>クレハ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;星野 さやか&gt;(九州女子プロレス)
+&lt;AYANO&gt;(九州女子プロレス)
+&lt;KAORI&gt;(九州女子プロレス)
+&lt;KARIN&gt;(九州女子プロレス)</t>
+    <rPh sb="9" eb="13">
+      <t>キュウシュウジョシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堀このみ(Rose)
+彩桜(アップタウン)
+結菜(伊藤道場)(休)
+七世真理子(Rose)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3085,13 +3082,13 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -3118,7 +3115,7 @@
         <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>18</v>
@@ -3130,7 +3127,7 @@
         <v>102</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>77</v>
@@ -4263,7 +4260,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4421,7 +4418,7 @@
         <v>33</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>96</v>
@@ -4511,7 +4508,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>34</v>
@@ -4748,7 +4745,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>35</v>
@@ -4758,7 +4755,7 @@
         <v>192</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
@@ -4808,7 +4805,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4898,7 +4895,7 @@
       <c r="AF49" s="1"/>
       <c r="AJ49" s="1"/>
     </row>
-    <row r="50" spans="2:36" ht="132" x14ac:dyDescent="0.7">
+    <row r="50" spans="2:36" ht="115.5" x14ac:dyDescent="0.7">
       <c r="B50" s="3">
         <v>2022</v>
       </c>
@@ -4909,7 +4906,7 @@
         <v>31</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>120</v>
@@ -4958,7 +4955,7 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>189</v>
@@ -4967,7 +4964,7 @@
         <v>196</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>139</v>
@@ -5032,7 +5029,7 @@
         <v>177</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>63</v>
@@ -5060,11 +5057,11 @@
         <v>105</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5080,7 +5077,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>129</v>
@@ -5089,13 +5086,13 @@
         <v>175</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>83</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>153</v>
@@ -5111,7 +5108,7 @@
         <v>170</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5119,14 +5116,14 @@
         <v>104</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5142,16 +5139,16 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>151</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
@@ -5176,11 +5173,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5191,28 +5188,28 @@
       <c r="AF54" s="1"/>
       <c r="AJ54" s="1"/>
     </row>
-    <row r="55" spans="2:36" ht="82.5" x14ac:dyDescent="0.7">
+    <row r="55" spans="2:36" ht="66" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5225,13 +5222,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA26EA03-A7A4-4D7C-A6E7-8A677BB15139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E526D3FA-3027-428F-A978-F5534C767062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -207,13 +207,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>救世忍者乱丸</t>
-    <rPh sb="0" eb="6">
-      <t>キュウセイニンジャランマル</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MARU</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1875,6 +1868,17 @@
 彩桜(アップタウン)
 結菜(伊藤道場)(休)
 七世真理子(Rose)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>救世忍者乱丸
+浜田文子</t>
+    <rPh sb="0" eb="6">
+      <t>キュウセイニンジャランマル</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ハマダアヤコ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2845,7 +2849,7 @@
   <sheetData>
     <row r="1" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -2871,7 +2875,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -3039,7 +3043,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -3079,43 +3083,43 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>18</v>
@@ -3124,16 +3128,16 @@
         <v>3</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>6</v>
@@ -3440,7 +3444,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="W13" s="3"/>
       <c r="Y13" s="1"/>
@@ -3477,7 +3481,7 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>9</v>
@@ -3515,7 +3519,7 @@
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
@@ -3586,10 +3590,10 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3779,7 +3783,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -3790,10 +3794,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3828,7 +3832,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3852,7 +3856,7 @@
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -3865,7 +3869,7 @@
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
@@ -3875,7 +3879,7 @@
       <c r="AF25" s="1"/>
       <c r="AJ25" s="1"/>
     </row>
-    <row r="26" spans="2:36" ht="16.5" x14ac:dyDescent="0.7">
+    <row r="26" spans="2:36" ht="33" x14ac:dyDescent="0.7">
       <c r="B26" s="3">
         <v>1998</v>
       </c>
@@ -3899,10 +3903,10 @@
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -3917,7 +3921,7 @@
         <v>1999</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -3938,7 +3942,7 @@
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="W27" s="3"/>
       <c r="Y27" s="1"/>
@@ -3956,7 +3960,7 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -3965,7 +3969,7 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
@@ -3978,7 +3982,7 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
@@ -4009,7 +4013,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -4049,7 +4053,7 @@
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W30" s="3"/>
       <c r="Y30" s="1"/>
@@ -4105,7 +4109,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4119,10 +4123,10 @@
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4152,13 +4156,13 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="W33" s="3"/>
       <c r="Y33" s="1"/>
@@ -4178,16 +4182,16 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
@@ -4198,11 +4202,11 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
@@ -4235,11 +4239,11 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4254,13 +4258,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4276,11 +4280,11 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4314,7 +4318,7 @@
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W37" s="3"/>
       <c r="Y37" s="1"/>
@@ -4340,12 +4344,12 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -4353,7 +4357,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4372,15 +4376,15 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -4390,14 +4394,14 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4412,16 +4416,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4431,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
@@ -4442,10 +4446,10 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="W40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4461,15 +4465,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4482,18 +4486,18 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4508,10 +4512,10 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -4531,10 +4535,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4549,10 +4553,10 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -4560,7 +4564,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -4573,11 +4577,11 @@
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4592,11 +4596,11 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4617,10 +4621,10 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4635,7 +4639,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4643,37 +4647,37 @@
         <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
@@ -4688,16 +4692,16 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4707,30 +4711,30 @@
         <v>21</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4745,33 +4749,33 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -4782,10 +4786,10 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4800,12 +4804,12 @@
         <v>2020</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4813,7 +4817,7 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -4821,16 +4825,16 @@
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4845,26 +4849,26 @@
         <v>2021</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>20</v>
@@ -4874,17 +4878,17 @@
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4900,34 +4904,34 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4937,10 +4941,10 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4955,51 +4959,51 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5014,54 +5018,54 @@
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5077,53 +5081,53 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5139,45 +5143,45 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5190,30 +5194,30 @@
     </row>
     <row r="55" spans="2:36" ht="66" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="H55" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5222,13 +5226,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>
@@ -5250,7 +5254,7 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5323,7 +5327,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
@@ -5543,7 +5547,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5594,7 +5598,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5628,7 +5632,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5663,7 +5667,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5678,34 +5682,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5714,10 +5718,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E526D3FA-3027-428F-A978-F5534C767062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159B0248-4234-422C-9E90-513FDC0025AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1813,19 +1813,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;森田朋依&gt;(HCC)(11.8デビュー予定)</t>
-    <rPh sb="1" eb="3">
-      <t>モリタ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>トモ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AWG/ACTRIUM</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1878,6 +1865,13 @@
     </rPh>
     <rPh sb="7" eb="11">
       <t>ハマダアヤコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;森田ともえ&gt;(HCC)(11.8デビュー予定)</t>
+    <rPh sb="1" eb="3">
+      <t>モリタ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3086,7 +3080,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>207</v>
@@ -3906,7 +3900,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4422,7 +4416,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -5146,7 +5140,7 @@
         <v>216</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>150</v>
@@ -5181,7 +5175,7 @@
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5201,13 +5195,13 @@
         <v>223</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>230</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>213</v>
@@ -5232,7 +5226,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159B0248-4234-422C-9E90-513FDC0025AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A371201-9287-44AA-B050-CAC9F03BA179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1624,10 +1624,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>蒼あいな</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;中嶋野乃&gt;
 &lt;えん&gt;</t>
     <phoneticPr fontId="1"/>
@@ -1851,13 +1847,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>堀このみ(Rose)
-彩桜(アップタウン)
-結菜(伊藤道場)(休)
-七世真理子(Rose)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>救世忍者乱丸
 浜田文子</t>
     <rPh sb="0" eb="6">
@@ -1872,6 +1861,29 @@
     <t>&lt;森田ともえ&gt;(HCC)(11.8デビュー予定)</t>
     <rPh sb="1" eb="3">
       <t>モリタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒼あいな
+4代目めでタイガール(?)</t>
+    <rPh sb="6" eb="8">
+      <t>ダイメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堀このみ(Rose)
+彩桜(アップタウン)
+結菜(伊藤道場)(休)
+七世真理子(Rose)
+RIRU(道頓堀)
+仁々芽咲(道頓堀)</t>
+    <rPh sb="51" eb="54">
+      <t>ドウトンボリ</t>
+    </rPh>
+    <rPh sb="61" eb="64">
+      <t>ドウトンボリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2869,7 +2881,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -3029,7 +3041,7 @@
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="W2" s="1" cm="1">
         <f t="array" ref="W2">SUMPRODUCT(
@@ -3037,7 +3049,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -3080,7 +3092,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>207</v>
@@ -3125,7 +3137,7 @@
         <v>101</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>76</v>
@@ -3900,7 +3912,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4416,7 +4428,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -4506,7 +4518,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>33</v>
@@ -4753,7 +4765,7 @@
         <v>191</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
@@ -4803,7 +4815,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4904,7 +4916,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>119</v>
@@ -5027,7 +5039,7 @@
         <v>176</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>62</v>
@@ -5055,11 +5067,11 @@
         <v>104</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5075,7 +5087,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>128</v>
@@ -5084,13 +5096,13 @@
         <v>174</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>152</v>
@@ -5114,14 +5126,14 @@
         <v>103</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5137,10 +5149,10 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>150</v>
@@ -5171,11 +5183,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5192,22 +5204,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5220,13 +5232,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A371201-9287-44AA-B050-CAC9F03BA179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0182560F-5DBF-446E-BFE8-071396C85A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1212,14 +1212,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鈴木ユラ(アルマリブレ)
-真白優希(Rose)(休)</t>
-    <rPh sb="24" eb="25">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>沙恵(休)</t>
     <rPh sb="3" eb="4">
       <t>キュウ</t>
@@ -1311,14 +1303,6 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ミヤコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>藍川はるか
-ノア・ヒカリ</t>
-    <rPh sb="0" eb="2">
-      <t>アイカワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1798,11 +1782,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;Y&gt;
-&lt;みく&gt;(11.29デビュー予定)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;鈴夏&gt;(10.24デビュー予定)
 &lt;涼寧&gt;
 &lt;雅&gt;</t>
@@ -1884,6 +1863,50 @@
     </rPh>
     <rPh sb="61" eb="64">
       <t>ドウトンボリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;Y&gt;
+&lt;みく&gt;(11.29デビュー予定)
+&lt;秋田ワン子&gt;(10.25デビュー予定)</t>
+    <rPh sb="23" eb="25">
+      <t>アキタ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木ユラ(アルマリブレ)
+真白優希(Rose)(休)(10.31退団予定)</t>
+    <rPh sb="24" eb="25">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="32" eb="36">
+      <t>タイダンヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>藍川はるか
+ノア・ヒカリ
+ももねえ(2026.12月引退予定)</t>
+    <rPh sb="0" eb="2">
+      <t>アイカワ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>インタイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2881,7 +2904,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2937,7 +2960,7 @@
      LEN(I5:I1001) - LEN(SUBSTITUTE(I5:I1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="1" cm="1">
         <f t="array" ref="J2">SUMPRODUCT(
@@ -3049,7 +3072,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -3092,13 +3115,13 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -3125,7 +3148,7 @@
         <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>18</v>
@@ -3137,7 +3160,7 @@
         <v>101</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>76</v>
@@ -3912,7 +3935,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4188,7 +4211,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -4270,7 +4293,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4290,7 +4313,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4363,7 +4386,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4428,7 +4451,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -4474,12 +4497,12 @@
         <v>159</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4518,7 +4541,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>33</v>
@@ -4559,7 +4582,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>31</v>
@@ -4606,7 +4629,7 @@
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4673,7 +4696,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4698,7 +4721,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>117</v>
@@ -4707,7 +4730,7 @@
         <v>120</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4737,10 +4760,10 @@
         <v>80</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4755,17 +4778,17 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
@@ -4774,7 +4797,7 @@
         <v>139</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4795,7 +4818,7 @@
         <v>121</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4815,7 +4838,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4837,7 +4860,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>147</v>
@@ -4861,7 +4884,7 @@
         <v>154</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>7</v>
@@ -4874,7 +4897,7 @@
         <v>61</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>20</v>
@@ -4894,7 +4917,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4910,19 +4933,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>119</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>16</v>
@@ -4947,7 +4970,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>135</v>
@@ -4965,16 +4988,16 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>138</v>
@@ -5006,10 +5029,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5036,10 +5059,10 @@
         <v>109</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>62</v>
@@ -5067,11 +5090,11 @@
         <v>104</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5087,22 +5110,22 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>128</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>152</v>
@@ -5118,7 +5141,7 @@
         <v>169</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5126,14 +5149,14 @@
         <v>103</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5149,23 +5172,23 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>150</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>166</v>
@@ -5183,11 +5206,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5204,26 +5227,26 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="H55" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5232,13 +5255,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0182560F-5DBF-446E-BFE8-071396C85A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB7D511-381A-433D-9BBC-E79B6128E53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="12893" yWindow="1020" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -1707,12 +1707,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;ユウカ&gt;(仮)
-&lt;双葉しおり&gt;(仮)
-&lt;ゆい&gt;(11.8デビュー予定)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>NENE
 Syansyan(新臺灣)</t>
     <rPh sb="14" eb="15">
@@ -1908,6 +1902,12 @@
     <rPh sb="28" eb="30">
       <t>ヨテイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;ユウカ&gt;(仮)
+&lt;双葉しおり&gt;(11.8デビュー予定)
+&lt;ゆい&gt;(11.8デビュー予定)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3115,7 +3115,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>205</v>
@@ -3935,7 +3935,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4451,7 +4451,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -4763,7 +4763,7 @@
         <v>172</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4860,7 +4860,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>147</v>
@@ -4939,7 +4939,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>119</v>
@@ -5062,7 +5062,7 @@
         <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>62</v>
@@ -5110,7 +5110,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>128</v>
@@ -5119,13 +5119,13 @@
         <v>173</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>152</v>
@@ -5156,7 +5156,7 @@
         <v>218</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5175,7 +5175,7 @@
         <v>213</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>150</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5227,22 +5227,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>210</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5261,7 +5261,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB7D511-381A-433D-9BBC-E79B6128E53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9896F8F-FE04-4B7F-88B4-7BCE6100CA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12893" yWindow="1020" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1043,10 +1043,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ザ・レディAI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>&lt;ひな&gt;
 &lt;希咲みなみ&gt;
 &lt;直江ミう&gt;</t>
@@ -1776,12 +1772,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;鈴夏&gt;(10.24デビュー予定)
-&lt;涼寧&gt;
-&lt;雅&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>AWG/ACTRIUM</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1908,6 +1898,16 @@
     <t>&lt;ユウカ&gt;(仮)
 &lt;双葉しおり&gt;(11.8デビュー予定)
 &lt;ゆい&gt;(11.8デビュー予定)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;涼寧&gt;
+&lt;雅&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ザ・レディAI
+鈴夏</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3115,13 +3115,13 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -3148,7 +3148,7 @@
         <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>18</v>
@@ -3160,7 +3160,7 @@
         <v>101</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>76</v>
@@ -3826,7 +3826,7 @@
         <v>131</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3935,7 +3935,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4138,7 +4138,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4155,7 +4155,7 @@
         <v>48</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4211,12 +4211,12 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
@@ -4293,7 +4293,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4386,7 +4386,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4451,7 +4451,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -4494,15 +4494,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4515,7 +4515,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4526,7 +4526,7 @@
         <v>116</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4541,7 +4541,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>33</v>
@@ -4564,7 +4564,7 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>144</v>
@@ -4582,7 +4582,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>31</v>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4653,7 +4653,7 @@
         <v>99</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4696,7 +4696,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4721,7 +4721,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>117</v>
@@ -4730,7 +4730,7 @@
         <v>120</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4740,7 +4740,7 @@
         <v>21</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>57</v>
@@ -4760,10 +4760,10 @@
         <v>80</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4778,17 +4778,17 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
@@ -4797,7 +4797,7 @@
         <v>139</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4818,7 +4818,7 @@
         <v>121</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4838,7 +4838,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4860,7 +4860,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>147</v>
@@ -4881,23 +4881,23 @@
         <v>40</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>20</v>
@@ -4917,7 +4917,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4933,19 +4933,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>119</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>16</v>
@@ -4970,7 +4970,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>135</v>
@@ -4988,16 +4988,16 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>138</v>
@@ -5029,10 +5029,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5059,10 +5059,10 @@
         <v>109</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>62</v>
@@ -5075,7 +5075,7 @@
         <v>91</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>134</v>
@@ -5090,11 +5090,11 @@
         <v>104</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5110,25 +5110,25 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>128</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -5138,10 +5138,10 @@
         <v>137</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5149,14 +5149,14 @@
         <v>103</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5172,26 +5172,26 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>149</v>
@@ -5206,11 +5206,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5227,26 +5227,26 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5255,13 +5255,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>
@@ -5727,7 +5727,7 @@
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
@@ -5747,7 +5747,7 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>129</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9896F8F-FE04-4B7F-88B4-7BCE6100CA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7997D852-E3B9-4AC7-99EB-B0849C29312A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12893" yWindow="1020" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -1030,11 +1030,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>柳川澄樺
-神姫楽ミサ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>陽岬来永</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1582,24 +1577,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ビクトリア弓月
-田中きずな(10.24復帰予定)
-瀬戸レア</t>
-    <rPh sb="8" eb="10">
-      <t>タナカ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>フッキ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>セト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アイスリボン/Hotシュシュ/COR</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1616,29 +1593,6 @@
     <t>&lt;浜名あみ&gt;(10.25デビュー予定)
 &lt;TSUBAKI&gt;(10.25デビュー予定)</t>
     <rPh sb="16" eb="18">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>石川奈青(休)
-桜井麻衣(10.24退団予定)</t>
-    <rPh sb="0" eb="4">
-      <t>イシカワナオ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクライ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>マイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>タイダン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
       <t>ヨテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1908,6 +1862,37 @@
   <si>
     <t>ザ・レディAI
 鈴夏</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビクトリア弓月
+田中きずな
+瀬戸レア</t>
+    <rPh sb="8" eb="10">
+      <t>タナカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>石川奈青(休)</t>
+    <rPh sb="0" eb="4">
+      <t>イシカワナオ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>柳川澄樺
+神姫楽ミサ
+桜井麻衣(休)</t>
+    <rPh sb="16" eb="17">
+      <t>キュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2936,7 +2921,7 @@
      LEN(F5:F1001) - LEN(SUBSTITUTE(F5:F1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" cm="1">
         <f t="array" ref="G2">SUMPRODUCT(
@@ -3072,7 +3057,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -3115,13 +3100,13 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -3148,7 +3133,7 @@
         <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>18</v>
@@ -3160,7 +3145,7 @@
         <v>101</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>76</v>
@@ -3826,7 +3811,7 @@
         <v>131</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3935,7 +3920,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4138,7 +4123,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4155,7 +4140,7 @@
         <v>48</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4211,12 +4196,12 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
@@ -4293,7 +4278,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4313,7 +4298,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4386,7 +4371,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4451,7 +4436,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -4494,15 +4479,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4515,7 +4500,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4526,7 +4511,7 @@
         <v>116</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4541,7 +4526,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>33</v>
@@ -4564,7 +4549,7 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>144</v>
@@ -4582,7 +4567,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>31</v>
@@ -4610,7 +4595,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4629,7 +4614,7 @@
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4653,7 +4638,7 @@
         <v>99</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4696,7 +4681,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
@@ -4721,7 +4706,7 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>117</v>
@@ -4730,7 +4715,7 @@
         <v>120</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4740,7 +4725,7 @@
         <v>21</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>57</v>
@@ -4760,10 +4745,10 @@
         <v>80</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4778,17 +4763,17 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
@@ -4797,7 +4782,7 @@
         <v>139</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
@@ -4818,7 +4803,7 @@
         <v>121</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4838,7 +4823,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4860,10 +4845,10 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4881,23 +4866,23 @@
         <v>40</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>20</v>
@@ -4917,7 +4902,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4933,19 +4918,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>119</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>16</v>
@@ -4970,7 +4955,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>135</v>
@@ -4988,16 +4973,16 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>138</v>
@@ -5029,10 +5014,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5059,10 +5044,10 @@
         <v>109</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>62</v>
@@ -5075,7 +5060,7 @@
         <v>91</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>134</v>
@@ -5090,11 +5075,11 @@
         <v>104</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5110,25 +5095,25 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>128</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -5138,10 +5123,10 @@
         <v>137</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5149,14 +5134,14 @@
         <v>103</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5172,45 +5157,45 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5227,26 +5212,26 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="H55" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5255,13 +5240,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>
@@ -5727,7 +5712,7 @@
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
@@ -5747,7 +5732,7 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>129</v>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7997D852-E3B9-4AC7-99EB-B0849C29312A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B74649E-16DA-46F5-ABCD-7796789E864A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12893" yWindow="1020" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="239">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1680,15 +1680,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>山岡聖怜(10.24復帰予定)
-心希
-山﨑裕花</t>
-    <rPh sb="16" eb="18">
-      <t>シンノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鉄アキラ
 姫ゆりあ(10.18復帰予定)
 金屋あんね
@@ -1892,6 +1883,15 @@
 桜井麻衣(休)</t>
     <rPh sb="16" eb="17">
       <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山岡聖怜
+心希
+山﨑裕花</t>
+    <rPh sb="5" eb="7">
+      <t>シンノ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3100,7 +3100,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>203</v>
@@ -3920,7 +3920,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4436,7 +4436,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -4748,7 +4748,7 @@
         <v>170</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4823,7 +4823,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4845,10 +4845,10 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4924,7 +4924,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>119</v>
@@ -4982,7 +4982,7 @@
         <v>191</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>138</v>
@@ -5095,7 +5095,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>128</v>
@@ -5104,7 +5104,7 @@
         <v>171</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
@@ -5141,7 +5141,7 @@
         <v>214</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5160,10 +5160,10 @@
         <v>209</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>200</v>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5212,22 +5212,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="G55" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>207</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5246,7 +5246,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B74649E-16DA-46F5-ABCD-7796789E864A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4048AF06-E7C5-43B8-BF67-187D1CC8B3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12893" yWindow="1020" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="3375" yWindow="2303" windowWidth="14873" windowHeight="11332" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="240">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1467,10 +1467,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ちゅら愛花</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>郷田明日香(休)
 ブランキー真帆
 Chi Chi
@@ -1587,14 +1583,6 @@
   </si>
   <si>
     <t>渡辺桃</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;浜名あみ&gt;(10.25デビュー予定)
-&lt;TSUBAKI&gt;(10.25デビュー予定)</t>
-    <rPh sb="16" eb="18">
-      <t>ヨテイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1796,21 +1784,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>&lt;Y&gt;
-&lt;みく&gt;(11.29デビュー予定)
-&lt;秋田ワン子&gt;(10.25デビュー予定)</t>
-    <rPh sb="23" eb="25">
-      <t>アキタ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鈴木ユラ(アルマリブレ)
 真白優希(Rose)(休)(10.31退団予定)</t>
     <rPh sb="24" eb="25">
@@ -1893,6 +1866,28 @@
     <rPh sb="5" eb="7">
       <t>シンノ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;浜名あみ&gt;(10.25デビュー予定)
+</t>
+    <rPh sb="16" eb="18">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TSUBAKI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ちゅら愛花
+秋田ワン子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;Y&gt;
+&lt;みく&gt;(11.29デビュー予定)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2889,7 +2884,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2937,7 +2932,7 @@
      LEN(H5:H1001) - LEN(SUBSTITUTE(H5:H1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" cm="1">
         <f t="array" ref="I2">SUMPRODUCT(
@@ -3100,13 +3095,13 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -3133,7 +3128,7 @@
         <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>18</v>
@@ -3145,7 +3140,7 @@
         <v>101</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>76</v>
@@ -3920,7 +3915,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4278,7 +4273,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4436,7 +4431,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>95</v>
@@ -4526,7 +4521,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>33</v>
@@ -4748,7 +4743,7 @@
         <v>170</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4763,7 +4758,7 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>34</v>
@@ -4773,7 +4768,7 @@
         <v>187</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
@@ -4823,7 +4818,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4845,10 +4840,10 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -4902,7 +4897,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4924,7 +4919,7 @@
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>119</v>
@@ -4955,7 +4950,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="W50" s="3" t="s">
         <v>135</v>
@@ -4973,7 +4968,7 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>184</v>
@@ -4982,7 +4977,7 @@
         <v>191</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>138</v>
@@ -5014,10 +5009,10 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5047,7 +5042,7 @@
         <v>173</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>62</v>
@@ -5075,11 +5070,11 @@
         <v>104</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5095,7 +5090,7 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>128</v>
@@ -5104,13 +5099,13 @@
         <v>171</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>150</v>
@@ -5126,7 +5121,7 @@
         <v>167</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -5134,14 +5129,14 @@
         <v>103</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5157,20 +5152,22 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H54" s="3"/>
+        <v>199</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="I54" s="3" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>182</v>
@@ -5191,11 +5188,11 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5212,22 +5209,22 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -5240,13 +5237,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4048AF06-E7C5-43B8-BF67-187D1CC8B3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E3AD47-624B-4C20-A1E3-2B209FD536E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="2303" windowWidth="14873" windowHeight="11332" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="1013" yWindow="975" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1869,18 +1869,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;浜名あみ&gt;(10.25デビュー予定)
-</t>
-    <rPh sb="16" eb="18">
-      <t>ヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>TSUBAKI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ちゅら愛花
 秋田ワン子</t>
     <phoneticPr fontId="1"/>
@@ -1888,6 +1876,11 @@
   <si>
     <t>&lt;Y&gt;
 &lt;みく&gt;(11.29デビュー予定)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TSUBAKI
+浜名あみ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2884,7 +2877,7 @@
     <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.7">
       <c r="B2" s="1">
         <f>SUM(C2:RW2)</f>
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C2" s="1" cm="1">
         <f t="array" ref="C2">SUMPRODUCT(
@@ -2932,7 +2925,7 @@
      LEN(H5:H1001) - LEN(SUBSTITUTE(H5:H1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" cm="1">
         <f t="array" ref="I2">SUMPRODUCT(
@@ -5164,10 +5157,10 @@
         <v>199</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>182</v>
@@ -5220,11 +5213,9 @@
       <c r="G55" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>236</v>
-      </c>
+      <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E3AD47-624B-4C20-A1E3-2B209FD536E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19275F8-A3EC-4A03-AE63-86B3486E2FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1013" yWindow="975" windowWidth="14872" windowHeight="11333" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
   <sheets>
     <sheet name="現役選手デビュー年団体別一覧" sheetId="1" r:id="rId1"/>
@@ -601,31 +601,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>野崎渚
-真琴
-松本浩代
-雫有希</t>
-    <rPh sb="0" eb="2">
-      <t>ノザキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ナギサ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>マコト</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>マツモト</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒロヨ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>シズクアキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ジュリア(WWE)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1012,13 +987,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>雪妃真矢(休)</t>
-    <rPh sb="5" eb="6">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>里奈</t>
     <rPh sb="0" eb="2">
       <t>リナ</t>
@@ -1162,14 +1130,6 @@
   <si>
     <t>まなせゆうな(休)</t>
     <rPh sb="7" eb="8">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>永島千佳世
-倉垣翼(休)</t>
-    <rPh sb="10" eb="11">
       <t>キュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1784,17 +1744,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鈴木ユラ(アルマリブレ)
-真白優希(Rose)(休)(10.31退団予定)</t>
-    <rPh sb="24" eb="25">
-      <t>キュウ</t>
-    </rPh>
-    <rPh sb="32" eb="36">
-      <t>タイダンヨテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>藍川はるか
 ノア・ヒカリ
 ももねえ(2026.12月引退予定)</t>
@@ -1851,15 +1800,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>柳川澄樺
-神姫楽ミサ
-桜井麻衣(休)</t>
-    <rPh sb="16" eb="17">
-      <t>キュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>山岡聖怜
 心希
 山﨑裕花</t>
@@ -1881,6 +1821,57 @@
   <si>
     <t>TSUBAKI
 浜名あみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>柳川澄樺
+神姫楽ミサ
+桜井麻衣(休)
+真白優希(休)</t>
+    <rPh sb="16" eb="17">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木ユラ(アルマリブレ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雪妃真矢</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野崎渚
+真琴
+松本浩代
+雫有希(12/20から休)</t>
+    <rPh sb="0" eb="2">
+      <t>ノザキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナギサ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マコト</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>マツモト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒロヨ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>シズクアキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>永島千佳世
+倉垣翼</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3037,7 +3028,7 @@
      LEN(V5:V1001) - LEN(SUBSTITUTE(V5:V1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W2" s="1" cm="1">
         <f t="array" ref="W2">SUMPRODUCT(
@@ -3045,7 +3036,7 @@
      LEN(W5:W1001) - LEN(SUBSTITUTE(W5:W1001, CHAR(10), "")) + 1
   )
 )</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -3088,13 +3079,13 @@
         <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
@@ -3115,13 +3106,13 @@
         <v>45</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>18</v>
@@ -3130,10 +3121,10 @@
         <v>3</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>76</v>
@@ -3446,7 +3437,7 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="W13" s="3"/>
       <c r="Y13" s="1"/>
@@ -3592,10 +3583,10 @@
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
@@ -3796,10 +3787,10 @@
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -3834,7 +3825,7 @@
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -3908,7 +3899,7 @@
         <v>63</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
@@ -4111,7 +4102,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -4128,7 +4119,7 @@
         <v>48</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
@@ -4164,7 +4155,7 @@
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W33" s="3"/>
       <c r="Y33" s="1"/>
@@ -4184,12 +4175,12 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
@@ -4208,7 +4199,7 @@
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="s">
-        <v>88</v>
+        <v>237</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
@@ -4245,7 +4236,7 @@
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
@@ -4260,13 +4251,13 @@
         <v>2008</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -4286,7 +4277,7 @@
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
@@ -4359,7 +4350,7 @@
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="W38" s="3"/>
       <c r="Y38" s="1"/>
@@ -4378,7 +4369,7 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>84</v>
@@ -4403,7 +4394,7 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
@@ -4418,16 +4409,16 @@
         <v>2012</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
@@ -4451,7 +4442,7 @@
         <v>78</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W40" s="3"/>
       <c r="Y40" s="1"/>
@@ -4467,15 +4458,15 @@
         <v>2013</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4488,7 +4479,7 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4496,10 +4487,10 @@
         <v>81</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
@@ -4514,7 +4505,7 @@
         <v>2014</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>33</v>
@@ -4537,10 +4528,10 @@
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
@@ -4555,7 +4546,7 @@
         <v>2015</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>31</v>
@@ -4583,7 +4574,7 @@
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
@@ -4598,11 +4589,11 @@
         <v>2016</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -4623,10 +4614,10 @@
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -4641,7 +4632,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4652,34 +4643,34 @@
         <v>83</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
       <c r="S45" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="T45" s="3"/>
       <c r="U45" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
@@ -4694,16 +4685,16 @@
         <v>2018</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -4713,7 +4704,7 @@
         <v>21</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>57</v>
@@ -4726,17 +4717,17 @@
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3" t="s">
         <v>80</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -4751,30 +4742,30 @@
         <v>2019</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>58</v>
@@ -4788,10 +4779,10 @@
       <c r="T47" s="3"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -4801,7 +4792,7 @@
       <c r="AF47" s="1"/>
       <c r="AJ47" s="1"/>
     </row>
-    <row r="48" spans="2:36" ht="49.5" x14ac:dyDescent="0.7">
+    <row r="48" spans="2:36" ht="66" x14ac:dyDescent="0.7">
       <c r="B48" s="3">
         <v>2020</v>
       </c>
@@ -4811,7 +4802,7 @@
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4833,7 +4824,7 @@
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>234</v>
@@ -4854,23 +4845,23 @@
         <v>40</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>20</v>
@@ -4890,7 +4881,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="W49" s="3"/>
       <c r="Y49" s="1"/>
@@ -4906,19 +4897,19 @@
         <v>2022</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>16</v>
@@ -4933,7 +4924,7 @@
         <v>59</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
@@ -4943,10 +4934,10 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
@@ -4961,51 +4952,51 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>39</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P51" s="3"/>
       <c r="Q51" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -5029,29 +5020,29 @@
         <v>25</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>62</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3" t="s">
@@ -5060,14 +5051,14 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="U52" s="3"/>
       <c r="V52" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="W52" s="3"/>
       <c r="Y52" s="1"/>
@@ -5083,53 +5074,53 @@
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>82</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="U53" s="3"/>
       <c r="V53" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -5145,47 +5136,47 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="J54" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="U54" s="3"/>
       <c r="V54" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="W54" s="3"/>
       <c r="Y54" s="1"/>
@@ -5198,28 +5189,28 @@
     </row>
     <row r="55" spans="2:36" ht="66" x14ac:dyDescent="0.7">
       <c r="B55" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E55" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5228,13 +5219,13 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="W55" s="3"/>
       <c r="Y55" s="1"/>
@@ -5329,7 +5320,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
@@ -5549,7 +5540,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A34" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B34" s="3">
         <v>2006</v>
@@ -5600,7 +5591,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A41" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B41" s="3">
         <v>2013</v>
@@ -5634,7 +5625,7 @@
         <v>2017</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
@@ -5669,7 +5660,7 @@
     </row>
     <row r="50" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A50" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" s="3">
         <v>2022</v>
@@ -5684,34 +5675,34 @@
         <v>2023</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A52" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B52" s="3">
         <v>2024</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" x14ac:dyDescent="0.7">
       <c r="A53" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B53" s="3">
         <v>2025</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A54" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B54" s="3">
         <v>2026</v>
@@ -5720,10 +5711,10 @@
     </row>
     <row r="55" spans="1:3" ht="49.5" x14ac:dyDescent="0.7">
       <c r="A55" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C55" s="3"/>
     </row>

--- a/woman-excel.xlsx
+++ b/woman-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\docker-claudecode\2女子プロレスラーの一覧\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19275F8-A3EC-4A03-AE63-86B3486E2FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BF44B5-8216-4DF3-A526-7B816CB1CD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{006E6351-9C88-4E01-B808-191D08DA05AD}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="240">
   <si>
     <t>Stardom</t>
     <phoneticPr fontId="1"/>
@@ -1872,6 +1872,13 @@
   <si>
     <t>永島千佳世
 倉垣翼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>香藤満月(休)</t>
+    <rPh sb="5" eb="6">
+      <t>キュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4967,7 +4974,7 @@
         <v>137</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>39</v>
